--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,678 @@
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IF Elfsborg vs Västerås SK</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IF Elfsborg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Josko Ried</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Stellenbosch vs Marumo Gallants</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KI Klaksvik vs Lech Poznan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Telstar vs Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Telstar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Acassuso vs Midland</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Midland</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Galatasaray vs Çorum FK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto vs Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sporting CP vs Vitória de Guimaraes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Boston River vs Danubio</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ponte Preta vs Náutico</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Universidad de Concepción vs La Serena</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Universidad de Concepción</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Racing Club vs Banfield</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sport vs Londrina</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -803,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +1576,25 @@
       </c>
       <c r="E5" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,8 +813,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -861,8 +859,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -909,8 +905,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -957,8 +951,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -1005,8 +997,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -1053,8 +1043,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -1101,8 +1089,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -1149,8 +1135,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -1197,8 +1181,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -1245,8 +1227,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -1293,8 +1273,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -1341,8 +1319,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -1389,8 +1365,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -1437,8 +1411,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -1459,6 +1431,342 @@
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC vs LA Galaxy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Monterrey vs FC Juarez</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Real Salt Lake vs Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Colorado Rapids vs Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LAFC vs San Diego FC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LAFC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Atlas vs Tigres UANL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1475,7 +1783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1903,25 @@
       </c>
       <c r="E6" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,8 +1457,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -1505,8 +1503,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>6-1</t>
@@ -1553,8 +1549,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -1601,8 +1595,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -1649,8 +1641,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -1697,8 +1687,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -1745,8 +1733,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -1767,6 +1753,2886 @@
         <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ADO Den Haag vs FC Groningen</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FC Groningen</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Waasland-Beveren vs Anderlecht</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld vs Energie Cottbus</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dynamo Dresden vs SV Darmstadt 98</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Odense Boldklub vs AC Horsens</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Odense Boldklub</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FC Nordsjælland vs Silkeborg IF</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FC Nordsjælland</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IF Brommapojkarna vs Örgryte IS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IF Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Degerfors IF vs IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Djurgården vs AIK</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Watford vs Southampton</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam vs Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FC Twente vs PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hibernian vs Partick Thistle</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stenhousemuir vs Motherwell</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Malaysia vs Vietnam</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Brest</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière vs KAA Gent</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Lyngby Boldklub vs FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GAIS vs Malmö FF</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kalmar FF vs Hammarby IF</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hammarby IF</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FC Basel vs Barcelona</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam vs Heerenveen</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TSV Hartberg vs Austria Vienna</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Austria Vienna</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Burnley vs West Ham United</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Molde vs Tromso</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sarpsborg FK vs Sandefjord</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sarpsborg FK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rangers vs St Mirren</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Eibar vs Tenerife</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Newcastle United vs Strasbourg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Schalke 04 vs Real Madrid</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir vs Kocaelispor</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Frosinone vs Juve Stabia</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad vs Spartak Moscow</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Spartak Moscow</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Genoa vs Ascoli</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Al Orobah vs Abha</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Espanyol vs Levante</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rapid Vienna vs Grazer AK</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Rapid Vienna</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>8-0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Arouca vs Moreirense</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Arouca</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Burgos vs Córdoba</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Girona vs Leganés</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Anorthosis vs Apoel Nicosia</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Apoel Nicosia</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fredrikstad vs Kristiansund BK</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tristán Suárez vs Almirante Brown</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tristán Suárez</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Al Wehda vs Al Shabab</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>6</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Besiktas vs Eyupspor</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Lens vs Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hellas Verona vs Virtus Entella</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Lazio vs Mantova</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Braga vs Gil Vicente</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FC Famalicao vs Maritimo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FC Famalicao</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Las Palmas vs Albacete</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Racing (Córdoba) vs San Martín (San Juan)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Racing (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>River Plate vs Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>New York City FC vs Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York City FC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC vs Portland Timbers</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine vs Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>América vs Atlético de San Luis</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Central Córdoba (Santiago del Estero) vs Instituto (Córdoba)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Instituto (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Santos vs Guadalajara</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1783,7 +4649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,6 +4788,25 @@
       </c>
       <c r="E7" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1935,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,6 +4955,195 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partido_resuelto</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>alerta_1er_tiempo</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1779,8 +1779,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -1827,8 +1825,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -1875,8 +1871,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -1923,8 +1917,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -1971,8 +1963,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -2019,8 +2009,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -2067,8 +2055,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -2115,8 +2101,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -2163,8 +2147,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -2211,8 +2193,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -2259,8 +2239,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -2307,8 +2285,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -2355,8 +2331,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -2403,8 +2377,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -2451,8 +2423,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -2499,8 +2469,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -2547,8 +2515,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -2595,8 +2561,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -2643,8 +2607,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -2691,8 +2653,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -2739,8 +2699,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>2-5</t>
@@ -2787,8 +2745,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -2835,8 +2791,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -2883,8 +2837,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -2931,8 +2883,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -2979,8 +2929,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -3027,8 +2975,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -3075,8 +3021,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -3123,8 +3067,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -3171,8 +3113,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -3219,8 +3159,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -3267,8 +3205,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -3315,8 +3251,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -3363,8 +3297,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -3411,8 +3343,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -3459,8 +3389,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -3507,8 +3435,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -3555,8 +3481,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>8-0</t>
@@ -3603,8 +3527,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -3651,8 +3573,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -3699,8 +3619,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -3747,8 +3665,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -3795,8 +3711,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -3843,8 +3757,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -3891,8 +3803,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -3939,8 +3849,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -3987,8 +3895,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -4035,8 +3941,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -4083,8 +3987,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -4131,8 +4033,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -4179,8 +4079,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -4227,8 +4125,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -4275,8 +4171,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -4323,8 +4217,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -4371,8 +4263,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -4419,8 +4309,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -4467,8 +4355,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -4515,8 +4401,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -4563,8 +4447,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -4611,8 +4493,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -4633,6 +4513,1158 @@
         <v>0</v>
       </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pisa vs Empoli</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Al Anwar vs Al Ahli</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Al Zulfi vs Al Riyadh</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sassuolo vs Cesena</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Brøndby IF vs Sønderjyske Fodbold</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Brøndby IF</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>4</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BK Häcken vs Halmstads BK</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BK Häcken</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>4</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Sporting Gijón vs CD Sabadell</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>All Boys vs Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>De Graafschap vs Jong AZ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Jong Ajax vs FC Emmen</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FC Emmen</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>4</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht vs Vitesse</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>4</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Al Adalah vs Al Fayha</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Al Fayha</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Al Raed vs Al Hilal</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>4</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Samsunspor vs Goztepe</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Cremonese vs Sampdoria</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deportivo vs Elche</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Deportivo</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Casa Pia vs Benfica</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0-7</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Palermo vs Lecce</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Almería vs Eldense</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lanús vs Independiente</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield vs Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Internacional vs Remo</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Necaxa vs León</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pachuca vs Puebla</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4649,7 +5681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4807,6 +5839,25 @@
       </c>
       <c r="E8" t="n">
         <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4820,7 +5871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5144,6 +6195,132 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>partido_resuelto</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4539,8 +4539,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -4587,8 +4585,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -4635,8 +4631,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -4683,8 +4677,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -4731,8 +4723,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -4779,8 +4769,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -4827,8 +4815,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -4875,8 +4861,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -4923,8 +4907,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>2-5</t>
@@ -4971,8 +4953,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>4-6</t>
@@ -5019,8 +4999,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -5067,8 +5045,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -5115,8 +5091,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -5163,8 +5137,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -5211,8 +5183,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -5259,8 +5229,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -5307,8 +5275,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>0-7</t>
@@ -5355,8 +5321,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -5403,8 +5367,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -5451,8 +5413,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -5499,8 +5459,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -5547,8 +5505,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -5595,8 +5551,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -5643,8 +5597,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -5665,6 +5617,918 @@
         <v>0</v>
       </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua vs Beijing Guoan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Persib vs Bali United</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Persib</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Thailand vs Singapore</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1. FC Heidenheim 1846 vs Bayern Munich</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>3</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Al Okhdood vs Al Khaleej</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Mutilvera vs Peña Sport</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Peña Sport</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Wigan Athletic vs Aston Villa U21</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Wigan Athletic</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Stockport County vs Everton U21</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Stockport County</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>6-3</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>6</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Reading vs Wycombe Wanderers</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Leyton Orient vs AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Northampton Town vs Brighton &amp; Hove Albion U21</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Northampton Town</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Al Diriyah vs Al Nassr</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Barnet vs Arsenal U21</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb vs Viking FK</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>2</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Fenerbahce vs Lyon</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Levski Sofia vs AEK Athens</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Aurora</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra vs Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Guabirá vs Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5681,7 +6545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5858,6 +6722,25 @@
       </c>
       <c r="E9" t="n">
         <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>19</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5871,7 +6754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6321,6 +7204,132 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>partido_resuelto</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -5643,8 +5643,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -5691,8 +5689,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -5739,8 +5735,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -5787,8 +5781,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -5835,8 +5827,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -5883,8 +5873,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -5931,8 +5919,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -5979,8 +5965,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>6-3</t>
@@ -6027,8 +6011,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -6075,8 +6057,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -6123,8 +6103,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -6171,8 +6149,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -6219,8 +6195,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -6267,8 +6241,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -6315,8 +6287,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -6363,8 +6333,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -6411,8 +6379,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -6459,8 +6425,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -6507,8 +6471,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -6545,7 +6507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6703,22 @@
       </c>
       <c r="E10" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -6507,7 +6507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6718,6 +6718,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -6507,7 +6507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6734,6 +6734,22 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6491,6 +6491,1302 @@
         <v>0</v>
       </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Birmingham City vs Bristol City</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Birmingham City</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Southampton vs Stoke City</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>West Ham United vs Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Athletic Club vs Sevilla</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Real Oviedo vs Leganés</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Lens vs AJ Auxerre</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Royal Charleroi SC vs KV Mechelen</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Royal Charleroi SC</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Internazionale vs Monza</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Internazionale</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>AEK Athens vs Iraklis</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Albacete vs Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Al Ahli vs Abha</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Olympiacos vs Atromitos</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Fenerbahce vs Konyaspor</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata vs Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Fluminense vs Remo</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Heerenveen vs PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Universidad Católica (Quito) vs Manta F.C.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Universidad Católica (Quito)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Sporting CP vs Alverca</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ceará vs Londrina</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Independiente vs Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Internacional vs Atlético-MG</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Técnico Universitario vs Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Técnico Universitario</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Guadalajara vs Tijuana</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Inter Miami CF vs Toronto FC</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FC Cincinnati vs Seattle Sounders FC</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs D.C. United</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6507,7 +7803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6751,6 +8047,25 @@
       </c>
       <c r="E13" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>27</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L158"/>
+  <dimension ref="A1:L206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6517,8 +6517,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -6565,8 +6563,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -6613,8 +6609,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -6661,8 +6655,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -6709,8 +6701,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -6757,8 +6747,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -6805,8 +6793,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -6853,8 +6839,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -6901,8 +6885,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -6949,8 +6931,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -6997,8 +6977,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -7045,8 +7023,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -7093,8 +7069,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -7141,8 +7115,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -7189,8 +7161,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -7237,8 +7207,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -7285,8 +7253,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -7333,8 +7299,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -7381,8 +7345,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -7429,8 +7391,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -7477,8 +7437,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -7525,8 +7483,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -7573,8 +7529,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -7621,8 +7575,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -7669,8 +7621,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -7717,8 +7667,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -7765,8 +7713,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -7787,6 +7733,2310 @@
         <v>0</v>
       </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sønderjyske Fodbold vs FC Nordsjælland</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FC Nordsjælland</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SSV Jeddeloh II vs 1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>AGF vs Odense Boldklub</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Randers FC</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs FC Groningen</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Manchester City vs AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Angers vs Lille</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Bahlinger SC 1929 vs 1. FC Magdeburg</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>1. FC Magdeburg</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>FC Carl Zeiss Jena vs SV Darmstadt 98</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SV Darmstadt 98</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Schott vs Borussia Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Borussia Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Westfalia Rhynern vs Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0-6</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Vitória de Guimaraes vs C.D. Nacional</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Vitória de Guimaraes</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>5</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Dynamo Makhachkala vs Krasnodar</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Hammarby IF vs GAIS</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Hammarby IF</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>5</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SC Cambuur vs Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>2</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Atlético Madrid vs Villarreal</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>2</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>La Serena vs Cobresal</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Fortuna Düsseldorf vs SC Freiburg</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SC Freiburg</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>5</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1. FC Phönix Lübeck vs SC Paderborn 07</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SC Paderborn 07</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Frosinone vs Juventus</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>3</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Venezia vs Lecce</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>3</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Club Brugge vs Cercle Brugge KSV</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Pisa vs Padova</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>2</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Hellas Verona vs Ascoli</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>4</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Castellón vs CD Sabadell</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PAOK vs Levadiakos</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Goztepe vs Genclerbirligi</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Atalanta vs Sassuolo</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Torino vs AC Milan</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino vs Grêmio</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Palmeiras vs Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ponte Preta vs Avaí</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF vs Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Palermo vs Juve Stabia</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Elche vs Barcelona</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>FC Porto vs Arouca</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Belgrano (Córdoba) vs Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Belgrano (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Melgar vs Alianza Lima</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Melgar</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Santos vs Mirassol</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Nacional vs Progreso</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Criciúma vs Fortaleza</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>River Plate vs Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Atlanta United FC vs Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Deportivo Cali vs Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Universitario vs Los Chankas</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Atlético Junior vs Once Caldas</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Atlético Junior</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7803,7 +10053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8066,6 +10316,25 @@
       </c>
       <c r="E14" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>48</v>
+      </c>
+      <c r="C15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -8079,7 +10348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8655,6 +10924,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>partido_resuelto</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>18</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7759,8 +7759,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -7807,8 +7805,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -7855,8 +7851,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -7903,8 +7897,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -7951,8 +7943,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -7999,8 +7989,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -8047,8 +8035,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -8095,8 +8081,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -8143,8 +8127,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -8191,8 +8173,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -8239,8 +8219,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -8287,8 +8265,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>0-6</t>
@@ -8335,8 +8311,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -8383,8 +8357,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -8431,8 +8403,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -8479,8 +8449,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
           <t>2-5</t>
@@ -8527,8 +8495,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -8575,8 +8541,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -8623,8 +8587,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>1-5</t>
@@ -8671,8 +8633,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -8719,8 +8679,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -8767,8 +8725,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -8815,8 +8771,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -8863,8 +8817,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -8911,8 +8863,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -8959,8 +8909,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -9007,8 +8955,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -9055,8 +9001,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -9103,8 +9047,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -9151,8 +9093,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -9199,8 +9139,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -9247,8 +9185,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -9295,8 +9231,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -9343,8 +9277,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -9391,8 +9323,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -9439,8 +9369,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -9487,8 +9415,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -9535,8 +9461,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -9583,8 +9507,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -9631,8 +9553,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -9679,8 +9599,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -9727,8 +9645,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -9775,8 +9691,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -9823,8 +9737,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -9871,8 +9783,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -9919,8 +9829,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -9967,8 +9875,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -10015,8 +9921,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -10037,6 +9941,534 @@
         <v>0</v>
       </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Al Taawoun vs Al Fayha</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Al Taawoun</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Arsenal Sarandi vs Ituzaingó</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Arsenal Sarandi</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sportivo Italiano vs Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Sportivo Italiano</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Barnsley vs Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Ipswich Town vs Leicester City</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Alloa Athletic vs Motherwell B</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Alloa Athletic</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Annan Athletic vs Berwick Rangers</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Annan Athletic</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Cove Rangers vs Dundee United B</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Cove Rangers</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt vs NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Excursionistas vs Argentino de Merlo</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Excursionistas</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -10053,7 +10485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10335,6 +10767,25 @@
       </c>
       <c r="E15" t="n">
         <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L217"/>
+  <dimension ref="A1:L246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9967,8 +9967,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10015,8 +10013,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10063,8 +10059,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10111,8 +10105,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10159,8 +10151,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10207,8 +10197,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10255,8 +10243,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10303,8 +10289,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10351,8 +10335,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10399,8 +10381,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10447,8 +10427,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -10469,6 +10447,1398 @@
         <v>0</v>
       </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Jablonec vs Rangers</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Iberia 1999 vs Jagiellonia Bialystok</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SC Freiburg vs Motherwell</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SC Freiburg</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SK Brann vs PAOK</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>F.C. København vs FC Inter Turku</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>F.C. København</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>FC Hradec Králové vs Panathinaikos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Viktoria Plzen vs Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Viktoria Plzen</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Kauno Zalgiris vs Besiktas</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Lillestrom vs Egnatia</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Lillestrom</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia vs Sint-Truidense</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv vs Atalanta</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam vs FC Sion</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>AGF vs Benfica</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CSKA Sofia vs OFI Crete</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Celta Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Austria Vienna vs Braga</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Borac Banja Luka vs Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Borac Banja Luka</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion vs Tromso</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Anderlecht vs Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Ferencvaros vs Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Chelsea vs Luton Town</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Boreham Wood vs Boston United</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Barcelona vs Athletic Club</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Always Ready vs Aurora</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Fulham vs AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata vs Barracas Central</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero vs Guabirá</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Internacional vs Grêmio</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Llaneros FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -10485,7 +11855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10786,6 +12156,22 @@
       </c>
       <c r="E16" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>29</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L246"/>
+  <dimension ref="A1:L295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10473,8 +10473,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10521,8 +10519,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10569,8 +10565,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10617,8 +10611,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10665,8 +10657,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10713,8 +10703,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10761,8 +10749,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10809,8 +10795,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10857,8 +10841,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10905,8 +10887,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -10953,8 +10933,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11001,8 +10979,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11049,8 +11025,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11097,8 +11071,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11145,8 +11117,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11193,8 +11163,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11241,8 +11209,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11289,8 +11255,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11337,8 +11301,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11385,8 +11347,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11433,8 +11393,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11481,8 +11439,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11529,8 +11485,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11577,8 +11531,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11625,8 +11577,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11673,8 +11623,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11721,8 +11669,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11769,8 +11715,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11817,8 +11761,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11839,6 +11781,2358 @@
         <v>0</v>
       </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Al Riyadh vs Neom SC</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Al Fayha vs Abha</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Al Fayha</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>VfL Bochum vs VfL Osnabruck</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>VfL Bochum</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Elche</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>AC Horsens vs Viborg FF</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Viborg FF</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Austria Lustenau vs WSG Swarovski Tirol</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Austria Lustenau</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>FC Groningen vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>FC Groningen</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Stade Laval vs Grenoble</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Stade Laval</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Montpellier vs Boulogne</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Rodez Aveyron vs Pau</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Rodez Aveyron</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>FC Volendam vs FC Dordrecht</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Jong Ajax vs Helmond Sport</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Jong Ajax</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Jong AZ vs MVV Maastricht</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Jong AZ</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>TOP Oss vs Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>TOP Oss</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Roda JC Kerkrade vs NAC Breda</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>NAC Breda</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk vs Jong PSV</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Al Khaleej vs Al Hilal</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Al Nassr vs Al Taawoun</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Bayern Munich vs VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Cremonese vs Modena</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Lille vs Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>AC Milan vs Venezia</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Racing Genk vs Waasland-Beveren</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Racing Genk</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>AFC Fylde vs Forest Green Rovers</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Forest Green Rovers</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Aldershot Town vs Harrogate Town</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Altrincham vs FC Halifax Town</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Barrow vs Yeovil Town</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Gateshead vs Sutton United</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Sutton United</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Hartlepool United vs Eastleigh</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Hartlepool United</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>AFC Hornchurch vs Woking</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>AFC Hornchurch</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Scunthorpe United vs Solihull Moors</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Scunthorpe United</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Southend United vs Kidderminster Harriers</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Southend United</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Tamworth vs Worthing</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Tamworth</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Crystal Palace vs Manchester City</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Wrexham vs Birmingham City</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>0</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño vs Rubio Ñú</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Tenerife vs Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Rio Ave vs Sporting CP</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Alavés vs Villarreal</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos vs FC Cajamarca</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Mushuc Runa vs Delfín</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Sportivo San Lorenzo vs Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Unión (Santa Fe) vs Sarmiento (Junín)</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Unión (Santa Fe)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Montevideo Wanderers vs Central Español Fútbol Club</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Montevideo Wanderers</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>CD Municipal Limeño vs Isidro Metapán</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>CD Municipal Limeño</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Goiás vs São Bernardo</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Náutico vs Athletic</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Novorizontino vs Sport</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -11855,7 +14149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12172,6 +14466,22 @@
       </c>
       <c r="E17" t="n">
         <v>68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>49</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L295"/>
+  <dimension ref="A1:L365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11807,8 +11807,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11855,8 +11853,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11903,8 +11899,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11951,8 +11945,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -11999,8 +11991,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12047,8 +12037,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12095,8 +12083,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12143,8 +12129,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12191,8 +12175,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12239,8 +12221,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12287,8 +12267,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12335,8 +12313,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12383,8 +12359,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12431,8 +12405,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12479,8 +12451,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12527,8 +12497,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12575,8 +12543,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12623,8 +12589,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12671,8 +12635,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12719,8 +12681,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12767,8 +12727,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12815,8 +12773,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12863,8 +12819,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12911,8 +12865,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -12959,8 +12911,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13007,8 +12957,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13055,8 +13003,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13103,8 +13049,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13151,8 +13095,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13199,8 +13141,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13247,8 +13187,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13295,8 +13233,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13343,8 +13279,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13391,8 +13325,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13439,8 +13371,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13487,8 +13417,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13535,8 +13463,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13583,8 +13509,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13631,8 +13555,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13679,8 +13601,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13727,8 +13647,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13775,8 +13693,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13823,8 +13739,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13871,8 +13785,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13919,8 +13831,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -13967,8 +13877,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14015,8 +13923,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14063,8 +13969,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14111,8 +14015,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14133,6 +14035,3366 @@
         <v>0</v>
       </c>
       <c r="L295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Liverpool vs Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Derby County vs Swansea City</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Middlesbrough vs West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Fakel Voronezh vs Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SV ELVERSBERG vs Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>FC Cologne vs TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Mainz vs SC Paderborn 07</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>RB Leipzig vs Borussia Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth vs Everton</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Coventry City vs Hull City</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière vs KV Mechelen</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Bristol City vs Portsmouth</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Charlton Athletic vs Preston North End</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Norwich City vs Burnley</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Southampton vs Millwall</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Watford vs West Ham United</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Celtic vs Falkirk</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>0</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs St Johnstone</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Kilmarnock vs Dundee United</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="n">
+        <v>0</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Progreso vs Danubio</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Excelsior vs Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Arouca vs Maritimo</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Arouca</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Krasnodar vs Rostov</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Levante vs Real Betis</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Strasbourg vs Lens</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Konyaspor vs Kocaelispor</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Konyaspor</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Al Kholood vs Al Ahli</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>KV Kortrijk vs Royal Charleroi SC</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Royal Charleroi SC</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="n">
+        <v>0</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur vs Newcastle United</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="n">
+        <v>0</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund vs Hamburg SV</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="n">
+        <v>0</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Fiorentina vs Frosinone</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Monza vs Udinese</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" t="n">
+        <v>0</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Sassuolo vs Torino</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" t="n">
+        <v>0</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Volos NFC vs Iraklis</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0</v>
+      </c>
+      <c r="K329" t="n">
+        <v>0</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar vs Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" t="n">
+        <v>0</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Real Sociedad vs Espanyol</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Académico de Viseu vs FC Porto</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" t="n">
+        <v>0</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" t="n">
+        <v>0</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Boston River vs Cerro</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
+        <v>0</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Leganés vs Eldense</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" t="n">
+        <v>0</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Independiente del Valle vs Universidad Católica (Quito)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" t="n">
+        <v>0</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Los Chankas vs Juan Pablo II</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Los Chankas</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I337" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" t="n">
+        <v>0</v>
+      </c>
+      <c r="K337" t="n">
+        <v>0</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Al Ettifaq vs Al Diriyah</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Al Diriyah</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" t="n">
+        <v>0</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Al Fateh vs Al Ittihad</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" t="n">
+        <v>0</v>
+      </c>
+      <c r="K339" t="n">
+        <v>0</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Panetolikos vs Kalamata</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" t="n">
+        <v>0</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Galatasaray vs Goztepe</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" t="n">
+        <v>0</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>AJ Auxerre vs Angers</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>AJ Auxerre</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Lorient vs Troyes</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K343" t="n">
+        <v>0</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Lyon vs Le Havre AC</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K344" t="n">
+        <v>0</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Juventus vs Parma</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K345" t="n">
+        <v>0</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>OH Leuven vs Standard Liege</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Standard Liege</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" t="n">
+        <v>0</v>
+      </c>
+      <c r="K346" t="n">
+        <v>0</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>PEC Zwolle vs NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" t="n">
+        <v>0</v>
+      </c>
+      <c r="K347" t="n">
+        <v>0</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense vs 2 de Mayo</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Sevilla vs Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" t="n">
+        <v>0</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Girona vs Las Palmas</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" t="n">
+        <v>0</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" t="n">
+        <v>0</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Seattle Sounders FC vs Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>UTC vs Universitario</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" t="n">
+        <v>0</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba vs América de Cali</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Atlético-MG vs Vitória</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Atlético-MG</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="n">
+        <v>0</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Botafogo-SP vs Cuiabá</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="n">
+        <v>0</v>
+      </c>
+      <c r="K356" t="n">
+        <v>0</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta vs Club Olimpia</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" t="n">
+        <v>0</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Huracán vs Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Huracán</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I358" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" t="n">
+        <v>0</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>São Paulo vs Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I359" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" t="n">
+        <v>0</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Atlas vs Querétaro</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Pachuca vs Guadalajara</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Inter Miami CF vs CF Montréal</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" t="n">
+        <v>0</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>D.C. United vs LAFC</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>LAFC</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="n">
+        <v>0</v>
+      </c>
+      <c r="K363" t="n">
+        <v>0</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Atlanta United FC vs Charlotte FC</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Atlético Junior vs Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Atlético Junior</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" t="n">
+        <v>0</v>
+      </c>
+      <c r="L365" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -14149,7 +17411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14482,6 +17744,22 @@
       </c>
       <c r="E18" t="n">
         <v>88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>70</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L365"/>
+  <dimension ref="A1:L446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14061,8 +14061,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14109,8 +14107,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14157,8 +14153,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14205,8 +14199,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14253,8 +14245,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14301,8 +14291,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14349,8 +14337,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14397,8 +14383,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14445,8 +14429,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14493,8 +14475,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14541,8 +14521,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14589,8 +14567,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14637,8 +14613,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14685,8 +14659,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14733,8 +14705,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14781,8 +14751,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14829,8 +14797,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14877,8 +14843,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14925,8 +14889,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -14973,8 +14935,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15021,8 +14981,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15069,8 +15027,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15117,8 +15073,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15165,8 +15119,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15213,8 +15165,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15261,8 +15211,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15309,8 +15257,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15357,8 +15303,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15405,8 +15349,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15453,8 +15395,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15501,8 +15441,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15549,8 +15487,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15597,8 +15533,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15645,8 +15579,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15693,8 +15625,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15741,8 +15671,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15789,8 +15717,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15837,8 +15763,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15885,8 +15809,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15933,8 +15855,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -15981,8 +15901,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16029,8 +15947,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16077,8 +15993,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16125,8 +16039,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16173,8 +16085,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16221,8 +16131,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16269,8 +16177,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16317,8 +16223,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16365,8 +16269,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16413,8 +16315,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16461,8 +16361,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16509,8 +16407,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16557,8 +16453,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16605,8 +16499,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16653,8 +16545,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16701,8 +16591,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16749,8 +16637,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16797,8 +16683,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16845,8 +16729,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16893,8 +16775,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16941,8 +16821,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -16989,8 +16867,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17037,8 +16913,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17085,8 +16959,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17133,8 +17005,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17181,8 +17051,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17229,8 +17097,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17277,8 +17143,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17325,8 +17189,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17373,8 +17235,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -17395,6 +17255,3894 @@
         <v>0</v>
       </c>
       <c r="L365" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Machico vs Camacha</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Machico</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>FC Utrecht vs PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="n">
+        <v>0</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Rangers</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" t="n">
+        <v>0</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>KAA Gent vs Club Brugge</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" t="n">
+        <v>0</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SV Darmstadt 98 vs Hannover 96</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" t="n">
+        <v>0</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>1. FC Magdeburg vs Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>1. FC Magdeburg</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" t="n">
+        <v>0</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>St. Pauli vs Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam vs ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
+        <v>0</v>
+      </c>
+      <c r="K373" t="n">
+        <v>0</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Willem II vs Heerenveen</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" t="n">
+        <v>0</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Chelsea vs Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="n">
+        <v>0</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Sunderland vs Fulham</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Paris FC vs Nice</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" t="n">
+        <v>0</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SC Freiburg vs Werder Bremen</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>SC Freiburg</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Dundee vs Hibernian</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
+        <v>0</v>
+      </c>
+      <c r="K379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Antwerp vs Sint-Truidense</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Antwerp</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="n">
+        <v>0</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>C.D. Nacional vs Estrela</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>C.D. Nacional</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0</v>
+      </c>
+      <c r="K381" t="n">
+        <v>0</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Spartak Moscow vs Gazovik Orenburg</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Spartak Moscow</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" t="n">
+        <v>0</v>
+      </c>
+      <c r="K382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Telstar vs Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Real Madrid vs Málaga</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" t="n">
+        <v>0</v>
+      </c>
+      <c r="K384" t="n">
+        <v>0</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Stade Rennais vs Le Mans</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Stade Rennais</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" t="n">
+        <v>0</v>
+      </c>
+      <c r="K385" t="n">
+        <v>0</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Manchester United vs Ipswich Town</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+      <c r="J386" t="n">
+        <v>0</v>
+      </c>
+      <c r="K386" t="n">
+        <v>0</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>FC Augsburg vs Schalke 04</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>FC Augsburg</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>0</v>
+      </c>
+      <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Eyupspor vs Alanyaspor</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Alanyaspor</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>FC Caldas vs Sintrense</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>FC Caldas</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" t="n">
+        <v>0</v>
+      </c>
+      <c r="K389" t="n">
+        <v>0</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>CD Cinfães vs Espinho</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>CD Cinfães</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" t="n">
+        <v>0</v>
+      </c>
+      <c r="K390" t="n">
+        <v>0</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Sporting da Covilhã vs Mortágua</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Sporting da Covilhã</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>0</v>
+      </c>
+      <c r="K391" t="n">
+        <v>0</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>AD Fazendense vs CCRD Mocarriense</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>AD Fazendense</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I392" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" t="n">
+        <v>0</v>
+      </c>
+      <c r="K392" t="n">
+        <v>0</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Florgrade vs São João de Ver</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>São João de Ver</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0</v>
+      </c>
+      <c r="K393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Lusitano Évora 1911 vs Os Belenenses</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Os Belenenses</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0</v>
+      </c>
+      <c r="K394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Nazarenos vs Vitoria Sernache</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Vitoria Sernache</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0</v>
+      </c>
+      <c r="K395" t="n">
+        <v>0</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Sanjoanense vs CD de Pacos de Brandao</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Sanjoanense</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>0</v>
+      </c>
+      <c r="K396" t="n">
+        <v>0</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Union St.-Gilloise vs Anderlecht</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Union St.-Gilloise</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0</v>
+      </c>
+      <c r="K397" t="n">
+        <v>0</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Aris vs OFI Crete</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>0</v>
+      </c>
+      <c r="K398" t="n">
+        <v>0</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Casa Pia vs Moreirense</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J399" t="n">
+        <v>0</v>
+      </c>
+      <c r="K399" t="n">
+        <v>0</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Rubin Kazan vs Dynamo Makhachkala</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I400" t="n">
+        <v>2</v>
+      </c>
+      <c r="J400" t="n">
+        <v>0</v>
+      </c>
+      <c r="K400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Mallorca vs Ceuta</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J401" t="n">
+        <v>0</v>
+      </c>
+      <c r="K401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>KVC Westerlo vs Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J402" t="n">
+        <v>0</v>
+      </c>
+      <c r="K402" t="n">
+        <v>0</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Atromitos vs PAOK</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>0</v>
+      </c>
+      <c r="J403" t="n">
+        <v>0</v>
+      </c>
+      <c r="K403" t="n">
+        <v>0</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Banfield vs River Plate</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>2</v>
+      </c>
+      <c r="J404" t="n">
+        <v>0</v>
+      </c>
+      <c r="K404" t="n">
+        <v>0</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Asteras Tripoli vs Olympiacos</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>2</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Kifisia vs AEK Athens</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>2</v>
+      </c>
+      <c r="J406" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SC Cambuur vs FC Twente</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>1</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" t="n">
+        <v>0</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Aucas vs Libertad (Ecuador)</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>2</v>
+      </c>
+      <c r="J408" t="n">
+        <v>0</v>
+      </c>
+      <c r="K408" t="n">
+        <v>0</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Al Qadsiah vs Al-Faisaly</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Al Qadsiah</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>1</v>
+      </c>
+      <c r="J409" t="n">
+        <v>0</v>
+      </c>
+      <c r="K409" t="n">
+        <v>0</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir vs Kasimpasa</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>3</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Samsunspor vs Fenerbahce</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>1</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0</v>
+      </c>
+      <c r="K411" t="n">
+        <v>0</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>AS Monaco vs Marseille</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>AS Monaco</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>1</v>
+      </c>
+      <c r="J412" t="n">
+        <v>0</v>
+      </c>
+      <c r="K412" t="n">
+        <v>0</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Cagliari vs Internazionale</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Internazionale</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>0</v>
+      </c>
+      <c r="K413" t="n">
+        <v>0</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Lazio vs Genoa</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>0</v>
+      </c>
+      <c r="K414" t="n">
+        <v>0</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Corinthians vs Santos</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0</v>
+      </c>
+      <c r="K415" t="n">
+        <v>0</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Flamengo vs Botafogo</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" t="n">
+        <v>0</v>
+      </c>
+      <c r="K416" t="n">
+        <v>0</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>América Mineiro vs Ponte Preta</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>3</v>
+      </c>
+      <c r="J417" t="n">
+        <v>0</v>
+      </c>
+      <c r="K417" t="n">
+        <v>0</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Universidad de Concepción vs Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>5</v>
+      </c>
+      <c r="J418" t="n">
+        <v>0</v>
+      </c>
+      <c r="K418" t="n">
+        <v>0</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Águilas Doradas vs Boyacá Chicó FC</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>4</v>
+      </c>
+      <c r="J419" t="n">
+        <v>0</v>
+      </c>
+      <c r="K419" t="n">
+        <v>0</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Cerro Porteño vs Libertad</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>3</v>
+      </c>
+      <c r="J420" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Avaí vs Atlético Goianiense</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>2</v>
+      </c>
+      <c r="J421" t="n">
+        <v>0</v>
+      </c>
+      <c r="K421" t="n">
+        <v>0</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Celta Vigo vs Athletic Club</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>1</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0</v>
+      </c>
+      <c r="K422" t="n">
+        <v>0</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>FC Famalicao vs Gil Vicente</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>FC Famalicao</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>1</v>
+      </c>
+      <c r="J423" t="n">
+        <v>0</v>
+      </c>
+      <c r="K423" t="n">
+        <v>0</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Córdoba vs Granada</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>1</v>
+      </c>
+      <c r="J424" t="n">
+        <v>0</v>
+      </c>
+      <c r="K424" t="n">
+        <v>0</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Aldosivi</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>7</v>
+      </c>
+      <c r="J425" t="n">
+        <v>0</v>
+      </c>
+      <c r="K425" t="n">
+        <v>0</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Columbus Crew vs New England Revolution</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>2</v>
+      </c>
+      <c r="J426" t="n">
+        <v>0</v>
+      </c>
+      <c r="K426" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Orense vs Macará</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Orense</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>0</v>
+      </c>
+      <c r="J427" t="n">
+        <v>0</v>
+      </c>
+      <c r="K427" t="n">
+        <v>0</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Sport Boys vs Sporting Cristal</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Sport Boys</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>3</v>
+      </c>
+      <c r="J428" t="n">
+        <v>0</v>
+      </c>
+      <c r="K428" t="n">
+        <v>0</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>CRB vs Criciúma</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>4</v>
+      </c>
+      <c r="J429" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Independiente Medellín vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>0</v>
+      </c>
+      <c r="J430" t="n">
+        <v>0</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Grêmio vs Chapecoense</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>5</v>
+      </c>
+      <c r="J431" t="n">
+        <v>0</v>
+      </c>
+      <c r="K431" t="n">
+        <v>0</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Mirassol vs Palmeiras</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>0</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0</v>
+      </c>
+      <c r="K432" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Vila Nova vs Ceará</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>1</v>
+      </c>
+      <c r="J433" t="n">
+        <v>0</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Colo Colo vs Audax Italiano</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" t="n">
+        <v>0</v>
+      </c>
+      <c r="K434" t="n">
+        <v>0</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Guaraní vs Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Guaraní</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>1</v>
+      </c>
+      <c r="J435" t="n">
+        <v>0</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Cerro Largo vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0</v>
+      </c>
+      <c r="K436" t="n">
+        <v>0</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Independiente vs Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>0</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Bahia vs Internacional</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" t="n">
+        <v>0</v>
+      </c>
+      <c r="K438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>St. Louis CITY SC vs FC Dallas</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Emelec vs Leones</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Millonarios vs Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>1</v>
+      </c>
+      <c r="J441" t="n">
+        <v>0</v>
+      </c>
+      <c r="K441" t="n">
+        <v>0</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Toluca vs FC Juarez</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" t="n">
+        <v>0</v>
+      </c>
+      <c r="K442" t="n">
+        <v>0</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido vs Huachipato</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" t="n">
+        <v>0</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Cienciano del Cusco vs Cusco FC</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Cienciano del Cusco</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" t="n">
+        <v>0</v>
+      </c>
+      <c r="K444" t="n">
+        <v>0</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia vs Racing Club</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0</v>
+      </c>
+      <c r="K445" t="n">
+        <v>0</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Deportivo Cali vs Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -17411,7 +21159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17760,6 +21508,25 @@
       </c>
       <c r="E19" t="n">
         <v>109</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>81</v>
+      </c>
+      <c r="C20" t="n">
+        <v>57</v>
+      </c>
+      <c r="D20" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -17773,7 +21540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18517,6 +22284,195 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>21</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L446"/>
+  <dimension ref="A1:L490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17281,8 +17281,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -17329,8 +17327,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr">
         <is>
           <t>1-6</t>
@@ -17377,8 +17373,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -17425,8 +17419,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -17473,8 +17465,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -17521,8 +17511,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -17569,8 +17557,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -17617,8 +17603,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -17665,8 +17649,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -17713,8 +17695,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -17761,8 +17741,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -17809,8 +17787,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -17857,8 +17833,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -17905,8 +17879,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -17953,8 +17925,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -18001,8 +17971,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -18049,8 +18017,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -18097,8 +18063,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -18145,8 +18109,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -18193,8 +18155,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -18241,8 +18201,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -18289,8 +18247,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -18337,8 +18293,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -18385,8 +18339,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -18433,8 +18385,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -18481,8 +18431,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -18529,8 +18477,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -18577,8 +18523,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -18625,8 +18569,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -18673,8 +18615,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -18721,8 +18661,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -18769,8 +18707,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -18817,8 +18753,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -18865,8 +18799,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -18913,8 +18845,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -18961,8 +18891,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -19009,8 +18937,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -19057,8 +18983,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -19105,8 +19029,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -19153,8 +19075,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -19201,8 +19121,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -19249,8 +19167,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -19297,8 +19213,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -19345,8 +19259,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -19393,8 +19305,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -19441,8 +19351,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -19489,8 +19397,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -19537,8 +19443,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -19585,8 +19489,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -19633,8 +19535,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -19681,8 +19581,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -19729,8 +19627,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -19777,8 +19673,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -19825,8 +19719,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -19873,8 +19765,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -19921,8 +19811,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -19969,8 +19857,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -20017,8 +19903,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -20065,8 +19949,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -20113,8 +19995,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -20161,8 +20041,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -20209,8 +20087,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -20257,8 +20133,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -20305,8 +20179,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -20353,8 +20225,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -20401,8 +20271,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -20449,8 +20317,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -20497,8 +20363,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -20545,8 +20409,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -20593,8 +20455,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -20641,8 +20501,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -20689,8 +20547,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -20737,8 +20593,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -20785,8 +20639,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -20833,8 +20685,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -20881,8 +20731,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -20929,8 +20777,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -20977,8 +20823,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -21025,8 +20869,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -21073,8 +20915,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -21121,8 +20961,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -21143,6 +20981,2118 @@
         <v>0</v>
       </c>
       <c r="L446" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Persib vs Manila Digger</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Persib</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Boston United vs AFC Hornchurch</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Boston United</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="n">
+        <v>0</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Carlisle United vs Scunthorpe United</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Carlisle United</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="n">
+        <v>0</v>
+      </c>
+      <c r="K449" t="n">
+        <v>0</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Eastleigh vs Aldershot Town</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Eastleigh</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="n">
+        <v>0</v>
+      </c>
+      <c r="K450" t="n">
+        <v>0</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Forest Green Rovers vs Altrincham</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Forest Green Rovers</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J451" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" t="n">
+        <v>0</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Harrogate Town vs Gateshead</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>0</v>
+      </c>
+      <c r="J452" t="n">
+        <v>0</v>
+      </c>
+      <c r="K452" t="n">
+        <v>0</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Kidderminster Harriers vs Barrow</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>0</v>
+      </c>
+      <c r="J453" t="n">
+        <v>0</v>
+      </c>
+      <c r="K453" t="n">
+        <v>0</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Solihull Moors vs AFC Fylde</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Solihull Moors</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" t="n">
+        <v>0</v>
+      </c>
+      <c r="K454" t="n">
+        <v>0</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Sutton United vs Wealdstone</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Sutton United</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>0</v>
+      </c>
+      <c r="J455" t="n">
+        <v>0</v>
+      </c>
+      <c r="K455" t="n">
+        <v>0</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Woking vs Southend United</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Southend United</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>0</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" t="n">
+        <v>0</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Worthing vs Boreham Wood</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>0</v>
+      </c>
+      <c r="J457" t="n">
+        <v>0</v>
+      </c>
+      <c r="K457" t="n">
+        <v>0</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Lecce vs AS Roma</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" t="n">
+        <v>0</v>
+      </c>
+      <c r="K458" t="n">
+        <v>0</v>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Levadiakos vs Panathinaikos</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>0</v>
+      </c>
+      <c r="K459" t="n">
+        <v>0</v>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>F.C. København vs Sønderjyske Fodbold</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>F.C. København</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>0</v>
+      </c>
+      <c r="J460" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" t="n">
+        <v>0</v>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Djurgården vs Mjällby AIF</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>0</v>
+      </c>
+      <c r="J461" t="n">
+        <v>0</v>
+      </c>
+      <c r="K461" t="n">
+        <v>0</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>GAIS vs IF Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>0</v>
+      </c>
+      <c r="J462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" t="n">
+        <v>0</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>IK Sirius vs Malmö FF</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>IK Sirius</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>0</v>
+      </c>
+      <c r="J463" t="n">
+        <v>0</v>
+      </c>
+      <c r="K463" t="n">
+        <v>0</v>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Burgos vs Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>0</v>
+      </c>
+      <c r="J464" t="n">
+        <v>0</v>
+      </c>
+      <c r="K464" t="n">
+        <v>0</v>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Osasuna vs Getafe</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>0</v>
+      </c>
+      <c r="J465" t="n">
+        <v>0</v>
+      </c>
+      <c r="K465" t="n">
+        <v>0</v>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Jong AZ vs Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Jong AZ</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>0</v>
+      </c>
+      <c r="J466" t="n">
+        <v>0</v>
+      </c>
+      <c r="K466" t="n">
+        <v>0</v>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Jong PSV vs Jong Ajax</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Jong PSV</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>0</v>
+      </c>
+      <c r="J467" t="n">
+        <v>0</v>
+      </c>
+      <c r="K467" t="n">
+        <v>0</v>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Amed SFK vs Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>0</v>
+      </c>
+      <c r="J468" t="n">
+        <v>0</v>
+      </c>
+      <c r="K468" t="n">
+        <v>0</v>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Besiktas vs Çorum FK</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>0</v>
+      </c>
+      <c r="J469" t="n">
+        <v>0</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo) vs Albion FC</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J470" t="n">
+        <v>0</v>
+      </c>
+      <c r="K470" t="n">
+        <v>0</v>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Atalanta vs Bologna</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" t="n">
+        <v>0</v>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Dijon FCO vs Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+      <c r="J472" t="n">
+        <v>0</v>
+      </c>
+      <c r="K472" t="n">
+        <v>0</v>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Aston Villa vs Arsenal</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+      <c r="J473" t="n">
+        <v>0</v>
+      </c>
+      <c r="K473" t="n">
+        <v>0</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Guabirá</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" t="n">
+        <v>0</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Benfica vs Estoril</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>0</v>
+      </c>
+      <c r="J475" t="n">
+        <v>0</v>
+      </c>
+      <c r="K475" t="n">
+        <v>0</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Braga vs Vitória de Guimaraes</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" t="n">
+        <v>0</v>
+      </c>
+      <c r="K476" t="n">
+        <v>0</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Barcelona vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I477" t="n">
+        <v>0</v>
+      </c>
+      <c r="J477" t="n">
+        <v>0</v>
+      </c>
+      <c r="K477" t="n">
+        <v>0</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia vs Platense</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I478" t="n">
+        <v>2</v>
+      </c>
+      <c r="J478" t="n">
+        <v>0</v>
+      </c>
+      <c r="K478" t="n">
+        <v>0</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata vs Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I479" t="n">
+        <v>3</v>
+      </c>
+      <c r="J479" t="n">
+        <v>0</v>
+      </c>
+      <c r="K479" t="n">
+        <v>0</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Comunicaciones vs Deportivo Merlo</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Comunicaciones</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I480" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" t="n">
+        <v>0</v>
+      </c>
+      <c r="K480" t="n">
+        <v>0</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Los Andes vs Acassuso</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I481" t="n">
+        <v>1</v>
+      </c>
+      <c r="J481" t="n">
+        <v>0</v>
+      </c>
+      <c r="K481" t="n">
+        <v>0</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Unión La Calera vs La Serena</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>3</v>
+      </c>
+      <c r="J482" t="n">
+        <v>0</v>
+      </c>
+      <c r="K482" t="n">
+        <v>0</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>UCV FC vs Rayo Zuliano</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>UCV FC</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>0</v>
+      </c>
+      <c r="J483" t="n">
+        <v>0</v>
+      </c>
+      <c r="K483" t="n">
+        <v>0</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Fortaleza vs Operário PR</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>4</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0</v>
+      </c>
+      <c r="K484" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Remo vs Coritiba</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I485" t="n">
+        <v>3</v>
+      </c>
+      <c r="J485" t="n">
+        <v>0</v>
+      </c>
+      <c r="K485" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto vs Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I486" t="n">
+        <v>8</v>
+      </c>
+      <c r="J486" t="n">
+        <v>0</v>
+      </c>
+      <c r="K486" t="n">
+        <v>0</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Academia Puerto Cabello vs Anzoátegui FC</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Academia Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="n">
+        <v>0</v>
+      </c>
+      <c r="K487" t="n">
+        <v>0</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Instituto (Córdoba) vs San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Instituto (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I488" t="n">
+        <v>3</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Tigre vs Barracas Central</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I489" t="n">
+        <v>2</v>
+      </c>
+      <c r="J489" t="n">
+        <v>0</v>
+      </c>
+      <c r="K489" t="n">
+        <v>0</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Deportes Tolima vs Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I490" t="n">
+        <v>3</v>
+      </c>
+      <c r="J490" t="n">
+        <v>0</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -21159,7 +23109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21527,6 +23477,25 @@
       </c>
       <c r="E20" t="n">
         <v>81</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>44</v>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>75</v>
+      </c>
+      <c r="E21" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -21540,7 +23509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22473,6 +24442,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L490"/>
+  <dimension ref="A1:L527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21007,8 +21007,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -21055,8 +21053,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -21103,8 +21099,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -21151,8 +21145,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -21199,8 +21191,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -21247,8 +21237,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -21295,8 +21283,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -21343,8 +21329,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -21391,8 +21375,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -21439,8 +21421,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -21487,8 +21467,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -21535,8 +21513,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -21583,8 +21559,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
       <c r="G459" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -21631,8 +21605,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -21679,8 +21651,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -21727,8 +21697,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -21775,8 +21743,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
       <c r="G463" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -21823,8 +21789,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -21871,8 +21835,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -21919,8 +21881,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -21967,8 +21927,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -22015,8 +21973,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -22063,8 +22019,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
           <t>6-2</t>
@@ -22111,8 +22065,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -22159,8 +22111,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -22207,8 +22157,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -22255,8 +22203,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -22303,8 +22249,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -22351,8 +22295,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -22399,8 +22341,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -22447,8 +22387,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -22495,8 +22433,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -22543,8 +22479,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -22591,8 +22525,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -22639,8 +22571,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -22687,8 +22617,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -22735,8 +22663,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -22783,8 +22709,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -22831,8 +22755,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -22879,8 +22801,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -22927,8 +22847,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
       <c r="G487" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -22975,8 +22893,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -23023,8 +22939,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -23071,8 +22985,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -23093,6 +23005,1782 @@
         <v>0</v>
       </c>
       <c r="L490" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Parma vs Cremonese</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I491" t="n">
+        <v>0</v>
+      </c>
+      <c r="J491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" t="n">
+        <v>0</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Wolfsberger vs LASK Linz</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I492" t="n">
+        <v>3</v>
+      </c>
+      <c r="J492" t="n">
+        <v>0</v>
+      </c>
+      <c r="K492" t="n">
+        <v>0</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Kruger United vs Orlando Pirates</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Orlando Pirates</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>0</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Al Hilal vs Al Ahli</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I494" t="n">
+        <v>2</v>
+      </c>
+      <c r="J494" t="n">
+        <v>0</v>
+      </c>
+      <c r="K494" t="n">
+        <v>0</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Achilles Veen vs SV Poortugaal</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Achilles Veen</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I495" t="n">
+        <v>0</v>
+      </c>
+      <c r="J495" t="n">
+        <v>0</v>
+      </c>
+      <c r="K495" t="n">
+        <v>0</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>ADO '20 vs Excelsior Maassluis</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>ADO '20</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I496" t="n">
+        <v>0</v>
+      </c>
+      <c r="J496" t="n">
+        <v>0</v>
+      </c>
+      <c r="K496" t="n">
+        <v>0</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>SC Genemuiden vs FC Lisse</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>SC Genemuiden</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I497" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Harkemase Boys vs Excelsior '31</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Harkemase Boys</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I498" t="n">
+        <v>0</v>
+      </c>
+      <c r="J498" t="n">
+        <v>0</v>
+      </c>
+      <c r="K498" t="n">
+        <v>0</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Sportlust '46 vs SV Blauw Geel '38</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Sportlust '46</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" t="n">
+        <v>0</v>
+      </c>
+      <c r="K499" t="n">
+        <v>0</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Lincoln City vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Lincoln City</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>1</v>
+      </c>
+      <c r="J500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K500" t="n">
+        <v>0</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Derby County</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I501" t="n">
+        <v>4</v>
+      </c>
+      <c r="J501" t="n">
+        <v>0</v>
+      </c>
+      <c r="K501" t="n">
+        <v>0</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Preston North End vs Bristol City</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" t="n">
+        <v>0</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Sheffield United vs Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>5</v>
+      </c>
+      <c r="J503" t="n">
+        <v>0</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Swansea City vs Watford</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>1</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>West Ham United vs Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I505" t="n">
+        <v>1</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Bradford City vs Cambridge United</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Bradford City</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I506" t="n">
+        <v>5</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0</v>
+      </c>
+      <c r="K506" t="n">
+        <v>0</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Doncaster Rovers vs Notts County</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Doncaster Rovers</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0</v>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Huddersfield Town vs Oxford United</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Huddersfield Town</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I508" t="n">
+        <v>3</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0</v>
+      </c>
+      <c r="K508" t="n">
+        <v>0</v>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Leicester City vs Plymouth Argyle</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I509" t="n">
+        <v>3</v>
+      </c>
+      <c r="J509" t="n">
+        <v>0</v>
+      </c>
+      <c r="K509" t="n">
+        <v>0</v>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Accrington Stanley vs Grimsby Town</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I510" t="n">
+        <v>4</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Bristol Rovers vs Colchester United</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I511" t="n">
+        <v>3</v>
+      </c>
+      <c r="J511" t="n">
+        <v>0</v>
+      </c>
+      <c r="K511" t="n">
+        <v>0</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Cheltenham Town vs York City</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>York City</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>1</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0</v>
+      </c>
+      <c r="K512" t="n">
+        <v>0</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Chesterfield vs Gillingham</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I513" t="n">
+        <v>6</v>
+      </c>
+      <c r="J513" t="n">
+        <v>0</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra vs Walsall</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I514" t="n">
+        <v>3</v>
+      </c>
+      <c r="J514" t="n">
+        <v>0</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Exeter City vs Barnet</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I515" t="n">
+        <v>3</v>
+      </c>
+      <c r="J515" t="n">
+        <v>0</v>
+      </c>
+      <c r="K515" t="n">
+        <v>0</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Fleetwood Town vs Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I516" t="n">
+        <v>1</v>
+      </c>
+      <c r="J516" t="n">
+        <v>0</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Northampton Town vs Crawley Town</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Northampton Town</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I517" t="n">
+        <v>4</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Rochdale vs Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Rochdale</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I518" t="n">
+        <v>4</v>
+      </c>
+      <c r="J518" t="n">
+        <v>0</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Salford City vs Newport County</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I519" t="n">
+        <v>7</v>
+      </c>
+      <c r="J519" t="n">
+        <v>0</v>
+      </c>
+      <c r="K519" t="n">
+        <v>0</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>HEBC Hamburg vs Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I520" t="n">
+        <v>5</v>
+      </c>
+      <c r="J520" t="n">
+        <v>0</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Stranraer vs Celtic B</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Stranraer</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I521" t="n">
+        <v>2</v>
+      </c>
+      <c r="J521" t="n">
+        <v>0</v>
+      </c>
+      <c r="K521" t="n">
+        <v>0</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Stoke City vs Norwich City</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I522" t="n">
+        <v>1</v>
+      </c>
+      <c r="J522" t="n">
+        <v>0</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Torino vs Monza</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Rubio Ñú vs Sportivo San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Rubio Ñú</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I524" t="n">
+        <v>4</v>
+      </c>
+      <c r="J524" t="n">
+        <v>0</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Delfín vs Técnico Universitario</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Delfín</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I525" t="n">
+        <v>4</v>
+      </c>
+      <c r="J525" t="n">
+        <v>0</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2 de Mayo vs Sportivo Luqueño</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2 de Mayo</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I526" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Atlético-MG vs Cruzeiro</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Atlético-MG</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>0</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -23109,7 +24797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23496,6 +25184,25 @@
       </c>
       <c r="E21" t="n">
         <v>44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>37</v>
+      </c>
+      <c r="C22" t="n">
+        <v>27</v>
+      </c>
+      <c r="D22" t="n">
+        <v>73</v>
+      </c>
+      <c r="E22" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -23509,7 +25216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24610,6 +26317,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>24</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>12</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L527"/>
+  <dimension ref="A1:L577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23031,8 +23031,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
       <c r="G491" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -23079,8 +23077,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -23127,8 +23123,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -23175,8 +23169,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -23223,8 +23215,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
       <c r="G495" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -23271,8 +23261,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -23319,8 +23307,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
       <c r="G497" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -23367,8 +23353,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
       <c r="G498" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -23415,8 +23399,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
       <c r="G499" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -23463,8 +23445,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -23511,8 +23491,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -23559,8 +23537,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -23607,8 +23583,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
       <c r="G503" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -23655,8 +23629,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
       <c r="G504" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -23703,8 +23675,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -23751,8 +23721,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -23799,8 +23767,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
       <c r="G507" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -23847,8 +23813,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -23895,8 +23859,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
       <c r="G509" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -23943,8 +23905,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
       <c r="G510" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -23991,8 +23951,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
       <c r="G511" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -24039,8 +23997,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
       <c r="G512" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -24087,8 +24043,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
       <c r="G513" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -24135,8 +24089,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
       <c r="G514" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -24183,8 +24135,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E515" t="inlineStr"/>
-      <c r="F515" t="inlineStr"/>
       <c r="G515" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -24231,8 +24181,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -24279,8 +24227,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
       <c r="G517" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -24327,8 +24273,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
       <c r="G518" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -24375,8 +24319,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E519" t="inlineStr"/>
-      <c r="F519" t="inlineStr"/>
       <c r="G519" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -24423,8 +24365,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -24471,8 +24411,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
       <c r="G521" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -24519,8 +24457,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
       <c r="G522" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -24567,8 +24503,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
       <c r="G523" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -24615,8 +24549,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr"/>
       <c r="G524" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -24663,8 +24595,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E525" t="inlineStr"/>
-      <c r="F525" t="inlineStr"/>
       <c r="G525" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -24711,8 +24641,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E526" t="inlineStr"/>
-      <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -24759,8 +24687,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E527" t="inlineStr"/>
-      <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -24781,6 +24707,2406 @@
         <v>0</v>
       </c>
       <c r="L527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka vs Urawa Red Diamonds</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" t="n">
+        <v>0</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka vs Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I529" t="n">
+        <v>0</v>
+      </c>
+      <c r="J529" t="n">
+        <v>0</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Machida Zelvia vs Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Mito Hollyhock vs Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I531" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" t="n">
+        <v>0</v>
+      </c>
+      <c r="K531" t="n">
+        <v>0</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima vs Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" t="n">
+        <v>0</v>
+      </c>
+      <c r="K532" t="n">
+        <v>0</v>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse vs FC Tokyo</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>FC Tokyo</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J533" t="n">
+        <v>0</v>
+      </c>
+      <c r="K533" t="n">
+        <v>0</v>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy 1969 vs Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J534" t="n">
+        <v>0</v>
+      </c>
+      <c r="K534" t="n">
+        <v>0</v>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>V-Varen Nagasaki vs Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" t="n">
+        <v>0</v>
+      </c>
+      <c r="K535" t="n">
+        <v>0</v>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos vs Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" t="n">
+        <v>0</v>
+      </c>
+      <c r="K536" t="n">
+        <v>0</v>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Sassuolo vs Frosinone</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" t="n">
+        <v>0</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0</v>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Udinese vs Venezia</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I538" t="n">
+        <v>0</v>
+      </c>
+      <c r="J538" t="n">
+        <v>0</v>
+      </c>
+      <c r="K538" t="n">
+        <v>0</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Austria Vienna vs WSG Swarovski Tirol</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Austria Vienna</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I539" t="n">
+        <v>0</v>
+      </c>
+      <c r="J539" t="n">
+        <v>0</v>
+      </c>
+      <c r="K539" t="n">
+        <v>0</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns vs Milford FC</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I540" t="n">
+        <v>0</v>
+      </c>
+      <c r="J540" t="n">
+        <v>0</v>
+      </c>
+      <c r="K540" t="n">
+        <v>0</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>AGF vs FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="n">
+        <v>0</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>VV Staphorst vs UNA</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>VV Staphorst</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I542" t="n">
+        <v>0</v>
+      </c>
+      <c r="J542" t="n">
+        <v>0</v>
+      </c>
+      <c r="K542" t="n">
+        <v>0</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>USV Hercules vs EVV Echt</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>USV Hercules</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I543" t="n">
+        <v>0</v>
+      </c>
+      <c r="J543" t="n">
+        <v>0</v>
+      </c>
+      <c r="K543" t="n">
+        <v>0</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Sint-Truidense vs Union St.-Gilloise</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Union St.-Gilloise</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr"/>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I544" t="n">
+        <v>1</v>
+      </c>
+      <c r="J544" t="n">
+        <v>0</v>
+      </c>
+      <c r="K544" t="n">
+        <v>0</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Millwall vs Wrexham</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I545" t="n">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>0</v>
+      </c>
+      <c r="K545" t="n">
+        <v>0</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers vs Cardiff City</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I546" t="n">
+        <v>0</v>
+      </c>
+      <c r="J546" t="n">
+        <v>0</v>
+      </c>
+      <c r="K546" t="n">
+        <v>0</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion vs Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I547" t="n">
+        <v>2</v>
+      </c>
+      <c r="J547" t="n">
+        <v>0</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0</v>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Barnsley vs Blackpool</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr"/>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I548" t="n">
+        <v>3</v>
+      </c>
+      <c r="J548" t="n">
+        <v>0</v>
+      </c>
+      <c r="K548" t="n">
+        <v>0</v>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Burton Albion vs AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Burton Albion</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I549" t="n">
+        <v>4</v>
+      </c>
+      <c r="J549" t="n">
+        <v>0</v>
+      </c>
+      <c r="K549" t="n">
+        <v>0</v>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Luton Town vs Stockport County</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Luton Town</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr"/>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I550" t="n">
+        <v>1</v>
+      </c>
+      <c r="J550" t="n">
+        <v>0</v>
+      </c>
+      <c r="K550" t="n">
+        <v>0</v>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Wigan Athletic vs Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Wigan Athletic</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr"/>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I551" t="n">
+        <v>2</v>
+      </c>
+      <c r="J551" t="n">
+        <v>0</v>
+      </c>
+      <c r="K551" t="n">
+        <v>0</v>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Celtic vs Aberdeen</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr"/>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I552" t="n">
+        <v>2</v>
+      </c>
+      <c r="J552" t="n">
+        <v>0</v>
+      </c>
+      <c r="K552" t="n">
+        <v>0</v>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Motherwell vs Dundee United</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I553" t="n">
+        <v>6</v>
+      </c>
+      <c r="J553" t="n">
+        <v>0</v>
+      </c>
+      <c r="K553" t="n">
+        <v>0</v>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>VfL Osnabruck vs Bayern Munich</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr"/>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I554" t="n">
+        <v>1</v>
+      </c>
+      <c r="J554" t="n">
+        <v>0</v>
+      </c>
+      <c r="K554" t="n">
+        <v>0</v>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Kilmarnock vs St Mirren</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>St Mirren</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr"/>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I555" t="n">
+        <v>2</v>
+      </c>
+      <c r="J555" t="n">
+        <v>0</v>
+      </c>
+      <c r="K555" t="n">
+        <v>0</v>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Reading vs Mansfield Town</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr"/>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I556" t="n">
+        <v>2</v>
+      </c>
+      <c r="J556" t="n">
+        <v>0</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0</v>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Falkirk vs Rangers</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr"/>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I557" t="n">
+        <v>3</v>
+      </c>
+      <c r="J557" t="n">
+        <v>0</v>
+      </c>
+      <c r="K557" t="n">
+        <v>0</v>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Macará vs Manta F.C.</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr"/>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I558" t="n">
+        <v>5</v>
+      </c>
+      <c r="J558" t="n">
+        <v>0</v>
+      </c>
+      <c r="K558" t="n">
+        <v>0</v>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Nacional Asunción vs Libertad</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr"/>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I559" t="n">
+        <v>2</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Burnley vs Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr"/>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I560" t="n">
+        <v>1</v>
+      </c>
+      <c r="J560" t="n">
+        <v>0</v>
+      </c>
+      <c r="K560" t="n">
+        <v>0</v>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca vs Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr"/>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I561" t="n">
+        <v>5</v>
+      </c>
+      <c r="J561" t="n">
+        <v>0</v>
+      </c>
+      <c r="K561" t="n">
+        <v>0</v>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Club Olimpia vs Guaraní</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr"/>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I562" t="n">
+        <v>3</v>
+      </c>
+      <c r="J562" t="n">
+        <v>0</v>
+      </c>
+      <c r="K562" t="n">
+        <v>0</v>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido vs Universidad de Concepción</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr"/>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I563" t="n">
+        <v>3</v>
+      </c>
+      <c r="J563" t="n">
+        <v>0</v>
+      </c>
+      <c r="K563" t="n">
+        <v>0</v>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Flamengo vs Mirassol</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr"/>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I564" t="n">
+        <v>2</v>
+      </c>
+      <c r="J564" t="n">
+        <v>0</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Colegiales vs Midland</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr"/>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I565" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" t="n">
+        <v>0</v>
+      </c>
+      <c r="K565" t="n">
+        <v>0</v>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Charleston Battery vs Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr"/>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I566" t="n">
+        <v>1</v>
+      </c>
+      <c r="J566" t="n">
+        <v>0</v>
+      </c>
+      <c r="K566" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Westchester SC vs Chattanooga Red Wolves</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Westchester SC</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr"/>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I567" t="n">
+        <v>1</v>
+      </c>
+      <c r="J567" t="n">
+        <v>0</v>
+      </c>
+      <c r="K567" t="n">
+        <v>0</v>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Charlotte Independence vs Portland Hearts of Pine</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr"/>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I568" t="n">
+        <v>0</v>
+      </c>
+      <c r="J568" t="n">
+        <v>0</v>
+      </c>
+      <c r="K568" t="n">
+        <v>0</v>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Fort Wayne vs Richmond Kickers</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr"/>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I569" t="n">
+        <v>1</v>
+      </c>
+      <c r="J569" t="n">
+        <v>0</v>
+      </c>
+      <c r="K569" t="n">
+        <v>0</v>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Barcelona SC vs Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr"/>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I570" t="n">
+        <v>0</v>
+      </c>
+      <c r="J570" t="n">
+        <v>0</v>
+      </c>
+      <c r="K570" t="n">
+        <v>0</v>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Forward Madison FC vs One Knoxville</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr"/>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I571" t="n">
+        <v>0</v>
+      </c>
+      <c r="J571" t="n">
+        <v>0</v>
+      </c>
+      <c r="K571" t="n">
+        <v>0</v>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield vs Boca Juniors</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr"/>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I572" t="n">
+        <v>0</v>
+      </c>
+      <c r="J572" t="n">
+        <v>0</v>
+      </c>
+      <c r="K572" t="n">
+        <v>0</v>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Santos vs Palmeiras</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr"/>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I573" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" t="n">
+        <v>0</v>
+      </c>
+      <c r="K573" t="n">
+        <v>0</v>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Vitória vs Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I574" t="n">
+        <v>0</v>
+      </c>
+      <c r="J574" t="n">
+        <v>0</v>
+      </c>
+      <c r="K574" t="n">
+        <v>0</v>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Deportes Limache vs Ñublense</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr"/>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I575" t="n">
+        <v>0</v>
+      </c>
+      <c r="J575" t="n">
+        <v>0</v>
+      </c>
+      <c r="K575" t="n">
+        <v>0</v>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Toluca vs León</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr"/>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I576" t="n">
+        <v>0</v>
+      </c>
+      <c r="J576" t="n">
+        <v>0</v>
+      </c>
+      <c r="K576" t="n">
+        <v>0</v>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>América vs Monterrey</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr"/>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" t="n">
+        <v>0</v>
+      </c>
+      <c r="K577" t="n">
+        <v>0</v>
+      </c>
+      <c r="L577" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -24797,7 +27123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25203,6 +27529,25 @@
       </c>
       <c r="E22" t="n">
         <v>37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" t="n">
+        <v>39</v>
+      </c>
+      <c r="D23" t="n">
+        <v>78</v>
+      </c>
+      <c r="E23" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -25216,7 +27561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26527,6 +28872,195 @@
         <v>50</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>18</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>15</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L577"/>
+  <dimension ref="A1:L598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24733,8 +24733,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr"/>
-      <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -24781,8 +24779,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E529" t="inlineStr"/>
-      <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -24829,8 +24825,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -24877,8 +24871,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -24925,8 +24917,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E532" t="inlineStr"/>
-      <c r="F532" t="inlineStr"/>
       <c r="G532" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -24973,8 +24963,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E533" t="inlineStr"/>
-      <c r="F533" t="inlineStr"/>
       <c r="G533" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -25021,8 +25009,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -25069,8 +25055,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E535" t="inlineStr"/>
-      <c r="F535" t="inlineStr"/>
       <c r="G535" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -25117,8 +25101,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -25165,8 +25147,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
       <c r="G537" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -25213,8 +25193,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -25261,8 +25239,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -25309,8 +25285,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -25357,8 +25331,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
       <c r="G541" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -25405,8 +25377,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -25453,8 +25423,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -25501,8 +25469,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -25549,8 +25515,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -25597,8 +25561,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E546" t="inlineStr"/>
-      <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -25645,8 +25607,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E547" t="inlineStr"/>
-      <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -25693,8 +25653,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -25741,8 +25699,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E549" t="inlineStr"/>
-      <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -25789,8 +25745,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -25837,8 +25791,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -25885,8 +25837,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -25933,8 +25883,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr"/>
       <c r="G553" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -25981,8 +25929,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr"/>
       <c r="G554" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -26029,8 +25975,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E555" t="inlineStr"/>
-      <c r="F555" t="inlineStr"/>
       <c r="G555" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -26077,8 +26021,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E556" t="inlineStr"/>
-      <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -26125,8 +26067,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
       <c r="G557" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -26173,8 +26113,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E558" t="inlineStr"/>
-      <c r="F558" t="inlineStr"/>
       <c r="G558" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -26221,8 +26159,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E559" t="inlineStr"/>
-      <c r="F559" t="inlineStr"/>
       <c r="G559" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -26269,8 +26205,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E560" t="inlineStr"/>
-      <c r="F560" t="inlineStr"/>
       <c r="G560" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -26317,8 +26251,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E561" t="inlineStr"/>
-      <c r="F561" t="inlineStr"/>
       <c r="G561" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -26365,8 +26297,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E562" t="inlineStr"/>
-      <c r="F562" t="inlineStr"/>
       <c r="G562" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -26413,8 +26343,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -26461,8 +26389,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E564" t="inlineStr"/>
-      <c r="F564" t="inlineStr"/>
       <c r="G564" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -26509,8 +26435,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E565" t="inlineStr"/>
-      <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -26557,8 +26481,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -26605,8 +26527,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E567" t="inlineStr"/>
-      <c r="F567" t="inlineStr"/>
       <c r="G567" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -26653,8 +26573,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
       <c r="G568" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -26701,8 +26619,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr"/>
-      <c r="F569" t="inlineStr"/>
       <c r="G569" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -26749,8 +26665,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E570" t="inlineStr"/>
-      <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -26797,8 +26711,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E571" t="inlineStr"/>
-      <c r="F571" t="inlineStr"/>
       <c r="G571" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -26845,8 +26757,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
       <c r="G572" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -26893,8 +26803,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
       <c r="G573" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -26941,8 +26849,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E574" t="inlineStr"/>
-      <c r="F574" t="inlineStr"/>
       <c r="G574" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -26989,8 +26895,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
       <c r="G575" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -27037,8 +26941,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
       <c r="G576" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -27085,8 +26987,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
       <c r="G577" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -27107,6 +27007,1014 @@
         <v>0</v>
       </c>
       <c r="L577" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Al Fayha vs Al Kholood</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr"/>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" t="n">
+        <v>0</v>
+      </c>
+      <c r="K578" t="n">
+        <v>0</v>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Palermo vs Mantova</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr"/>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J579" t="n">
+        <v>0</v>
+      </c>
+      <c r="K579" t="n">
+        <v>0</v>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Neom SC vs Al Khaleej</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr"/>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I580" t="n">
+        <v>0</v>
+      </c>
+      <c r="J580" t="n">
+        <v>0</v>
+      </c>
+      <c r="K580" t="n">
+        <v>0</v>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Mjällby AIF vs Djurgården</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" t="n">
+        <v>0</v>
+      </c>
+      <c r="K581" t="n">
+        <v>0</v>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>F.C. København vs FC Nordsjælland</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>F.C. København</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr"/>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I582" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" t="n">
+        <v>0</v>
+      </c>
+      <c r="K582" t="n">
+        <v>0</v>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Al Diriyah vs Al Qadsiah</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Al Qadsiah</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr"/>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I583" t="n">
+        <v>0</v>
+      </c>
+      <c r="J583" t="n">
+        <v>0</v>
+      </c>
+      <c r="K583" t="n">
+        <v>0</v>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>KAA Gent vs OH Leuven</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr"/>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" t="n">
+        <v>0</v>
+      </c>
+      <c r="K584" t="n">
+        <v>0</v>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Anderlecht vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr"/>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" t="n">
+        <v>0</v>
+      </c>
+      <c r="K585" t="n">
+        <v>0</v>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Toulouse vs Lille</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr"/>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>1</v>
+      </c>
+      <c r="J586" t="n">
+        <v>0</v>
+      </c>
+      <c r="K586" t="n">
+        <v>0</v>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Real Sociedad vs Celta Vigo</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr"/>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>2</v>
+      </c>
+      <c r="J587" t="n">
+        <v>0</v>
+      </c>
+      <c r="K587" t="n">
+        <v>0</v>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Universidad Católica (Quito) vs Aucas</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Universidad Católica (Quito)</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr"/>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J588" t="n">
+        <v>0</v>
+      </c>
+      <c r="K588" t="n">
+        <v>0</v>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Cagliari vs Hellas Verona</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr"/>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I589" t="n">
+        <v>1</v>
+      </c>
+      <c r="J589" t="n">
+        <v>0</v>
+      </c>
+      <c r="K589" t="n">
+        <v>0</v>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>América de Cali vs Alianza FC</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr"/>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I590" t="n">
+        <v>2</v>
+      </c>
+      <c r="J590" t="n">
+        <v>0</v>
+      </c>
+      <c r="K590" t="n">
+        <v>0</v>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Leones vs Orense</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Leones</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr"/>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I591" t="n">
+        <v>0</v>
+      </c>
+      <c r="J591" t="n">
+        <v>0</v>
+      </c>
+      <c r="K591" t="n">
+        <v>0</v>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta vs Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr"/>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I592" t="n">
+        <v>0</v>
+      </c>
+      <c r="J592" t="n">
+        <v>0</v>
+      </c>
+      <c r="K592" t="n">
+        <v>0</v>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Grêmio vs Internacional</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I593" t="n">
+        <v>1</v>
+      </c>
+      <c r="J593" t="n">
+        <v>0</v>
+      </c>
+      <c r="K593" t="n">
+        <v>0</v>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Náutico vs Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr"/>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I594" t="n">
+        <v>0</v>
+      </c>
+      <c r="J594" t="n">
+        <v>0</v>
+      </c>
+      <c r="K594" t="n">
+        <v>0</v>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Nacional Potosí vs Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I595" t="n">
+        <v>0</v>
+      </c>
+      <c r="J595" t="n">
+        <v>0</v>
+      </c>
+      <c r="K595" t="n">
+        <v>0</v>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Libertad (Ecuador) vs Emelec</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Libertad (Ecuador)</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I596" t="n">
+        <v>0</v>
+      </c>
+      <c r="J596" t="n">
+        <v>0</v>
+      </c>
+      <c r="K596" t="n">
+        <v>0</v>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr"/>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I597" t="n">
+        <v>0</v>
+      </c>
+      <c r="J597" t="n">
+        <v>0</v>
+      </c>
+      <c r="K597" t="n">
+        <v>0</v>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Tepatitlán FC vs Dorados de Sinaloa</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Tepatitlán FC</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I598" t="n">
+        <v>0</v>
+      </c>
+      <c r="J598" t="n">
+        <v>0</v>
+      </c>
+      <c r="K598" t="n">
+        <v>0</v>
+      </c>
+      <c r="L598" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -27123,7 +28031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27548,6 +28456,25 @@
       </c>
       <c r="E23" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -27561,7 +28488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29061,6 +29988,111 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L598"/>
+  <dimension ref="A1:L647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27033,8 +27033,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E578" t="inlineStr"/>
-      <c r="F578" t="inlineStr"/>
       <c r="G578" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -27081,8 +27079,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E579" t="inlineStr"/>
-      <c r="F579" t="inlineStr"/>
       <c r="G579" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -27129,8 +27125,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
       <c r="G580" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -27177,8 +27171,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
       <c r="G581" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -27225,8 +27217,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E582" t="inlineStr"/>
-      <c r="F582" t="inlineStr"/>
       <c r="G582" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -27273,8 +27263,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E583" t="inlineStr"/>
-      <c r="F583" t="inlineStr"/>
       <c r="G583" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -27321,8 +27309,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E584" t="inlineStr"/>
-      <c r="F584" t="inlineStr"/>
       <c r="G584" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -27369,8 +27355,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E585" t="inlineStr"/>
-      <c r="F585" t="inlineStr"/>
       <c r="G585" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -27417,8 +27401,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E586" t="inlineStr"/>
-      <c r="F586" t="inlineStr"/>
       <c r="G586" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -27465,8 +27447,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E587" t="inlineStr"/>
-      <c r="F587" t="inlineStr"/>
       <c r="G587" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -27513,8 +27493,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E588" t="inlineStr"/>
-      <c r="F588" t="inlineStr"/>
       <c r="G588" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -27561,8 +27539,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E589" t="inlineStr"/>
-      <c r="F589" t="inlineStr"/>
       <c r="G589" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -27609,8 +27585,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E590" t="inlineStr"/>
-      <c r="F590" t="inlineStr"/>
       <c r="G590" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -27657,8 +27631,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E591" t="inlineStr"/>
-      <c r="F591" t="inlineStr"/>
       <c r="G591" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -27705,8 +27677,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E592" t="inlineStr"/>
-      <c r="F592" t="inlineStr"/>
       <c r="G592" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -27753,8 +27723,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E593" t="inlineStr"/>
-      <c r="F593" t="inlineStr"/>
       <c r="G593" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -27801,8 +27769,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E594" t="inlineStr"/>
-      <c r="F594" t="inlineStr"/>
       <c r="G594" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -27849,8 +27815,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E595" t="inlineStr"/>
-      <c r="F595" t="inlineStr"/>
       <c r="G595" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -27897,8 +27861,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E596" t="inlineStr"/>
-      <c r="F596" t="inlineStr"/>
       <c r="G596" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -27945,8 +27907,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E597" t="inlineStr"/>
-      <c r="F597" t="inlineStr"/>
       <c r="G597" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -27993,8 +27953,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E598" t="inlineStr"/>
-      <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -28015,6 +27973,2358 @@
         <v>0</v>
       </c>
       <c r="L598" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Panthere FC vs Rayon Sport</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Panthere FC</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr"/>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I599" t="n">
+        <v>0</v>
+      </c>
+      <c r="J599" t="n">
+        <v>0</v>
+      </c>
+      <c r="K599" t="n">
+        <v>0</v>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Abha vs Al Ettifaq</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Al Ettifaq</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr"/>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I600" t="n">
+        <v>0</v>
+      </c>
+      <c r="J600" t="n">
+        <v>0</v>
+      </c>
+      <c r="K600" t="n">
+        <v>0</v>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld vs St. Pauli</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr"/>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I601" t="n">
+        <v>0</v>
+      </c>
+      <c r="J601" t="n">
+        <v>0</v>
+      </c>
+      <c r="K601" t="n">
+        <v>0</v>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Hannover 96 vs Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr"/>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I602" t="n">
+        <v>0</v>
+      </c>
+      <c r="J602" t="n">
+        <v>0</v>
+      </c>
+      <c r="K602" t="n">
+        <v>0</v>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Lyon vs AJ Auxerre</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I603" t="n">
+        <v>0</v>
+      </c>
+      <c r="J603" t="n">
+        <v>0</v>
+      </c>
+      <c r="K603" t="n">
+        <v>0</v>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Viborg FF vs Lyngby Boldklub</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Viborg FF</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr"/>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I604" t="n">
+        <v>0</v>
+      </c>
+      <c r="J604" t="n">
+        <v>0</v>
+      </c>
+      <c r="K604" t="n">
+        <v>0</v>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Aalesund vs IK Start</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Aalesund</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I605" t="n">
+        <v>0</v>
+      </c>
+      <c r="J605" t="n">
+        <v>0</v>
+      </c>
+      <c r="K605" t="n">
+        <v>0</v>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Fredrikstad vs Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr"/>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I606" t="n">
+        <v>0</v>
+      </c>
+      <c r="J606" t="n">
+        <v>0</v>
+      </c>
+      <c r="K606" t="n">
+        <v>0</v>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir vs Galatasaray</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr"/>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I607" t="n">
+        <v>1</v>
+      </c>
+      <c r="J607" t="n">
+        <v>0</v>
+      </c>
+      <c r="K607" t="n">
+        <v>0</v>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Marumo Gallants vs Polokwane City FC</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Marumo Gallants</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr"/>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I608" t="n">
+        <v>0</v>
+      </c>
+      <c r="J608" t="n">
+        <v>0</v>
+      </c>
+      <c r="K608" t="n">
+        <v>0</v>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam vs PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I609" t="n">
+        <v>3</v>
+      </c>
+      <c r="J609" t="n">
+        <v>0</v>
+      </c>
+      <c r="K609" t="n">
+        <v>0</v>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>JS Saoura vs Horoya</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr"/>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I610" t="n">
+        <v>0</v>
+      </c>
+      <c r="J610" t="n">
+        <v>0</v>
+      </c>
+      <c r="K610" t="n">
+        <v>0</v>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Dunkerque vs Clermont Foot</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr"/>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I611" t="n">
+        <v>0</v>
+      </c>
+      <c r="J611" t="n">
+        <v>0</v>
+      </c>
+      <c r="K611" t="n">
+        <v>0</v>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Grenoble vs Annecy</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr"/>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I612" t="n">
+        <v>0</v>
+      </c>
+      <c r="J612" t="n">
+        <v>0</v>
+      </c>
+      <c r="K612" t="n">
+        <v>0</v>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Stade Laval vs Red Star FC 93</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Red Star FC 93</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr"/>
+      <c r="F613" t="inlineStr"/>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I613" t="n">
+        <v>1</v>
+      </c>
+      <c r="J613" t="n">
+        <v>0</v>
+      </c>
+      <c r="K613" t="n">
+        <v>0</v>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Pau vs Sochaux</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr"/>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I614" t="n">
+        <v>1</v>
+      </c>
+      <c r="J614" t="n">
+        <v>0</v>
+      </c>
+      <c r="K614" t="n">
+        <v>0</v>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Almere City vs Jong Ajax</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr"/>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I615" t="n">
+        <v>0</v>
+      </c>
+      <c r="J615" t="n">
+        <v>0</v>
+      </c>
+      <c r="K615" t="n">
+        <v>0</v>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>FC Emmen vs FC Volendam</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>FC Emmen</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr"/>
+      <c r="F616" t="inlineStr"/>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>5-3</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I616" t="n">
+        <v>0</v>
+      </c>
+      <c r="J616" t="n">
+        <v>0</v>
+      </c>
+      <c r="K616" t="n">
+        <v>0</v>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Heracles Almelo vs De Graafschap</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Heracles Almelo</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr"/>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I617" t="n">
+        <v>0</v>
+      </c>
+      <c r="J617" t="n">
+        <v>0</v>
+      </c>
+      <c r="K617" t="n">
+        <v>0</v>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Vitesse vs TOP Oss</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr"/>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I618" t="n">
+        <v>0</v>
+      </c>
+      <c r="J618" t="n">
+        <v>0</v>
+      </c>
+      <c r="K618" t="n">
+        <v>0</v>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk vs NAC Breda</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>NAC Breda</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr"/>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I619" t="n">
+        <v>1</v>
+      </c>
+      <c r="J619" t="n">
+        <v>0</v>
+      </c>
+      <c r="K619" t="n">
+        <v>0</v>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>FC Cajamarca vs Cienciano del Cusco</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Cienciano del Cusco</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr"/>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I620" t="n">
+        <v>0</v>
+      </c>
+      <c r="J620" t="n">
+        <v>0</v>
+      </c>
+      <c r="K620" t="n">
+        <v>0</v>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Al Ahli vs Al Riyadh</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr"/>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I621" t="n">
+        <v>0</v>
+      </c>
+      <c r="J621" t="n">
+        <v>0</v>
+      </c>
+      <c r="K621" t="n">
+        <v>0</v>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Al Shabab vs Al Hilal</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr"/>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I622" t="n">
+        <v>0</v>
+      </c>
+      <c r="J622" t="n">
+        <v>0</v>
+      </c>
+      <c r="K622" t="n">
+        <v>0</v>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart vs FC Cologne</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr"/>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I623" t="n">
+        <v>2</v>
+      </c>
+      <c r="J623" t="n">
+        <v>0</v>
+      </c>
+      <c r="K623" t="n">
+        <v>0</v>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Livingston vs Stenhousemuir</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Livingston</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr"/>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I624" t="n">
+        <v>0</v>
+      </c>
+      <c r="J624" t="n">
+        <v>0</v>
+      </c>
+      <c r="K624" t="n">
+        <v>0</v>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano vs Racing (Córdoba)</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr"/>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I625" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" t="n">
+        <v>0</v>
+      </c>
+      <c r="K625" t="n">
+        <v>0</v>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Las Palmas vs Leganés</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr"/>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I626" t="n">
+        <v>0</v>
+      </c>
+      <c r="J626" t="n">
+        <v>0</v>
+      </c>
+      <c r="K626" t="n">
+        <v>0</v>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Genoa vs Como</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr"/>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I627" t="n">
+        <v>3</v>
+      </c>
+      <c r="J627" t="n">
+        <v>0</v>
+      </c>
+      <c r="K627" t="n">
+        <v>0</v>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Altrincham vs Eastleigh</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr"/>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I628" t="n">
+        <v>0</v>
+      </c>
+      <c r="J628" t="n">
+        <v>0</v>
+      </c>
+      <c r="K628" t="n">
+        <v>0</v>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Flackwell Heath vs Hanwell Town FC</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Hanwell Town FC</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr"/>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I629" t="n">
+        <v>0</v>
+      </c>
+      <c r="J629" t="n">
+        <v>0</v>
+      </c>
+      <c r="K629" t="n">
+        <v>0</v>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Three Bridges vs Kingstonian</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Three Bridges</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr"/>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I630" t="n">
+        <v>0</v>
+      </c>
+      <c r="J630" t="n">
+        <v>0</v>
+      </c>
+      <c r="K630" t="n">
+        <v>0</v>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Ossett United vs Pontefract Collieries</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Ossett United</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr"/>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I631" t="n">
+        <v>0</v>
+      </c>
+      <c r="J631" t="n">
+        <v>0</v>
+      </c>
+      <c r="K631" t="n">
+        <v>0</v>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Ipswich Town vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr"/>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I632" t="n">
+        <v>0</v>
+      </c>
+      <c r="J632" t="n">
+        <v>0</v>
+      </c>
+      <c r="K632" t="n">
+        <v>0</v>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Real Betis vs Real Madrid</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr"/>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I633" t="n">
+        <v>5</v>
+      </c>
+      <c r="J633" t="n">
+        <v>0</v>
+      </c>
+      <c r="K633" t="n">
+        <v>0</v>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Sandefjord vs Viking FK</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Viking FK</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr"/>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I634" t="n">
+        <v>1</v>
+      </c>
+      <c r="J634" t="n">
+        <v>0</v>
+      </c>
+      <c r="K634" t="n">
+        <v>0</v>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Real Oruro vs San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr"/>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I635" t="n">
+        <v>0</v>
+      </c>
+      <c r="J635" t="n">
+        <v>0</v>
+      </c>
+      <c r="K635" t="n">
+        <v>0</v>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain vs AS Monaco</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I636" t="n">
+        <v>7</v>
+      </c>
+      <c r="J636" t="n">
+        <v>0</v>
+      </c>
+      <c r="K636" t="n">
+        <v>0</v>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>FC Porto vs Moreirense</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I637" t="n">
+        <v>6</v>
+      </c>
+      <c r="J637" t="n">
+        <v>0</v>
+      </c>
+      <c r="K637" t="n">
+        <v>0</v>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Alianza Atlético vs UTC</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Alianza Atlético</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I638" t="n">
+        <v>0</v>
+      </c>
+      <c r="J638" t="n">
+        <v>0</v>
+      </c>
+      <c r="K638" t="n">
+        <v>0</v>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>ABB vs Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I639" t="n">
+        <v>0</v>
+      </c>
+      <c r="J639" t="n">
+        <v>0</v>
+      </c>
+      <c r="K639" t="n">
+        <v>0</v>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Belgrano (Córdoba) vs Huracán</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Belgrano (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I640" t="n">
+        <v>3</v>
+      </c>
+      <c r="J640" t="n">
+        <v>0</v>
+      </c>
+      <c r="K640" t="n">
+        <v>0</v>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Platense vs Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Platense</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I641" t="n">
+        <v>0</v>
+      </c>
+      <c r="J641" t="n">
+        <v>0</v>
+      </c>
+      <c r="K641" t="n">
+        <v>0</v>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Criciúma vs Cuiabá</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I642" t="n">
+        <v>1</v>
+      </c>
+      <c r="J642" t="n">
+        <v>0</v>
+      </c>
+      <c r="K642" t="n">
+        <v>0</v>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Loudoun United FC vs Colorado Springs Switchbacks FC</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Colorado Springs Switchbacks FC</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I643" t="n">
+        <v>0</v>
+      </c>
+      <c r="J643" t="n">
+        <v>0</v>
+      </c>
+      <c r="K643" t="n">
+        <v>0</v>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>CRB vs América Mineiro</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr"/>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I644" t="n">
+        <v>0</v>
+      </c>
+      <c r="J644" t="n">
+        <v>0</v>
+      </c>
+      <c r="K644" t="n">
+        <v>0</v>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion vs Audax Italiano</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I645" t="n">
+        <v>0</v>
+      </c>
+      <c r="J645" t="n">
+        <v>0</v>
+      </c>
+      <c r="K645" t="n">
+        <v>0</v>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Antigua GFC vs Aurora FC</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Antigua GFC</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr"/>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I646" t="n">
+        <v>0</v>
+      </c>
+      <c r="J646" t="n">
+        <v>0</v>
+      </c>
+      <c r="K646" t="n">
+        <v>0</v>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>FC Juarez vs Pachuca</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr"/>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I647" t="n">
+        <v>0</v>
+      </c>
+      <c r="J647" t="n">
+        <v>0</v>
+      </c>
+      <c r="K647" t="n">
+        <v>0</v>
+      </c>
+      <c r="L647" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -28031,7 +30341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28475,6 +30785,25 @@
       </c>
       <c r="E24" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>49</v>
+      </c>
+      <c r="C25" t="n">
+        <v>37</v>
+      </c>
+      <c r="D25" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -28488,7 +30817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30093,6 +32422,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>10</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L647"/>
+  <dimension ref="A1:L753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27999,8 +27999,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E599" t="inlineStr"/>
-      <c r="F599" t="inlineStr"/>
       <c r="G599" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -28047,8 +28045,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E600" t="inlineStr"/>
-      <c r="F600" t="inlineStr"/>
       <c r="G600" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -28095,8 +28091,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E601" t="inlineStr"/>
-      <c r="F601" t="inlineStr"/>
       <c r="G601" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -28143,8 +28137,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E602" t="inlineStr"/>
-      <c r="F602" t="inlineStr"/>
       <c r="G602" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -28191,8 +28183,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E603" t="inlineStr"/>
-      <c r="F603" t="inlineStr"/>
       <c r="G603" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -28239,8 +28229,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E604" t="inlineStr"/>
-      <c r="F604" t="inlineStr"/>
       <c r="G604" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -28287,8 +28275,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E605" t="inlineStr"/>
-      <c r="F605" t="inlineStr"/>
       <c r="G605" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -28335,8 +28321,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E606" t="inlineStr"/>
-      <c r="F606" t="inlineStr"/>
       <c r="G606" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -28383,8 +28367,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E607" t="inlineStr"/>
-      <c r="F607" t="inlineStr"/>
       <c r="G607" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -28431,8 +28413,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E608" t="inlineStr"/>
-      <c r="F608" t="inlineStr"/>
       <c r="G608" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -28479,8 +28459,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E609" t="inlineStr"/>
-      <c r="F609" t="inlineStr"/>
       <c r="G609" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -28527,8 +28505,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E610" t="inlineStr"/>
-      <c r="F610" t="inlineStr"/>
       <c r="G610" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -28575,8 +28551,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E611" t="inlineStr"/>
-      <c r="F611" t="inlineStr"/>
       <c r="G611" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -28623,8 +28597,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E612" t="inlineStr"/>
-      <c r="F612" t="inlineStr"/>
       <c r="G612" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -28671,8 +28643,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E613" t="inlineStr"/>
-      <c r="F613" t="inlineStr"/>
       <c r="G613" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -28719,8 +28689,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E614" t="inlineStr"/>
-      <c r="F614" t="inlineStr"/>
       <c r="G614" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -28767,8 +28735,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr"/>
-      <c r="F615" t="inlineStr"/>
       <c r="G615" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -28815,8 +28781,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E616" t="inlineStr"/>
-      <c r="F616" t="inlineStr"/>
       <c r="G616" t="inlineStr">
         <is>
           <t>5-3</t>
@@ -28863,8 +28827,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E617" t="inlineStr"/>
-      <c r="F617" t="inlineStr"/>
       <c r="G617" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -28911,8 +28873,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E618" t="inlineStr"/>
-      <c r="F618" t="inlineStr"/>
       <c r="G618" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -28959,8 +28919,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E619" t="inlineStr"/>
-      <c r="F619" t="inlineStr"/>
       <c r="G619" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -29007,8 +28965,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E620" t="inlineStr"/>
-      <c r="F620" t="inlineStr"/>
       <c r="G620" t="inlineStr">
         <is>
           <t>2-5</t>
@@ -29055,8 +29011,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E621" t="inlineStr"/>
-      <c r="F621" t="inlineStr"/>
       <c r="G621" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -29103,8 +29057,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E622" t="inlineStr"/>
-      <c r="F622" t="inlineStr"/>
       <c r="G622" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -29151,8 +29103,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E623" t="inlineStr"/>
-      <c r="F623" t="inlineStr"/>
       <c r="G623" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -29199,8 +29149,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E624" t="inlineStr"/>
-      <c r="F624" t="inlineStr"/>
       <c r="G624" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -29247,8 +29195,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E625" t="inlineStr"/>
-      <c r="F625" t="inlineStr"/>
       <c r="G625" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -29295,8 +29241,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E626" t="inlineStr"/>
-      <c r="F626" t="inlineStr"/>
       <c r="G626" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -29343,8 +29287,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E627" t="inlineStr"/>
-      <c r="F627" t="inlineStr"/>
       <c r="G627" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -29391,8 +29333,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E628" t="inlineStr"/>
-      <c r="F628" t="inlineStr"/>
       <c r="G628" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -29439,8 +29379,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E629" t="inlineStr"/>
-      <c r="F629" t="inlineStr"/>
       <c r="G629" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -29487,8 +29425,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E630" t="inlineStr"/>
-      <c r="F630" t="inlineStr"/>
       <c r="G630" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -29535,8 +29471,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E631" t="inlineStr"/>
-      <c r="F631" t="inlineStr"/>
       <c r="G631" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -29583,8 +29517,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr"/>
-      <c r="F632" t="inlineStr"/>
       <c r="G632" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -29631,8 +29563,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E633" t="inlineStr"/>
-      <c r="F633" t="inlineStr"/>
       <c r="G633" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -29679,8 +29609,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E634" t="inlineStr"/>
-      <c r="F634" t="inlineStr"/>
       <c r="G634" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -29727,8 +29655,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E635" t="inlineStr"/>
-      <c r="F635" t="inlineStr"/>
       <c r="G635" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -29775,8 +29701,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E636" t="inlineStr"/>
-      <c r="F636" t="inlineStr"/>
       <c r="G636" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -29823,8 +29747,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr"/>
-      <c r="F637" t="inlineStr"/>
       <c r="G637" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -29871,8 +29793,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr"/>
-      <c r="F638" t="inlineStr"/>
       <c r="G638" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -29919,8 +29839,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E639" t="inlineStr"/>
-      <c r="F639" t="inlineStr"/>
       <c r="G639" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -29967,8 +29885,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E640" t="inlineStr"/>
-      <c r="F640" t="inlineStr"/>
       <c r="G640" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -30015,8 +29931,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr"/>
-      <c r="F641" t="inlineStr"/>
       <c r="G641" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -30063,8 +29977,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E642" t="inlineStr"/>
-      <c r="F642" t="inlineStr"/>
       <c r="G642" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -30111,8 +30023,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E643" t="inlineStr"/>
-      <c r="F643" t="inlineStr"/>
       <c r="G643" t="inlineStr">
         <is>
           <t>4-5</t>
@@ -30159,8 +30069,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E644" t="inlineStr"/>
-      <c r="F644" t="inlineStr"/>
       <c r="G644" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -30207,8 +30115,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E645" t="inlineStr"/>
-      <c r="F645" t="inlineStr"/>
       <c r="G645" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -30255,8 +30161,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E646" t="inlineStr"/>
-      <c r="F646" t="inlineStr"/>
       <c r="G646" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -30303,8 +30207,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E647" t="inlineStr"/>
-      <c r="F647" t="inlineStr"/>
       <c r="G647" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -30325,6 +30227,5094 @@
         <v>0</v>
       </c>
       <c r="L647" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov vs Krasnodar</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr"/>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I648" t="n">
+        <v>0</v>
+      </c>
+      <c r="J648" t="n">
+        <v>0</v>
+      </c>
+      <c r="K648" t="n">
+        <v>0</v>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Newcastle United vs AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr"/>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I649" t="n">
+        <v>0</v>
+      </c>
+      <c r="J649" t="n">
+        <v>0</v>
+      </c>
+      <c r="K649" t="n">
+        <v>0</v>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Lincoln City vs Southampton</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr"/>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I650" t="n">
+        <v>0</v>
+      </c>
+      <c r="J650" t="n">
+        <v>0</v>
+      </c>
+      <c r="K650" t="n">
+        <v>0</v>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Preston North End vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I651" t="n">
+        <v>0</v>
+      </c>
+      <c r="J651" t="n">
+        <v>0</v>
+      </c>
+      <c r="K651" t="n">
+        <v>0</v>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Stoke City vs Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I652" t="n">
+        <v>0</v>
+      </c>
+      <c r="J652" t="n">
+        <v>0</v>
+      </c>
+      <c r="K652" t="n">
+        <v>0</v>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Fiorentina vs Torino</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I653" t="n">
+        <v>0</v>
+      </c>
+      <c r="J653" t="n">
+        <v>0</v>
+      </c>
+      <c r="K653" t="n">
+        <v>0</v>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>TSG Hoffenheim vs Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I654" t="n">
+        <v>0</v>
+      </c>
+      <c r="J654" t="n">
+        <v>0</v>
+      </c>
+      <c r="K654" t="n">
+        <v>0</v>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen vs 1. FC Union Berlin</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I655" t="n">
+        <v>0</v>
+      </c>
+      <c r="J655" t="n">
+        <v>0</v>
+      </c>
+      <c r="K655" t="n">
+        <v>0</v>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Borussia Mönchengladbach vs SV Elversberg</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Borussia Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I656" t="n">
+        <v>0</v>
+      </c>
+      <c r="J656" t="n">
+        <v>0</v>
+      </c>
+      <c r="K656" t="n">
+        <v>0</v>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Werder Bremen vs RB Leipzig</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I657" t="n">
+        <v>0</v>
+      </c>
+      <c r="J657" t="n">
+        <v>0</v>
+      </c>
+      <c r="K657" t="n">
+        <v>0</v>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>SC Paderborn 07 vs SC Freiburg</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>SC Freiburg</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I658" t="n">
+        <v>0</v>
+      </c>
+      <c r="J658" t="n">
+        <v>0</v>
+      </c>
+      <c r="K658" t="n">
+        <v>0</v>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Zenit St Petersburg vs CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I659" t="n">
+        <v>0</v>
+      </c>
+      <c r="J659" t="n">
+        <v>0</v>
+      </c>
+      <c r="K659" t="n">
+        <v>0</v>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Brentford vs Sunderland</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr"/>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I660" t="n">
+        <v>0</v>
+      </c>
+      <c r="J660" t="n">
+        <v>0</v>
+      </c>
+      <c r="K660" t="n">
+        <v>0</v>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion vs Leeds United</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I661" t="n">
+        <v>0</v>
+      </c>
+      <c r="J661" t="n">
+        <v>0</v>
+      </c>
+      <c r="K661" t="n">
+        <v>0</v>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Fulham vs Crystal Palace</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I662" t="n">
+        <v>0</v>
+      </c>
+      <c r="J662" t="n">
+        <v>0</v>
+      </c>
+      <c r="K662" t="n">
+        <v>0</v>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Manchester City vs Coventry City</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I663" t="n">
+        <v>0</v>
+      </c>
+      <c r="J663" t="n">
+        <v>0</v>
+      </c>
+      <c r="K663" t="n">
+        <v>0</v>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I664" t="n">
+        <v>0</v>
+      </c>
+      <c r="J664" t="n">
+        <v>0</v>
+      </c>
+      <c r="K664" t="n">
+        <v>0</v>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Royal Charleroi SC vs Union St.-Gilloise</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Union St.-Gilloise</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I665" t="n">
+        <v>0</v>
+      </c>
+      <c r="J665" t="n">
+        <v>0</v>
+      </c>
+      <c r="K665" t="n">
+        <v>0</v>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Burnley vs Bristol City</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I666" t="n">
+        <v>0</v>
+      </c>
+      <c r="J666" t="n">
+        <v>0</v>
+      </c>
+      <c r="K666" t="n">
+        <v>0</v>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Millwall vs Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I667" t="n">
+        <v>0</v>
+      </c>
+      <c r="J667" t="n">
+        <v>0</v>
+      </c>
+      <c r="K667" t="n">
+        <v>0</v>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Cardiff City</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I668" t="n">
+        <v>0</v>
+      </c>
+      <c r="J668" t="n">
+        <v>0</v>
+      </c>
+      <c r="K668" t="n">
+        <v>0</v>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers vs Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I669" t="n">
+        <v>0</v>
+      </c>
+      <c r="J669" t="n">
+        <v>0</v>
+      </c>
+      <c r="K669" t="n">
+        <v>0</v>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion vs Watford</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I670" t="n">
+        <v>0</v>
+      </c>
+      <c r="J670" t="n">
+        <v>0</v>
+      </c>
+      <c r="K670" t="n">
+        <v>0</v>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Kilmarnock</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I671" t="n">
+        <v>0</v>
+      </c>
+      <c r="J671" t="n">
+        <v>0</v>
+      </c>
+      <c r="K671" t="n">
+        <v>0</v>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Dundee United vs Falkirk</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I672" t="n">
+        <v>0</v>
+      </c>
+      <c r="J672" t="n">
+        <v>0</v>
+      </c>
+      <c r="K672" t="n">
+        <v>0</v>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Rangers vs Motherwell</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr"/>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I673" t="n">
+        <v>0</v>
+      </c>
+      <c r="J673" t="n">
+        <v>0</v>
+      </c>
+      <c r="K673" t="n">
+        <v>0</v>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Athletic Club vs Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I674" t="n">
+        <v>0</v>
+      </c>
+      <c r="J674" t="n">
+        <v>0</v>
+      </c>
+      <c r="K674" t="n">
+        <v>0</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Sporting Gijón vs Girona</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I675" t="n">
+        <v>0</v>
+      </c>
+      <c r="J675" t="n">
+        <v>0</v>
+      </c>
+      <c r="K675" t="n">
+        <v>0</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen vs Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I676" t="n">
+        <v>0</v>
+      </c>
+      <c r="J676" t="n">
+        <v>0</v>
+      </c>
+      <c r="K676" t="n">
+        <v>0</v>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Estrela vs FC Famalicao</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>FC Famalicao</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I677" t="n">
+        <v>0</v>
+      </c>
+      <c r="J677" t="n">
+        <v>0</v>
+      </c>
+      <c r="K677" t="n">
+        <v>0</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Lens vs Lorient</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I678" t="n">
+        <v>0</v>
+      </c>
+      <c r="J678" t="n">
+        <v>0</v>
+      </c>
+      <c r="K678" t="n">
+        <v>0</v>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Al Taawoun vs Al Fateh</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Al Taawoun</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I679" t="n">
+        <v>1</v>
+      </c>
+      <c r="J679" t="n">
+        <v>0</v>
+      </c>
+      <c r="K679" t="n">
+        <v>0</v>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Internazionale vs Napoli</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Internazionale</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr"/>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I680" t="n">
+        <v>3</v>
+      </c>
+      <c r="J680" t="n">
+        <v>0</v>
+      </c>
+      <c r="K680" t="n">
+        <v>0</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Volos NFC vs Olympiacos</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I681" t="n">
+        <v>0</v>
+      </c>
+      <c r="J681" t="n">
+        <v>0</v>
+      </c>
+      <c r="K681" t="n">
+        <v>0</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Rostov vs Fakel Voronezh</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I682" t="n">
+        <v>0</v>
+      </c>
+      <c r="J682" t="n">
+        <v>0</v>
+      </c>
+      <c r="K682" t="n">
+        <v>0</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>KV Mechelen vs KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr"/>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I683" t="n">
+        <v>0</v>
+      </c>
+      <c r="J683" t="n">
+        <v>0</v>
+      </c>
+      <c r="K683" t="n">
+        <v>0</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Hull City vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I684" t="n">
+        <v>0</v>
+      </c>
+      <c r="J684" t="n">
+        <v>0</v>
+      </c>
+      <c r="K684" t="n">
+        <v>0</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Schalke 04 vs Bayern Munich</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I685" t="n">
+        <v>3</v>
+      </c>
+      <c r="J685" t="n">
+        <v>0</v>
+      </c>
+      <c r="K685" t="n">
+        <v>0</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano vs Racing Santander</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I686" t="n">
+        <v>1</v>
+      </c>
+      <c r="J686" t="n">
+        <v>0</v>
+      </c>
+      <c r="K686" t="n">
+        <v>0</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>FC Utrecht vs Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>FC Utrecht</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I687" t="n">
+        <v>0</v>
+      </c>
+      <c r="J687" t="n">
+        <v>0</v>
+      </c>
+      <c r="K687" t="n">
+        <v>0</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Alverca vs Braga</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I688" t="n">
+        <v>1</v>
+      </c>
+      <c r="J688" t="n">
+        <v>0</v>
+      </c>
+      <c r="K688" t="n">
+        <v>0</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Maritimo vs Benfica</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I689" t="n">
+        <v>1</v>
+      </c>
+      <c r="J689" t="n">
+        <v>0</v>
+      </c>
+      <c r="K689" t="n">
+        <v>0</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Fenerbahce vs Besiktas</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="inlineStr"/>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I690" t="n">
+        <v>0</v>
+      </c>
+      <c r="J690" t="n">
+        <v>0</v>
+      </c>
+      <c r="K690" t="n">
+        <v>0</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>AEK Athens vs Aris</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I691" t="n">
+        <v>0</v>
+      </c>
+      <c r="J691" t="n">
+        <v>0</v>
+      </c>
+      <c r="K691" t="n">
+        <v>0</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam vs PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I692" t="n">
+        <v>1</v>
+      </c>
+      <c r="J692" t="n">
+        <v>0</v>
+      </c>
+      <c r="K692" t="n">
+        <v>0</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Danubio vs Peñarol</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I693" t="n">
+        <v>0</v>
+      </c>
+      <c r="J693" t="n">
+        <v>0</v>
+      </c>
+      <c r="K693" t="n">
+        <v>0</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Al Ittihad vs Al Nassr</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I694" t="n">
+        <v>0</v>
+      </c>
+      <c r="J694" t="n">
+        <v>0</v>
+      </c>
+      <c r="K694" t="n">
+        <v>0</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Nice vs Le Mans</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I695" t="n">
+        <v>4</v>
+      </c>
+      <c r="J695" t="n">
+        <v>0</v>
+      </c>
+      <c r="K695" t="n">
+        <v>0</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>AS Roma vs Atalanta</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr"/>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I696" t="n">
+        <v>4</v>
+      </c>
+      <c r="J696" t="n">
+        <v>0</v>
+      </c>
+      <c r="K696" t="n">
+        <v>0</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Standard Liege vs Antwerp</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Standard Liege</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I697" t="n">
+        <v>0</v>
+      </c>
+      <c r="J697" t="n">
+        <v>0</v>
+      </c>
+      <c r="K697" t="n">
+        <v>0</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Sint-Truidense vs RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Sint-Truidense</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I698" t="n">
+        <v>0</v>
+      </c>
+      <c r="J698" t="n">
+        <v>0</v>
+      </c>
+      <c r="K698" t="n">
+        <v>0</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Villarreal vs Deportivo</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr"/>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I699" t="n">
+        <v>5</v>
+      </c>
+      <c r="J699" t="n">
+        <v>0</v>
+      </c>
+      <c r="K699" t="n">
+        <v>0</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino vs Bahia</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr"/>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I700" t="n">
+        <v>4</v>
+      </c>
+      <c r="J700" t="n">
+        <v>0</v>
+      </c>
+      <c r="K700" t="n">
+        <v>0</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Swansea City vs Wrexham</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr"/>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I701" t="n">
+        <v>0</v>
+      </c>
+      <c r="J701" t="n">
+        <v>0</v>
+      </c>
+      <c r="K701" t="n">
+        <v>0</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Willem II vs Excelsior</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr"/>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I702" t="n">
+        <v>2</v>
+      </c>
+      <c r="J702" t="n">
+        <v>0</v>
+      </c>
+      <c r="K702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>St Mirren vs Celtic</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr"/>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I703" t="n">
+        <v>0</v>
+      </c>
+      <c r="J703" t="n">
+        <v>0</v>
+      </c>
+      <c r="K703" t="n">
+        <v>0</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Novorizontino vs Avaí</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I704" t="n">
+        <v>2</v>
+      </c>
+      <c r="J704" t="n">
+        <v>0</v>
+      </c>
+      <c r="K704" t="n">
+        <v>0</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Eldense vs Mallorca</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I705" t="n">
+        <v>0</v>
+      </c>
+      <c r="J705" t="n">
+        <v>0</v>
+      </c>
+      <c r="K705" t="n">
+        <v>0</v>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Sporting CP vs C.D. Nacional</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I706" t="n">
+        <v>3</v>
+      </c>
+      <c r="J706" t="n">
+        <v>0</v>
+      </c>
+      <c r="K706" t="n">
+        <v>0</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Gimnasia (Mendoza) vs Boca Juniors</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I707" t="n">
+        <v>0</v>
+      </c>
+      <c r="J707" t="n">
+        <v>0</v>
+      </c>
+      <c r="K707" t="n">
+        <v>0</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Sport Huancayo vs Sport Boys</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Sport Huancayo</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I708" t="n">
+        <v>1</v>
+      </c>
+      <c r="J708" t="n">
+        <v>0</v>
+      </c>
+      <c r="K708" t="n">
+        <v>0</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado vs Montevideo Wanderers</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I709" t="n">
+        <v>0</v>
+      </c>
+      <c r="J709" t="n">
+        <v>0</v>
+      </c>
+      <c r="K709" t="n">
+        <v>0</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Juventude vs Atlético Goianiense</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr"/>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I710" t="n">
+        <v>0</v>
+      </c>
+      <c r="J710" t="n">
+        <v>0</v>
+      </c>
+      <c r="K710" t="n">
+        <v>0</v>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó FC vs Once Caldas</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I711" t="n">
+        <v>5</v>
+      </c>
+      <c r="J711" t="n">
+        <v>0</v>
+      </c>
+      <c r="K711" t="n">
+        <v>0</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>São Paulo vs Atlético-MG</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I712" t="n">
+        <v>3</v>
+      </c>
+      <c r="J712" t="n">
+        <v>0</v>
+      </c>
+      <c r="K712" t="n">
+        <v>0</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Ceará vs Sport</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I713" t="n">
+        <v>2</v>
+      </c>
+      <c r="J713" t="n">
+        <v>0</v>
+      </c>
+      <c r="K713" t="n">
+        <v>0</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Sportivo San Lorenzo vs 2 de Mayo</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>2 de Mayo</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I714" t="n">
+        <v>0</v>
+      </c>
+      <c r="J714" t="n">
+        <v>0</v>
+      </c>
+      <c r="K714" t="n">
+        <v>0</v>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>San Lorenzo vs Talleres (Córdoba)</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr"/>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I715" t="n">
+        <v>1</v>
+      </c>
+      <c r="J715" t="n">
+        <v>0</v>
+      </c>
+      <c r="K715" t="n">
+        <v>0</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Atlético de San Luis vs Guadalajara</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr"/>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I716" t="n">
+        <v>0</v>
+      </c>
+      <c r="J716" t="n">
+        <v>0</v>
+      </c>
+      <c r="K716" t="n">
+        <v>0</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Independiente del Valle vs Macará</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I717" t="n">
+        <v>0</v>
+      </c>
+      <c r="J717" t="n">
+        <v>0</v>
+      </c>
+      <c r="K717" t="n">
+        <v>0</v>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Detroit City FC vs Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I718" t="n">
+        <v>0</v>
+      </c>
+      <c r="J718" t="n">
+        <v>0</v>
+      </c>
+      <c r="K718" t="n">
+        <v>0</v>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Indy Eleven vs Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I719" t="n">
+        <v>0</v>
+      </c>
+      <c r="J719" t="n">
+        <v>0</v>
+      </c>
+      <c r="K719" t="n">
+        <v>0</v>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Miami FC vs Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I720" t="n">
+        <v>0</v>
+      </c>
+      <c r="J720" t="n">
+        <v>0</v>
+      </c>
+      <c r="K720" t="n">
+        <v>0</v>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Sporting JAX vs Lexington</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I721" t="n">
+        <v>0</v>
+      </c>
+      <c r="J721" t="n">
+        <v>0</v>
+      </c>
+      <c r="K721" t="n">
+        <v>0</v>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Chattanooga Red Wolves vs Greenville Triumph</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Chattanooga Red Wolves</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I722" t="n">
+        <v>0</v>
+      </c>
+      <c r="J722" t="n">
+        <v>0</v>
+      </c>
+      <c r="K722" t="n">
+        <v>0</v>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo vs Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I723" t="n">
+        <v>0</v>
+      </c>
+      <c r="J723" t="n">
+        <v>0</v>
+      </c>
+      <c r="K723" t="n">
+        <v>0</v>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Philadelphia Union vs CF Montréal</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr"/>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I724" t="n">
+        <v>0</v>
+      </c>
+      <c r="J724" t="n">
+        <v>0</v>
+      </c>
+      <c r="K724" t="n">
+        <v>0</v>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Orlando City SC vs San Diego FC</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Orlando City SC</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr"/>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I725" t="n">
+        <v>0</v>
+      </c>
+      <c r="J725" t="n">
+        <v>0</v>
+      </c>
+      <c r="K725" t="n">
+        <v>0</v>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Columbus Crew vs Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr"/>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I726" t="n">
+        <v>0</v>
+      </c>
+      <c r="J726" t="n">
+        <v>0</v>
+      </c>
+      <c r="K726" t="n">
+        <v>0</v>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Toronto FC vs Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr"/>
+      <c r="F727" t="inlineStr"/>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I727" t="n">
+        <v>0</v>
+      </c>
+      <c r="J727" t="n">
+        <v>0</v>
+      </c>
+      <c r="K727" t="n">
+        <v>0</v>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Houston Dynamo FC</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr"/>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I728" t="n">
+        <v>0</v>
+      </c>
+      <c r="J728" t="n">
+        <v>0</v>
+      </c>
+      <c r="K728" t="n">
+        <v>0</v>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Rhode Island FC vs Louisville City FC</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr"/>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I729" t="n">
+        <v>0</v>
+      </c>
+      <c r="J729" t="n">
+        <v>0</v>
+      </c>
+      <c r="K729" t="n">
+        <v>0</v>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies vs Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr"/>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I730" t="n">
+        <v>0</v>
+      </c>
+      <c r="J730" t="n">
+        <v>0</v>
+      </c>
+      <c r="K730" t="n">
+        <v>0</v>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Sarasota Paradise vs Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I731" t="n">
+        <v>0</v>
+      </c>
+      <c r="J731" t="n">
+        <v>0</v>
+      </c>
+      <c r="K731" t="n">
+        <v>0</v>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Fluminense vs Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I732" t="n">
+        <v>0</v>
+      </c>
+      <c r="J732" t="n">
+        <v>0</v>
+      </c>
+      <c r="K732" t="n">
+        <v>0</v>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Universidad de Chile vs Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J733" t="n">
+        <v>0</v>
+      </c>
+      <c r="K733" t="n">
+        <v>0</v>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Union Omaha vs Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Union Omaha</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I734" t="n">
+        <v>0</v>
+      </c>
+      <c r="J734" t="n">
+        <v>0</v>
+      </c>
+      <c r="K734" t="n">
+        <v>0</v>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>FC Naples vs Athletic Club Boise</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Athletic Club Boise</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr"/>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I735" t="n">
+        <v>0</v>
+      </c>
+      <c r="J735" t="n">
+        <v>0</v>
+      </c>
+      <c r="K735" t="n">
+        <v>0</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield vs Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I736" t="n">
+        <v>0</v>
+      </c>
+      <c r="J736" t="n">
+        <v>0</v>
+      </c>
+      <c r="K736" t="n">
+        <v>0</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>FC Dallas vs Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr"/>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I737" t="n">
+        <v>0</v>
+      </c>
+      <c r="J737" t="n">
+        <v>0</v>
+      </c>
+      <c r="K737" t="n">
+        <v>0</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Austin FC vs San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I738" t="n">
+        <v>0</v>
+      </c>
+      <c r="J738" t="n">
+        <v>0</v>
+      </c>
+      <c r="K738" t="n">
+        <v>0</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>San Antonio FC vs FC Tulsa</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>San Antonio FC</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I739" t="n">
+        <v>0</v>
+      </c>
+      <c r="J739" t="n">
+        <v>0</v>
+      </c>
+      <c r="K739" t="n">
+        <v>0</v>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Corpus Christi FC vs Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I740" t="n">
+        <v>0</v>
+      </c>
+      <c r="J740" t="n">
+        <v>0</v>
+      </c>
+      <c r="K740" t="n">
+        <v>0</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Necaxa</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr"/>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I741" t="n">
+        <v>0</v>
+      </c>
+      <c r="J741" t="n">
+        <v>0</v>
+      </c>
+      <c r="K741" t="n">
+        <v>0</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Orange County SC vs Sacramento Republic FC</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr"/>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I742" t="n">
+        <v>0</v>
+      </c>
+      <c r="J742" t="n">
+        <v>0</v>
+      </c>
+      <c r="K742" t="n">
+        <v>0</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Inter Miami CF vs Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I743" t="n">
+        <v>0</v>
+      </c>
+      <c r="J743" t="n">
+        <v>0</v>
+      </c>
+      <c r="K743" t="n">
+        <v>0</v>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Real Salt Lake vs LAFC</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>LAFC</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I744" t="n">
+        <v>0</v>
+      </c>
+      <c r="J744" t="n">
+        <v>0</v>
+      </c>
+      <c r="K744" t="n">
+        <v>0</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Atlético Junior vs Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Atlético Junior</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I745" t="n">
+        <v>0</v>
+      </c>
+      <c r="J745" t="n">
+        <v>0</v>
+      </c>
+      <c r="K745" t="n">
+        <v>0</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Universitario vs Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I746" t="n">
+        <v>0</v>
+      </c>
+      <c r="J746" t="n">
+        <v>0</v>
+      </c>
+      <c r="K746" t="n">
+        <v>0</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>FC Cincinnati vs D.C. United</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I747" t="n">
+        <v>0</v>
+      </c>
+      <c r="J747" t="n">
+        <v>0</v>
+      </c>
+      <c r="K747" t="n">
+        <v>0</v>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Monterey Bay vs Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I748" t="n">
+        <v>0</v>
+      </c>
+      <c r="J748" t="n">
+        <v>0</v>
+      </c>
+      <c r="K748" t="n">
+        <v>0</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I749" t="n">
+        <v>0</v>
+      </c>
+      <c r="J749" t="n">
+        <v>0</v>
+      </c>
+      <c r="K749" t="n">
+        <v>0</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Portland Timbers vs Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>5-4</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I750" t="n">
+        <v>0</v>
+      </c>
+      <c r="J750" t="n">
+        <v>0</v>
+      </c>
+      <c r="K750" t="n">
+        <v>0</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights FC vs New Mexico United</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights FC</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr"/>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I751" t="n">
+        <v>0</v>
+      </c>
+      <c r="J751" t="n">
+        <v>0</v>
+      </c>
+      <c r="K751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>AV Alta FC vs One Knoxville</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>One Knoxville</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I752" t="n">
+        <v>0</v>
+      </c>
+      <c r="J752" t="n">
+        <v>0</v>
+      </c>
+      <c r="K752" t="n">
+        <v>0</v>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Atlas vs Atlante</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I753" t="n">
+        <v>0</v>
+      </c>
+      <c r="J753" t="n">
+        <v>0</v>
+      </c>
+      <c r="K753" t="n">
+        <v>0</v>
+      </c>
+      <c r="L753" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -30341,7 +35331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30804,6 +35794,25 @@
       </c>
       <c r="E25" t="n">
         <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>106</v>
+      </c>
+      <c r="C26" t="n">
+        <v>78</v>
+      </c>
+      <c r="D26" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -30817,7 +35826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32632,6 +37641,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>8</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>7</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>4</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>6</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L753"/>
+  <dimension ref="A1:L846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30253,8 +30253,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E648" t="inlineStr"/>
-      <c r="F648" t="inlineStr"/>
       <c r="G648" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -30301,8 +30299,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E649" t="inlineStr"/>
-      <c r="F649" t="inlineStr"/>
       <c r="G649" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -30349,8 +30345,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E650" t="inlineStr"/>
-      <c r="F650" t="inlineStr"/>
       <c r="G650" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -30397,8 +30391,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E651" t="inlineStr"/>
-      <c r="F651" t="inlineStr"/>
       <c r="G651" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -30445,8 +30437,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E652" t="inlineStr"/>
-      <c r="F652" t="inlineStr"/>
       <c r="G652" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -30493,8 +30483,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E653" t="inlineStr"/>
-      <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -30541,8 +30529,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E654" t="inlineStr"/>
-      <c r="F654" t="inlineStr"/>
       <c r="G654" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -30589,8 +30575,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E655" t="inlineStr"/>
-      <c r="F655" t="inlineStr"/>
       <c r="G655" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -30637,8 +30621,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E656" t="inlineStr"/>
-      <c r="F656" t="inlineStr"/>
       <c r="G656" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -30685,8 +30667,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E657" t="inlineStr"/>
-      <c r="F657" t="inlineStr"/>
       <c r="G657" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -30733,8 +30713,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E658" t="inlineStr"/>
-      <c r="F658" t="inlineStr"/>
       <c r="G658" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -30781,8 +30759,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E659" t="inlineStr"/>
-      <c r="F659" t="inlineStr"/>
       <c r="G659" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -30829,8 +30805,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E660" t="inlineStr"/>
-      <c r="F660" t="inlineStr"/>
       <c r="G660" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -30877,8 +30851,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
       <c r="G661" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -30925,8 +30897,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E662" t="inlineStr"/>
-      <c r="F662" t="inlineStr"/>
       <c r="G662" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -30973,8 +30943,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
       <c r="G663" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -31021,8 +30989,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
       <c r="G664" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -31069,8 +31035,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E665" t="inlineStr"/>
-      <c r="F665" t="inlineStr"/>
       <c r="G665" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -31117,8 +31081,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E666" t="inlineStr"/>
-      <c r="F666" t="inlineStr"/>
       <c r="G666" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -31165,8 +31127,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
       <c r="G667" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -31213,8 +31173,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E668" t="inlineStr"/>
-      <c r="F668" t="inlineStr"/>
       <c r="G668" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -31261,8 +31219,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E669" t="inlineStr"/>
-      <c r="F669" t="inlineStr"/>
       <c r="G669" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -31309,8 +31265,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E670" t="inlineStr"/>
-      <c r="F670" t="inlineStr"/>
       <c r="G670" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -31357,8 +31311,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E671" t="inlineStr"/>
-      <c r="F671" t="inlineStr"/>
       <c r="G671" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -31405,8 +31357,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E672" t="inlineStr"/>
-      <c r="F672" t="inlineStr"/>
       <c r="G672" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -31453,8 +31403,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E673" t="inlineStr"/>
-      <c r="F673" t="inlineStr"/>
       <c r="G673" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -31501,8 +31449,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E674" t="inlineStr"/>
-      <c r="F674" t="inlineStr"/>
       <c r="G674" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -31549,8 +31495,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E675" t="inlineStr"/>
-      <c r="F675" t="inlineStr"/>
       <c r="G675" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -31597,8 +31541,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E676" t="inlineStr"/>
-      <c r="F676" t="inlineStr"/>
       <c r="G676" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -31645,8 +31587,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E677" t="inlineStr"/>
-      <c r="F677" t="inlineStr"/>
       <c r="G677" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -31693,8 +31633,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E678" t="inlineStr"/>
-      <c r="F678" t="inlineStr"/>
       <c r="G678" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -31741,8 +31679,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E679" t="inlineStr"/>
-      <c r="F679" t="inlineStr"/>
       <c r="G679" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -31789,8 +31725,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E680" t="inlineStr"/>
-      <c r="F680" t="inlineStr"/>
       <c r="G680" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -31837,8 +31771,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E681" t="inlineStr"/>
-      <c r="F681" t="inlineStr"/>
       <c r="G681" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -31885,8 +31817,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E682" t="inlineStr"/>
-      <c r="F682" t="inlineStr"/>
       <c r="G682" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -31933,8 +31863,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E683" t="inlineStr"/>
-      <c r="F683" t="inlineStr"/>
       <c r="G683" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -31981,8 +31909,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E684" t="inlineStr"/>
-      <c r="F684" t="inlineStr"/>
       <c r="G684" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -32029,8 +31955,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E685" t="inlineStr"/>
-      <c r="F685" t="inlineStr"/>
       <c r="G685" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -32077,8 +32001,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E686" t="inlineStr"/>
-      <c r="F686" t="inlineStr"/>
       <c r="G686" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -32125,8 +32047,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E687" t="inlineStr"/>
-      <c r="F687" t="inlineStr"/>
       <c r="G687" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -32173,8 +32093,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E688" t="inlineStr"/>
-      <c r="F688" t="inlineStr"/>
       <c r="G688" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -32221,8 +32139,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E689" t="inlineStr"/>
-      <c r="F689" t="inlineStr"/>
       <c r="G689" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -32269,8 +32185,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E690" t="inlineStr"/>
-      <c r="F690" t="inlineStr"/>
       <c r="G690" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -32317,8 +32231,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E691" t="inlineStr"/>
-      <c r="F691" t="inlineStr"/>
       <c r="G691" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -32365,8 +32277,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E692" t="inlineStr"/>
-      <c r="F692" t="inlineStr"/>
       <c r="G692" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -32413,8 +32323,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E693" t="inlineStr"/>
-      <c r="F693" t="inlineStr"/>
       <c r="G693" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -32461,8 +32369,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E694" t="inlineStr"/>
-      <c r="F694" t="inlineStr"/>
       <c r="G694" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -32509,8 +32415,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E695" t="inlineStr"/>
-      <c r="F695" t="inlineStr"/>
       <c r="G695" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -32557,8 +32461,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E696" t="inlineStr"/>
-      <c r="F696" t="inlineStr"/>
       <c r="G696" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -32605,8 +32507,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E697" t="inlineStr"/>
-      <c r="F697" t="inlineStr"/>
       <c r="G697" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -32653,8 +32553,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
       <c r="G698" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -32701,8 +32599,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr"/>
       <c r="G699" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -32749,8 +32645,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E700" t="inlineStr"/>
-      <c r="F700" t="inlineStr"/>
       <c r="G700" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -32797,8 +32691,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E701" t="inlineStr"/>
-      <c r="F701" t="inlineStr"/>
       <c r="G701" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -32845,8 +32737,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E702" t="inlineStr"/>
-      <c r="F702" t="inlineStr"/>
       <c r="G702" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -32893,8 +32783,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E703" t="inlineStr"/>
-      <c r="F703" t="inlineStr"/>
       <c r="G703" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -32941,8 +32829,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E704" t="inlineStr"/>
-      <c r="F704" t="inlineStr"/>
       <c r="G704" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -32989,8 +32875,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E705" t="inlineStr"/>
-      <c r="F705" t="inlineStr"/>
       <c r="G705" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -33037,8 +32921,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E706" t="inlineStr"/>
-      <c r="F706" t="inlineStr"/>
       <c r="G706" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -33085,8 +32967,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E707" t="inlineStr"/>
-      <c r="F707" t="inlineStr"/>
       <c r="G707" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -33133,8 +33013,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E708" t="inlineStr"/>
-      <c r="F708" t="inlineStr"/>
       <c r="G708" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -33181,8 +33059,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E709" t="inlineStr"/>
-      <c r="F709" t="inlineStr"/>
       <c r="G709" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -33229,8 +33105,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E710" t="inlineStr"/>
-      <c r="F710" t="inlineStr"/>
       <c r="G710" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -33277,8 +33151,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E711" t="inlineStr"/>
-      <c r="F711" t="inlineStr"/>
       <c r="G711" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -33325,8 +33197,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E712" t="inlineStr"/>
-      <c r="F712" t="inlineStr"/>
       <c r="G712" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -33373,8 +33243,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E713" t="inlineStr"/>
-      <c r="F713" t="inlineStr"/>
       <c r="G713" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -33421,8 +33289,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E714" t="inlineStr"/>
-      <c r="F714" t="inlineStr"/>
       <c r="G714" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -33469,8 +33335,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E715" t="inlineStr"/>
-      <c r="F715" t="inlineStr"/>
       <c r="G715" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -33517,8 +33381,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E716" t="inlineStr"/>
-      <c r="F716" t="inlineStr"/>
       <c r="G716" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -33565,8 +33427,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E717" t="inlineStr"/>
-      <c r="F717" t="inlineStr"/>
       <c r="G717" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -33613,8 +33473,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E718" t="inlineStr"/>
-      <c r="F718" t="inlineStr"/>
       <c r="G718" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -33661,8 +33519,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E719" t="inlineStr"/>
-      <c r="F719" t="inlineStr"/>
       <c r="G719" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -33709,8 +33565,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E720" t="inlineStr"/>
-      <c r="F720" t="inlineStr"/>
       <c r="G720" t="inlineStr">
         <is>
           <t>sin resolver</t>
@@ -33757,8 +33611,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E721" t="inlineStr"/>
-      <c r="F721" t="inlineStr"/>
       <c r="G721" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -33805,8 +33657,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E722" t="inlineStr"/>
-      <c r="F722" t="inlineStr"/>
       <c r="G722" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -33853,8 +33703,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E723" t="inlineStr"/>
-      <c r="F723" t="inlineStr"/>
       <c r="G723" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -33901,8 +33749,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E724" t="inlineStr"/>
-      <c r="F724" t="inlineStr"/>
       <c r="G724" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -33949,8 +33795,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E725" t="inlineStr"/>
-      <c r="F725" t="inlineStr"/>
       <c r="G725" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -33997,8 +33841,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E726" t="inlineStr"/>
-      <c r="F726" t="inlineStr"/>
       <c r="G726" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -34045,8 +33887,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr"/>
-      <c r="F727" t="inlineStr"/>
       <c r="G727" t="inlineStr">
         <is>
           <t>4-4</t>
@@ -34093,8 +33933,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E728" t="inlineStr"/>
-      <c r="F728" t="inlineStr"/>
       <c r="G728" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -34141,8 +33979,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E729" t="inlineStr"/>
-      <c r="F729" t="inlineStr"/>
       <c r="G729" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -34189,8 +34025,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E730" t="inlineStr"/>
-      <c r="F730" t="inlineStr"/>
       <c r="G730" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -34237,8 +34071,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E731" t="inlineStr"/>
-      <c r="F731" t="inlineStr"/>
       <c r="G731" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -34285,8 +34117,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E732" t="inlineStr"/>
-      <c r="F732" t="inlineStr"/>
       <c r="G732" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -34333,8 +34163,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E733" t="inlineStr"/>
-      <c r="F733" t="inlineStr"/>
       <c r="G733" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -34381,8 +34209,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E734" t="inlineStr"/>
-      <c r="F734" t="inlineStr"/>
       <c r="G734" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -34429,8 +34255,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E735" t="inlineStr"/>
-      <c r="F735" t="inlineStr"/>
       <c r="G735" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -34477,8 +34301,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E736" t="inlineStr"/>
-      <c r="F736" t="inlineStr"/>
       <c r="G736" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -34525,8 +34347,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E737" t="inlineStr"/>
-      <c r="F737" t="inlineStr"/>
       <c r="G737" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -34573,8 +34393,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E738" t="inlineStr"/>
-      <c r="F738" t="inlineStr"/>
       <c r="G738" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -34621,8 +34439,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E739" t="inlineStr"/>
-      <c r="F739" t="inlineStr"/>
       <c r="G739" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -34669,8 +34485,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E740" t="inlineStr"/>
-      <c r="F740" t="inlineStr"/>
       <c r="G740" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -34717,8 +34531,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E741" t="inlineStr"/>
-      <c r="F741" t="inlineStr"/>
       <c r="G741" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -34765,8 +34577,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E742" t="inlineStr"/>
-      <c r="F742" t="inlineStr"/>
       <c r="G742" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -34813,8 +34623,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E743" t="inlineStr"/>
-      <c r="F743" t="inlineStr"/>
       <c r="G743" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -34861,8 +34669,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E744" t="inlineStr"/>
-      <c r="F744" t="inlineStr"/>
       <c r="G744" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -34909,8 +34715,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E745" t="inlineStr"/>
-      <c r="F745" t="inlineStr"/>
       <c r="G745" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -34957,8 +34761,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E746" t="inlineStr"/>
-      <c r="F746" t="inlineStr"/>
       <c r="G746" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -35005,8 +34807,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E747" t="inlineStr"/>
-      <c r="F747" t="inlineStr"/>
       <c r="G747" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -35053,8 +34853,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E748" t="inlineStr"/>
-      <c r="F748" t="inlineStr"/>
       <c r="G748" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -35101,8 +34899,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E749" t="inlineStr"/>
-      <c r="F749" t="inlineStr"/>
       <c r="G749" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -35149,8 +34945,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E750" t="inlineStr"/>
-      <c r="F750" t="inlineStr"/>
       <c r="G750" t="inlineStr">
         <is>
           <t>5-4</t>
@@ -35197,8 +34991,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E751" t="inlineStr"/>
-      <c r="F751" t="inlineStr"/>
       <c r="G751" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -35245,8 +35037,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E752" t="inlineStr"/>
-      <c r="F752" t="inlineStr"/>
       <c r="G752" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -35293,8 +35083,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E753" t="inlineStr"/>
-      <c r="F753" t="inlineStr"/>
       <c r="G753" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -35315,6 +35103,4470 @@
         <v>0</v>
       </c>
       <c r="L753" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>FC Groningen vs FC Twente</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I754" t="n">
+        <v>0</v>
+      </c>
+      <c r="J754" t="n">
+        <v>0</v>
+      </c>
+      <c r="K754" t="n">
+        <v>0</v>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Chongqing Tonglianglong vs Shanghai Shenhua</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I755" t="n">
+        <v>0</v>
+      </c>
+      <c r="J755" t="n">
+        <v>0</v>
+      </c>
+      <c r="K755" t="n">
+        <v>0</v>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Birmingham City vs Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I756" t="n">
+        <v>0</v>
+      </c>
+      <c r="J756" t="n">
+        <v>0</v>
+      </c>
+      <c r="K756" t="n">
+        <v>0</v>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Gazovik Orenburg vs Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Gazovik Orenburg</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I757" t="n">
+        <v>0</v>
+      </c>
+      <c r="J757" t="n">
+        <v>0</v>
+      </c>
+      <c r="K757" t="n">
+        <v>0</v>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Cercle Brugge KSV vs KAA Gent</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I758" t="n">
+        <v>0</v>
+      </c>
+      <c r="J758" t="n">
+        <v>0</v>
+      </c>
+      <c r="K758" t="n">
+        <v>0</v>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>SpVgg Greuther Fürth vs 1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I759" t="n">
+        <v>0</v>
+      </c>
+      <c r="J759" t="n">
+        <v>0</v>
+      </c>
+      <c r="K759" t="n">
+        <v>0</v>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>VfL Osnabruck vs TSV Eintracht Braunschweig</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>VfL Osnabruck</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I760" t="n">
+        <v>0</v>
+      </c>
+      <c r="J760" t="n">
+        <v>0</v>
+      </c>
+      <c r="K760" t="n">
+        <v>0</v>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Henan vs Chengdu Rongcheng</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Chengdu Rongcheng</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I761" t="n">
+        <v>0</v>
+      </c>
+      <c r="J761" t="n">
+        <v>0</v>
+      </c>
+      <c r="K761" t="n">
+        <v>0</v>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Yunnan Yukun vs Liaoning Tieren</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Yunnan Yukun</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr"/>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I762" t="n">
+        <v>0</v>
+      </c>
+      <c r="J762" t="n">
+        <v>0</v>
+      </c>
+      <c r="K762" t="n">
+        <v>0</v>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Sønderjyske Fodbold vs AC Horsens</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Sønderjyske Fodbold</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr"/>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I763" t="n">
+        <v>0</v>
+      </c>
+      <c r="J763" t="n">
+        <v>0</v>
+      </c>
+      <c r="K763" t="n">
+        <v>0</v>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Örgryte IS vs Hammarby IF</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Hammarby IF</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I764" t="n">
+        <v>0</v>
+      </c>
+      <c r="J764" t="n">
+        <v>0</v>
+      </c>
+      <c r="K764" t="n">
+        <v>0</v>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Eibar vs Granada</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr"/>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I765" t="n">
+        <v>0</v>
+      </c>
+      <c r="J765" t="n">
+        <v>0</v>
+      </c>
+      <c r="K765" t="n">
+        <v>0</v>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Emley AFC vs Bishop Auckland</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Emley AFC</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr"/>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I766" t="n">
+        <v>0</v>
+      </c>
+      <c r="J766" t="n">
+        <v>0</v>
+      </c>
+      <c r="K766" t="n">
+        <v>0</v>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Heerenveen vs AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr"/>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I767" t="n">
+        <v>0</v>
+      </c>
+      <c r="J767" t="n">
+        <v>0</v>
+      </c>
+      <c r="K767" t="n">
+        <v>0</v>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Telstar vs SC Cambuur</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Telstar</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr"/>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I768" t="n">
+        <v>0</v>
+      </c>
+      <c r="J768" t="n">
+        <v>0</v>
+      </c>
+      <c r="K768" t="n">
+        <v>0</v>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Everton vs Manchester United</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I769" t="n">
+        <v>0</v>
+      </c>
+      <c r="J769" t="n">
+        <v>0</v>
+      </c>
+      <c r="K769" t="n">
+        <v>0</v>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Troyes vs Strasbourg</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr"/>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>2-6</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I770" t="n">
+        <v>0</v>
+      </c>
+      <c r="J770" t="n">
+        <v>0</v>
+      </c>
+      <c r="K770" t="n">
+        <v>0</v>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Cerro vs Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr"/>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I771" t="n">
+        <v>0</v>
+      </c>
+      <c r="J771" t="n">
+        <v>0</v>
+      </c>
+      <c r="K771" t="n">
+        <v>0</v>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Virtus Entella vs Vicenza</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Virtus Entella</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr"/>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I772" t="n">
+        <v>0</v>
+      </c>
+      <c r="J772" t="n">
+        <v>0</v>
+      </c>
+      <c r="K772" t="n">
+        <v>0</v>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Modena vs US Avellino</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr"/>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J773" t="n">
+        <v>0</v>
+      </c>
+      <c r="K773" t="n">
+        <v>0</v>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense vs Club Olimpia</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr"/>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I774" t="n">
+        <v>0</v>
+      </c>
+      <c r="J774" t="n">
+        <v>0</v>
+      </c>
+      <c r="K774" t="n">
+        <v>0</v>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Juve Stabia vs Pisa</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr"/>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I775" t="n">
+        <v>0</v>
+      </c>
+      <c r="J775" t="n">
+        <v>0</v>
+      </c>
+      <c r="K775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Hamburg SV vs Mainz</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr"/>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I776" t="n">
+        <v>0</v>
+      </c>
+      <c r="J776" t="n">
+        <v>0</v>
+      </c>
+      <c r="K776" t="n">
+        <v>0</v>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>KV Kortrijk vs Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr"/>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I777" t="n">
+        <v>0</v>
+      </c>
+      <c r="J777" t="n">
+        <v>0</v>
+      </c>
+      <c r="K777" t="n">
+        <v>0</v>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Coritiba vs Mirassol</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr"/>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I778" t="n">
+        <v>0</v>
+      </c>
+      <c r="J778" t="n">
+        <v>0</v>
+      </c>
+      <c r="K778" t="n">
+        <v>0</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs Dundee</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr"/>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I779" t="n">
+        <v>0</v>
+      </c>
+      <c r="J779" t="n">
+        <v>0</v>
+      </c>
+      <c r="K779" t="n">
+        <v>0</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Çorum FK vs Eyupspor</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Çorum FK</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr"/>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I780" t="n">
+        <v>0</v>
+      </c>
+      <c r="J780" t="n">
+        <v>0</v>
+      </c>
+      <c r="K780" t="n">
+        <v>0</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Kasimpasa vs Amed SFK</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Kasimpasa</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr"/>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I781" t="n">
+        <v>0</v>
+      </c>
+      <c r="J781" t="n">
+        <v>0</v>
+      </c>
+      <c r="K781" t="n">
+        <v>0</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Londrina vs Operário PR</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr"/>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I782" t="n">
+        <v>0</v>
+      </c>
+      <c r="J782" t="n">
+        <v>0</v>
+      </c>
+      <c r="K782" t="n">
+        <v>0</v>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Stourbridge vs Rushall Olympic</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Stourbridge</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr"/>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I783" t="n">
+        <v>0</v>
+      </c>
+      <c r="J783" t="n">
+        <v>0</v>
+      </c>
+      <c r="K783" t="n">
+        <v>0</v>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Valencia vs Barcelona</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I784" t="n">
+        <v>0</v>
+      </c>
+      <c r="J784" t="n">
+        <v>0</v>
+      </c>
+      <c r="K784" t="n">
+        <v>0</v>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Real Oviedo vs Burgos</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr"/>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I785" t="n">
+        <v>0</v>
+      </c>
+      <c r="J785" t="n">
+        <v>0</v>
+      </c>
+      <c r="K785" t="n">
+        <v>0</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Santa Clara vs Rio Ave</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I786" t="n">
+        <v>0</v>
+      </c>
+      <c r="J786" t="n">
+        <v>0</v>
+      </c>
+      <c r="K786" t="n">
+        <v>0</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>IF Brommapojkarna vs IF Elfsborg</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>IF Elfsborg</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I787" t="n">
+        <v>0</v>
+      </c>
+      <c r="J787" t="n">
+        <v>0</v>
+      </c>
+      <c r="K787" t="n">
+        <v>0</v>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>ADO Den Haag vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I788" t="n">
+        <v>0</v>
+      </c>
+      <c r="J788" t="n">
+        <v>0</v>
+      </c>
+      <c r="K788" t="n">
+        <v>0</v>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>MVV Maastricht vs Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I789" t="n">
+        <v>0</v>
+      </c>
+      <c r="J789" t="n">
+        <v>0</v>
+      </c>
+      <c r="K789" t="n">
+        <v>0</v>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Miami FC vs Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I790" t="n">
+        <v>0</v>
+      </c>
+      <c r="J790" t="n">
+        <v>0</v>
+      </c>
+      <c r="K790" t="n">
+        <v>0</v>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Angers vs Stade Rennais</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Stade Rennais</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I791" t="n">
+        <v>0</v>
+      </c>
+      <c r="J791" t="n">
+        <v>0</v>
+      </c>
+      <c r="K791" t="n">
+        <v>0</v>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Hellas Verona vs Arezzo</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I792" t="n">
+        <v>0</v>
+      </c>
+      <c r="J792" t="n">
+        <v>0</v>
+      </c>
+      <c r="K792" t="n">
+        <v>0</v>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Arsenal vs Chelsea</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I793" t="n">
+        <v>0</v>
+      </c>
+      <c r="J793" t="n">
+        <v>0</v>
+      </c>
+      <c r="K793" t="n">
+        <v>0</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt vs FC Augsburg</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I794" t="n">
+        <v>0</v>
+      </c>
+      <c r="J794" t="n">
+        <v>0</v>
+      </c>
+      <c r="K794" t="n">
+        <v>0</v>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Bologna vs Sassuolo</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I795" t="n">
+        <v>0</v>
+      </c>
+      <c r="J795" t="n">
+        <v>0</v>
+      </c>
+      <c r="K795" t="n">
+        <v>0</v>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Atromitos vs Kalamata</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I796" t="n">
+        <v>1</v>
+      </c>
+      <c r="J796" t="n">
+        <v>0</v>
+      </c>
+      <c r="K796" t="n">
+        <v>0</v>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Central Español Fútbol Club vs Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I797" t="n">
+        <v>0</v>
+      </c>
+      <c r="J797" t="n">
+        <v>0</v>
+      </c>
+      <c r="K797" t="n">
+        <v>0</v>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Sporting Cristal vs Los Chankas</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Sporting Cristal</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I798" t="n">
+        <v>0</v>
+      </c>
+      <c r="J798" t="n">
+        <v>0</v>
+      </c>
+      <c r="K798" t="n">
+        <v>0</v>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Alavés vs Osasuna</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Alavés</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I799" t="n">
+        <v>3</v>
+      </c>
+      <c r="J799" t="n">
+        <v>0</v>
+      </c>
+      <c r="K799" t="n">
+        <v>0</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Málaga vs Levante</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I800" t="n">
+        <v>1</v>
+      </c>
+      <c r="J800" t="n">
+        <v>0</v>
+      </c>
+      <c r="K800" t="n">
+        <v>0</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Anderlecht vs Racing Genk</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I801" t="n">
+        <v>0</v>
+      </c>
+      <c r="J801" t="n">
+        <v>0</v>
+      </c>
+      <c r="K801" t="n">
+        <v>0</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>OFI Crete vs Kifisia</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>OFI Crete</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I802" t="n">
+        <v>0</v>
+      </c>
+      <c r="J802" t="n">
+        <v>0</v>
+      </c>
+      <c r="K802" t="n">
+        <v>0</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Castellón vs Albacete</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I803" t="n">
+        <v>0</v>
+      </c>
+      <c r="J803" t="n">
+        <v>0</v>
+      </c>
+      <c r="K803" t="n">
+        <v>0</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Levadiakos vs Panetolikos</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I804" t="n">
+        <v>0</v>
+      </c>
+      <c r="J804" t="n">
+        <v>0</v>
+      </c>
+      <c r="K804" t="n">
+        <v>0</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Vitória de Guimaraes vs Casa Pia</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Vitória de Guimaraes</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I805" t="n">
+        <v>4</v>
+      </c>
+      <c r="J805" t="n">
+        <v>0</v>
+      </c>
+      <c r="K805" t="n">
+        <v>0</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Trabzonspor vs Genclerbirligi</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I806" t="n">
+        <v>0</v>
+      </c>
+      <c r="J806" t="n">
+        <v>0</v>
+      </c>
+      <c r="K806" t="n">
+        <v>0</v>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Kocaelispor vs Samsunspor</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I807" t="n">
+        <v>0</v>
+      </c>
+      <c r="J807" t="n">
+        <v>0</v>
+      </c>
+      <c r="K807" t="n">
+        <v>0</v>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Waasland-Beveren vs OH Leuven</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Waasland-Beveren</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I808" t="n">
+        <v>0</v>
+      </c>
+      <c r="J808" t="n">
+        <v>0</v>
+      </c>
+      <c r="K808" t="n">
+        <v>0</v>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Cremonese vs Padova</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I809" t="n">
+        <v>0</v>
+      </c>
+      <c r="J809" t="n">
+        <v>0</v>
+      </c>
+      <c r="K809" t="n">
+        <v>0</v>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I810" t="n">
+        <v>1</v>
+      </c>
+      <c r="J810" t="n">
+        <v>0</v>
+      </c>
+      <c r="K810" t="n">
+        <v>0</v>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I811" t="n">
+        <v>0</v>
+      </c>
+      <c r="J811" t="n">
+        <v>0</v>
+      </c>
+      <c r="K811" t="n">
+        <v>0</v>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>O'Higgins vs Unión La Calera</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I812" t="n">
+        <v>0</v>
+      </c>
+      <c r="J812" t="n">
+        <v>0</v>
+      </c>
+      <c r="K812" t="n">
+        <v>0</v>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Panathinaikos vs PAOK</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I813" t="n">
+        <v>1</v>
+      </c>
+      <c r="J813" t="n">
+        <v>0</v>
+      </c>
+      <c r="K813" t="n">
+        <v>0</v>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Deportivo Garcilaso vs Atlético Grau</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Deportivo Garcilaso</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I814" t="n">
+        <v>0</v>
+      </c>
+      <c r="J814" t="n">
+        <v>0</v>
+      </c>
+      <c r="K814" t="n">
+        <v>0</v>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Marseille vs Paris FC</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I815" t="n">
+        <v>2</v>
+      </c>
+      <c r="J815" t="n">
+        <v>0</v>
+      </c>
+      <c r="K815" t="n">
+        <v>0</v>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Juventus vs AC Milan</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I816" t="n">
+        <v>0</v>
+      </c>
+      <c r="J816" t="n">
+        <v>0</v>
+      </c>
+      <c r="K816" t="n">
+        <v>0</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Espanyol vs Sevilla</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I817" t="n">
+        <v>1</v>
+      </c>
+      <c r="J817" t="n">
+        <v>0</v>
+      </c>
+      <c r="K817" t="n">
+        <v>0</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Internacional vs Santos</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I818" t="n">
+        <v>4</v>
+      </c>
+      <c r="J818" t="n">
+        <v>0</v>
+      </c>
+      <c r="K818" t="n">
+        <v>0</v>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Remo vs Flamengo</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I819" t="n">
+        <v>4</v>
+      </c>
+      <c r="J819" t="n">
+        <v>0</v>
+      </c>
+      <c r="K819" t="n">
+        <v>0</v>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Libertad vs Rubio Ñú</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I820" t="n">
+        <v>0</v>
+      </c>
+      <c r="J820" t="n">
+        <v>0</v>
+      </c>
+      <c r="K820" t="n">
+        <v>0</v>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Almería vs Cádiz</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I821" t="n">
+        <v>0</v>
+      </c>
+      <c r="J821" t="n">
+        <v>0</v>
+      </c>
+      <c r="K821" t="n">
+        <v>0</v>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Gil Vicente vs Académico de Viseu</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I822" t="n">
+        <v>7</v>
+      </c>
+      <c r="J822" t="n">
+        <v>0</v>
+      </c>
+      <c r="K822" t="n">
+        <v>0</v>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Nacional vs Juventud</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I823" t="n">
+        <v>0</v>
+      </c>
+      <c r="J823" t="n">
+        <v>0</v>
+      </c>
+      <c r="K823" t="n">
+        <v>0</v>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Central Córdoba (Santiago del Estero) vs Independiente</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I824" t="n">
+        <v>3</v>
+      </c>
+      <c r="J824" t="n">
+        <v>0</v>
+      </c>
+      <c r="K824" t="n">
+        <v>0</v>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Lanús vs Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I825" t="n">
+        <v>2</v>
+      </c>
+      <c r="J825" t="n">
+        <v>0</v>
+      </c>
+      <c r="K825" t="n">
+        <v>0</v>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Huachipato vs Colo Colo</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I826" t="n">
+        <v>6</v>
+      </c>
+      <c r="J826" t="n">
+        <v>0</v>
+      </c>
+      <c r="K826" t="n">
+        <v>0</v>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Juan Pablo II vs Alianza Lima</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Alianza Lima</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I827" t="n">
+        <v>0</v>
+      </c>
+      <c r="J827" t="n">
+        <v>0</v>
+      </c>
+      <c r="K827" t="n">
+        <v>0</v>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá vs Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr"/>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I828" t="n">
+        <v>3</v>
+      </c>
+      <c r="J828" t="n">
+        <v>0</v>
+      </c>
+      <c r="K828" t="n">
+        <v>0</v>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Delfín vs Universidad Católica (Quito)</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Universidad Católica (Quito)</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr"/>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I829" t="n">
+        <v>0</v>
+      </c>
+      <c r="J829" t="n">
+        <v>0</v>
+      </c>
+      <c r="K829" t="n">
+        <v>0</v>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Botafogo vs Palmeiras</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr"/>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I830" t="n">
+        <v>1</v>
+      </c>
+      <c r="J830" t="n">
+        <v>0</v>
+      </c>
+      <c r="K830" t="n">
+        <v>0</v>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Ponte Preta vs São Bernardo</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr"/>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I831" t="n">
+        <v>3</v>
+      </c>
+      <c r="J831" t="n">
+        <v>0</v>
+      </c>
+      <c r="K831" t="n">
+        <v>0</v>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño vs Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr"/>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I832" t="n">
+        <v>0</v>
+      </c>
+      <c r="J832" t="n">
+        <v>0</v>
+      </c>
+      <c r="K832" t="n">
+        <v>0</v>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine vs Westchester SC</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr"/>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I833" t="n">
+        <v>0</v>
+      </c>
+      <c r="J833" t="n">
+        <v>0</v>
+      </c>
+      <c r="K833" t="n">
+        <v>0</v>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>León vs América</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr"/>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I834" t="n">
+        <v>1</v>
+      </c>
+      <c r="J834" t="n">
+        <v>0</v>
+      </c>
+      <c r="K834" t="n">
+        <v>0</v>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>River Plate vs Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr"/>
+      <c r="F835" t="inlineStr"/>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I835" t="n">
+        <v>1</v>
+      </c>
+      <c r="J835" t="n">
+        <v>0</v>
+      </c>
+      <c r="K835" t="n">
+        <v>0</v>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Corinthians vs Chapecoense</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr"/>
+      <c r="F836" t="inlineStr"/>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I836" t="n">
+        <v>0</v>
+      </c>
+      <c r="J836" t="n">
+        <v>0</v>
+      </c>
+      <c r="K836" t="n">
+        <v>0</v>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Liverpool vs Boston River</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr"/>
+      <c r="F837" t="inlineStr"/>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I837" t="n">
+        <v>0</v>
+      </c>
+      <c r="J837" t="n">
+        <v>0</v>
+      </c>
+      <c r="K837" t="n">
+        <v>0</v>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Palestino vs Universidad de Concepción</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr"/>
+      <c r="F838" t="inlineStr"/>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I838" t="n">
+        <v>1</v>
+      </c>
+      <c r="J838" t="n">
+        <v>0</v>
+      </c>
+      <c r="K838" t="n">
+        <v>0</v>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Tapatío vs Leones Negros</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Tapatío</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr"/>
+      <c r="F839" t="inlineStr"/>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I839" t="n">
+        <v>0</v>
+      </c>
+      <c r="J839" t="n">
+        <v>0</v>
+      </c>
+      <c r="K839" t="n">
+        <v>0</v>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Cruz Azul vs Santos</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr"/>
+      <c r="F840" t="inlineStr"/>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K840" t="n">
+        <v>0</v>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Millonarios</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr"/>
+      <c r="F841" t="inlineStr"/>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J841" t="n">
+        <v>0</v>
+      </c>
+      <c r="K841" t="n">
+        <v>0</v>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Melgar vs ADT</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Melgar</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr"/>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I842" t="n">
+        <v>0</v>
+      </c>
+      <c r="J842" t="n">
+        <v>0</v>
+      </c>
+      <c r="K842" t="n">
+        <v>0</v>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Aucas vs Barcelona SC</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr"/>
+      <c r="F843" t="inlineStr"/>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I843" t="n">
+        <v>0</v>
+      </c>
+      <c r="J843" t="n">
+        <v>0</v>
+      </c>
+      <c r="K843" t="n">
+        <v>0</v>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca vs Libertad (Ecuador)</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I844" t="n">
+        <v>0</v>
+      </c>
+      <c r="J844" t="n">
+        <v>0</v>
+      </c>
+      <c r="K844" t="n">
+        <v>0</v>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Racing Club vs Atlético Tucumán</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr"/>
+      <c r="F845" t="inlineStr"/>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J845" t="n">
+        <v>0</v>
+      </c>
+      <c r="K845" t="n">
+        <v>0</v>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Toluca vs Monterrey</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr"/>
+      <c r="F846" t="inlineStr"/>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I846" t="n">
+        <v>0</v>
+      </c>
+      <c r="J846" t="n">
+        <v>0</v>
+      </c>
+      <c r="K846" t="n">
+        <v>0</v>
+      </c>
+      <c r="L846" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -35331,7 +39583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35813,6 +40065,25 @@
       </c>
       <c r="E26" t="n">
         <v>106</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>93</v>
+      </c>
+      <c r="C27" t="n">
+        <v>67</v>
+      </c>
+      <c r="D27" t="n">
+        <v>72</v>
+      </c>
+      <c r="E27" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -35826,7 +40097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37851,6 +42122,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>16</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>8</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L846"/>
+  <dimension ref="A1:L880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35129,8 +35129,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E754" t="inlineStr"/>
-      <c r="F754" t="inlineStr"/>
       <c r="G754" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -35177,8 +35175,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E755" t="inlineStr"/>
-      <c r="F755" t="inlineStr"/>
       <c r="G755" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -35225,8 +35221,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E756" t="inlineStr"/>
-      <c r="F756" t="inlineStr"/>
       <c r="G756" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -35273,8 +35267,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E757" t="inlineStr"/>
-      <c r="F757" t="inlineStr"/>
       <c r="G757" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -35321,8 +35313,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E758" t="inlineStr"/>
-      <c r="F758" t="inlineStr"/>
       <c r="G758" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -35369,8 +35359,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E759" t="inlineStr"/>
-      <c r="F759" t="inlineStr"/>
       <c r="G759" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -35417,8 +35405,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E760" t="inlineStr"/>
-      <c r="F760" t="inlineStr"/>
       <c r="G760" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -35465,8 +35451,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E761" t="inlineStr"/>
-      <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -35513,8 +35497,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E762" t="inlineStr"/>
-      <c r="F762" t="inlineStr"/>
       <c r="G762" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -35561,8 +35543,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E763" t="inlineStr"/>
-      <c r="F763" t="inlineStr"/>
       <c r="G763" t="inlineStr">
         <is>
           <t>2-5</t>
@@ -35609,8 +35589,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E764" t="inlineStr"/>
-      <c r="F764" t="inlineStr"/>
       <c r="G764" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -35657,8 +35635,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E765" t="inlineStr"/>
-      <c r="F765" t="inlineStr"/>
       <c r="G765" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -35705,8 +35681,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E766" t="inlineStr"/>
-      <c r="F766" t="inlineStr"/>
       <c r="G766" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -35753,8 +35727,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E767" t="inlineStr"/>
-      <c r="F767" t="inlineStr"/>
       <c r="G767" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -35801,8 +35773,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E768" t="inlineStr"/>
-      <c r="F768" t="inlineStr"/>
       <c r="G768" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -35849,8 +35819,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E769" t="inlineStr"/>
-      <c r="F769" t="inlineStr"/>
       <c r="G769" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -35897,8 +35865,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E770" t="inlineStr"/>
-      <c r="F770" t="inlineStr"/>
       <c r="G770" t="inlineStr">
         <is>
           <t>2-6</t>
@@ -35945,8 +35911,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E771" t="inlineStr"/>
-      <c r="F771" t="inlineStr"/>
       <c r="G771" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -35993,8 +35957,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E772" t="inlineStr"/>
-      <c r="F772" t="inlineStr"/>
       <c r="G772" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -36041,8 +36003,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E773" t="inlineStr"/>
-      <c r="F773" t="inlineStr"/>
       <c r="G773" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -36089,8 +36049,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E774" t="inlineStr"/>
-      <c r="F774" t="inlineStr"/>
       <c r="G774" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -36137,8 +36095,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E775" t="inlineStr"/>
-      <c r="F775" t="inlineStr"/>
       <c r="G775" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -36185,8 +36141,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E776" t="inlineStr"/>
-      <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -36233,8 +36187,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E777" t="inlineStr"/>
-      <c r="F777" t="inlineStr"/>
       <c r="G777" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -36281,8 +36233,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E778" t="inlineStr"/>
-      <c r="F778" t="inlineStr"/>
       <c r="G778" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -36329,8 +36279,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E779" t="inlineStr"/>
-      <c r="F779" t="inlineStr"/>
       <c r="G779" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -36377,8 +36325,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E780" t="inlineStr"/>
-      <c r="F780" t="inlineStr"/>
       <c r="G780" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -36425,8 +36371,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E781" t="inlineStr"/>
-      <c r="F781" t="inlineStr"/>
       <c r="G781" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -36473,8 +36417,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E782" t="inlineStr"/>
-      <c r="F782" t="inlineStr"/>
       <c r="G782" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -36521,8 +36463,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E783" t="inlineStr"/>
-      <c r="F783" t="inlineStr"/>
       <c r="G783" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -36569,8 +36509,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E784" t="inlineStr"/>
-      <c r="F784" t="inlineStr"/>
       <c r="G784" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -36617,8 +36555,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E785" t="inlineStr"/>
-      <c r="F785" t="inlineStr"/>
       <c r="G785" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -36665,8 +36601,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E786" t="inlineStr"/>
-      <c r="F786" t="inlineStr"/>
       <c r="G786" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -36713,8 +36647,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E787" t="inlineStr"/>
-      <c r="F787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -36761,8 +36693,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E788" t="inlineStr"/>
-      <c r="F788" t="inlineStr"/>
       <c r="G788" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -36809,8 +36739,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E789" t="inlineStr"/>
-      <c r="F789" t="inlineStr"/>
       <c r="G789" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -36857,8 +36785,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E790" t="inlineStr"/>
-      <c r="F790" t="inlineStr"/>
       <c r="G790" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -36905,8 +36831,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E791" t="inlineStr"/>
-      <c r="F791" t="inlineStr"/>
       <c r="G791" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -36953,8 +36877,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E792" t="inlineStr"/>
-      <c r="F792" t="inlineStr"/>
       <c r="G792" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -37001,8 +36923,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E793" t="inlineStr"/>
-      <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -37049,8 +36969,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E794" t="inlineStr"/>
-      <c r="F794" t="inlineStr"/>
       <c r="G794" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -37097,8 +37015,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E795" t="inlineStr"/>
-      <c r="F795" t="inlineStr"/>
       <c r="G795" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -37145,8 +37061,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E796" t="inlineStr"/>
-      <c r="F796" t="inlineStr"/>
       <c r="G796" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -37193,8 +37107,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E797" t="inlineStr"/>
-      <c r="F797" t="inlineStr"/>
       <c r="G797" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -37241,8 +37153,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E798" t="inlineStr"/>
-      <c r="F798" t="inlineStr"/>
       <c r="G798" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -37289,8 +37199,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E799" t="inlineStr"/>
-      <c r="F799" t="inlineStr"/>
       <c r="G799" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -37337,8 +37245,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E800" t="inlineStr"/>
-      <c r="F800" t="inlineStr"/>
       <c r="G800" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -37385,8 +37291,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E801" t="inlineStr"/>
-      <c r="F801" t="inlineStr"/>
       <c r="G801" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -37433,8 +37337,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E802" t="inlineStr"/>
-      <c r="F802" t="inlineStr"/>
       <c r="G802" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -37481,8 +37383,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E803" t="inlineStr"/>
-      <c r="F803" t="inlineStr"/>
       <c r="G803" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -37529,8 +37429,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E804" t="inlineStr"/>
-      <c r="F804" t="inlineStr"/>
       <c r="G804" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -37577,8 +37475,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E805" t="inlineStr"/>
-      <c r="F805" t="inlineStr"/>
       <c r="G805" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -37625,8 +37521,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E806" t="inlineStr"/>
-      <c r="F806" t="inlineStr"/>
       <c r="G806" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -37673,8 +37567,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E807" t="inlineStr"/>
-      <c r="F807" t="inlineStr"/>
       <c r="G807" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -37721,8 +37613,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E808" t="inlineStr"/>
-      <c r="F808" t="inlineStr"/>
       <c r="G808" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -37769,8 +37659,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E809" t="inlineStr"/>
-      <c r="F809" t="inlineStr"/>
       <c r="G809" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -37817,8 +37705,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E810" t="inlineStr"/>
-      <c r="F810" t="inlineStr"/>
       <c r="G810" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -37865,8 +37751,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E811" t="inlineStr"/>
-      <c r="F811" t="inlineStr"/>
       <c r="G811" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -37913,8 +37797,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E812" t="inlineStr"/>
-      <c r="F812" t="inlineStr"/>
       <c r="G812" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -37961,8 +37843,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E813" t="inlineStr"/>
-      <c r="F813" t="inlineStr"/>
       <c r="G813" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -38009,8 +37889,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E814" t="inlineStr"/>
-      <c r="F814" t="inlineStr"/>
       <c r="G814" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -38057,8 +37935,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E815" t="inlineStr"/>
-      <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -38105,8 +37981,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E816" t="inlineStr"/>
-      <c r="F816" t="inlineStr"/>
       <c r="G816" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -38153,8 +38027,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E817" t="inlineStr"/>
-      <c r="F817" t="inlineStr"/>
       <c r="G817" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -38201,8 +38073,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E818" t="inlineStr"/>
-      <c r="F818" t="inlineStr"/>
       <c r="G818" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -38249,8 +38119,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E819" t="inlineStr"/>
-      <c r="F819" t="inlineStr"/>
       <c r="G819" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -38297,8 +38165,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E820" t="inlineStr"/>
-      <c r="F820" t="inlineStr"/>
       <c r="G820" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -38345,8 +38211,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E821" t="inlineStr"/>
-      <c r="F821" t="inlineStr"/>
       <c r="G821" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -38393,8 +38257,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E822" t="inlineStr"/>
-      <c r="F822" t="inlineStr"/>
       <c r="G822" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -38441,8 +38303,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E823" t="inlineStr"/>
-      <c r="F823" t="inlineStr"/>
       <c r="G823" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -38489,8 +38349,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E824" t="inlineStr"/>
-      <c r="F824" t="inlineStr"/>
       <c r="G824" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -38537,8 +38395,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E825" t="inlineStr"/>
-      <c r="F825" t="inlineStr"/>
       <c r="G825" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -38585,8 +38441,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E826" t="inlineStr"/>
-      <c r="F826" t="inlineStr"/>
       <c r="G826" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -38633,8 +38487,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E827" t="inlineStr"/>
-      <c r="F827" t="inlineStr"/>
       <c r="G827" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -38681,8 +38533,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E828" t="inlineStr"/>
-      <c r="F828" t="inlineStr"/>
       <c r="G828" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -38729,8 +38579,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E829" t="inlineStr"/>
-      <c r="F829" t="inlineStr"/>
       <c r="G829" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -38777,8 +38625,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E830" t="inlineStr"/>
-      <c r="F830" t="inlineStr"/>
       <c r="G830" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -38825,8 +38671,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E831" t="inlineStr"/>
-      <c r="F831" t="inlineStr"/>
       <c r="G831" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -38873,8 +38717,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E832" t="inlineStr"/>
-      <c r="F832" t="inlineStr"/>
       <c r="G832" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -38921,8 +38763,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E833" t="inlineStr"/>
-      <c r="F833" t="inlineStr"/>
       <c r="G833" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -38969,8 +38809,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E834" t="inlineStr"/>
-      <c r="F834" t="inlineStr"/>
       <c r="G834" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -39017,8 +38855,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E835" t="inlineStr"/>
-      <c r="F835" t="inlineStr"/>
       <c r="G835" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -39065,8 +38901,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E836" t="inlineStr"/>
-      <c r="F836" t="inlineStr"/>
       <c r="G836" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -39113,8 +38947,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E837" t="inlineStr"/>
-      <c r="F837" t="inlineStr"/>
       <c r="G837" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -39161,8 +38993,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E838" t="inlineStr"/>
-      <c r="F838" t="inlineStr"/>
       <c r="G838" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -39209,8 +39039,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E839" t="inlineStr"/>
-      <c r="F839" t="inlineStr"/>
       <c r="G839" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -39257,8 +39085,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E840" t="inlineStr"/>
-      <c r="F840" t="inlineStr"/>
       <c r="G840" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -39305,8 +39131,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E841" t="inlineStr"/>
-      <c r="F841" t="inlineStr"/>
       <c r="G841" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -39353,8 +39177,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E842" t="inlineStr"/>
-      <c r="F842" t="inlineStr"/>
       <c r="G842" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -39401,8 +39223,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E843" t="inlineStr"/>
-      <c r="F843" t="inlineStr"/>
       <c r="G843" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -39449,8 +39269,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E844" t="inlineStr"/>
-      <c r="F844" t="inlineStr"/>
       <c r="G844" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -39497,8 +39315,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E845" t="inlineStr"/>
-      <c r="F845" t="inlineStr"/>
       <c r="G845" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -39545,8 +39361,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E846" t="inlineStr"/>
-      <c r="F846" t="inlineStr"/>
       <c r="G846" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -39567,6 +39381,1638 @@
         <v>0</v>
       </c>
       <c r="L846" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Asteras Tripoli vs Iraklis</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Asteras Tripoli</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr"/>
+      <c r="F847" t="inlineStr"/>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I847" t="n">
+        <v>0</v>
+      </c>
+      <c r="J847" t="n">
+        <v>0</v>
+      </c>
+      <c r="K847" t="n">
+        <v>0</v>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Al Khaleej vs Al Riyadh</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr"/>
+      <c r="F848" t="inlineStr"/>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I848" t="n">
+        <v>0</v>
+      </c>
+      <c r="J848" t="n">
+        <v>0</v>
+      </c>
+      <c r="K848" t="n">
+        <v>0</v>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Cagliari vs Lecce</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr"/>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I849" t="n">
+        <v>0</v>
+      </c>
+      <c r="J849" t="n">
+        <v>0</v>
+      </c>
+      <c r="K849" t="n">
+        <v>0</v>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs FC Nordsjælland</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr"/>
+      <c r="F850" t="inlineStr"/>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I850" t="n">
+        <v>0</v>
+      </c>
+      <c r="J850" t="n">
+        <v>0</v>
+      </c>
+      <c r="K850" t="n">
+        <v>0</v>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Kalmar FF vs Djurgården</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr"/>
+      <c r="F851" t="inlineStr"/>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I851" t="n">
+        <v>0</v>
+      </c>
+      <c r="J851" t="n">
+        <v>0</v>
+      </c>
+      <c r="K851" t="n">
+        <v>0</v>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Malmö FF vs AIK</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr"/>
+      <c r="F852" t="inlineStr"/>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I852" t="n">
+        <v>0</v>
+      </c>
+      <c r="J852" t="n">
+        <v>0</v>
+      </c>
+      <c r="K852" t="n">
+        <v>0</v>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Mjällby AIF vs IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Mjällby AIF</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr"/>
+      <c r="F853" t="inlineStr"/>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I853" t="n">
+        <v>0</v>
+      </c>
+      <c r="J853" t="n">
+        <v>0</v>
+      </c>
+      <c r="K853" t="n">
+        <v>0</v>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Goztepe vs Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr"/>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I854" t="n">
+        <v>0</v>
+      </c>
+      <c r="J854" t="n">
+        <v>0</v>
+      </c>
+      <c r="K854" t="n">
+        <v>0</v>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor vs Alanyaspor</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr"/>
+      <c r="F855" t="inlineStr"/>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I855" t="n">
+        <v>0</v>
+      </c>
+      <c r="J855" t="n">
+        <v>0</v>
+      </c>
+      <c r="K855" t="n">
+        <v>0</v>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Albion FC vs Progreso</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Albion FC</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr"/>
+      <c r="F856" t="inlineStr"/>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I856" t="n">
+        <v>0</v>
+      </c>
+      <c r="J856" t="n">
+        <v>0</v>
+      </c>
+      <c r="K856" t="n">
+        <v>0</v>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Jong PSV vs FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Jong PSV</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr"/>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I857" t="n">
+        <v>0</v>
+      </c>
+      <c r="J857" t="n">
+        <v>0</v>
+      </c>
+      <c r="K857" t="n">
+        <v>0</v>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Al Hilal vs Neom SC</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr"/>
+      <c r="F858" t="inlineStr"/>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I858" t="n">
+        <v>0</v>
+      </c>
+      <c r="J858" t="n">
+        <v>0</v>
+      </c>
+      <c r="K858" t="n">
+        <v>0</v>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht vs FC Eindhoven</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr"/>
+      <c r="F859" t="inlineStr"/>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I859" t="n">
+        <v>0</v>
+      </c>
+      <c r="J859" t="n">
+        <v>0</v>
+      </c>
+      <c r="K859" t="n">
+        <v>0</v>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Palermo vs Sampdoria</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr"/>
+      <c r="F860" t="inlineStr"/>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I860" t="n">
+        <v>0</v>
+      </c>
+      <c r="J860" t="n">
+        <v>0</v>
+      </c>
+      <c r="K860" t="n">
+        <v>0</v>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>CD Sabadell vs Córdoba</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>CD Sabadell</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr"/>
+      <c r="F861" t="inlineStr"/>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I861" t="n">
+        <v>0</v>
+      </c>
+      <c r="J861" t="n">
+        <v>0</v>
+      </c>
+      <c r="K861" t="n">
+        <v>0</v>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Nantes vs AS Nancy Lorraine</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr"/>
+      <c r="F862" t="inlineStr"/>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I862" t="n">
+        <v>1</v>
+      </c>
+      <c r="J862" t="n">
+        <v>0</v>
+      </c>
+      <c r="K862" t="n">
+        <v>0</v>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Carshalton Athletic vs Chertsey Town</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Carshalton Athletic</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr"/>
+      <c r="F863" t="inlineStr"/>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I863" t="n">
+        <v>0</v>
+      </c>
+      <c r="J863" t="n">
+        <v>0</v>
+      </c>
+      <c r="K863" t="n">
+        <v>0</v>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Redditch United vs Malvern Town</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Redditch United</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr"/>
+      <c r="F864" t="inlineStr"/>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I864" t="n">
+        <v>0</v>
+      </c>
+      <c r="J864" t="n">
+        <v>0</v>
+      </c>
+      <c r="K864" t="n">
+        <v>0</v>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Swindon Supermarine vs Winslow United</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Swindon Supermarine</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr"/>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I865" t="n">
+        <v>0</v>
+      </c>
+      <c r="J865" t="n">
+        <v>0</v>
+      </c>
+      <c r="K865" t="n">
+        <v>0</v>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Bromley vs AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr"/>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I866" t="n">
+        <v>0</v>
+      </c>
+      <c r="J866" t="n">
+        <v>0</v>
+      </c>
+      <c r="K866" t="n">
+        <v>0</v>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Guaraní vs Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Guaraní</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr"/>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I867" t="n">
+        <v>0</v>
+      </c>
+      <c r="J867" t="n">
+        <v>0</v>
+      </c>
+      <c r="K867" t="n">
+        <v>0</v>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Estoril vs Arouca</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr"/>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I868" t="n">
+        <v>0</v>
+      </c>
+      <c r="J868" t="n">
+        <v>0</v>
+      </c>
+      <c r="K868" t="n">
+        <v>0</v>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Elche vs Real Sociedad</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr"/>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I869" t="n">
+        <v>6</v>
+      </c>
+      <c r="J869" t="n">
+        <v>0</v>
+      </c>
+      <c r="K869" t="n">
+        <v>0</v>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Cerro Porteño vs Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr"/>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I870" t="n">
+        <v>0</v>
+      </c>
+      <c r="J870" t="n">
+        <v>0</v>
+      </c>
+      <c r="K870" t="n">
+        <v>0</v>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Barracas Central vs Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I871" t="n">
+        <v>1</v>
+      </c>
+      <c r="J871" t="n">
+        <v>0</v>
+      </c>
+      <c r="K871" t="n">
+        <v>0</v>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Carabobo vs Estudiantes de Mérida</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Carabobo</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I872" t="n">
+        <v>0</v>
+      </c>
+      <c r="J872" t="n">
+        <v>0</v>
+      </c>
+      <c r="K872" t="n">
+        <v>0</v>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Vitória vs Grêmio</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr"/>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I873" t="n">
+        <v>1</v>
+      </c>
+      <c r="J873" t="n">
+        <v>0</v>
+      </c>
+      <c r="K873" t="n">
+        <v>0</v>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>UCV FC vs Academia Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Academia Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I874" t="n">
+        <v>0</v>
+      </c>
+      <c r="J874" t="n">
+        <v>0</v>
+      </c>
+      <c r="K874" t="n">
+        <v>0</v>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Excursionistas vs Ituzaingó</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Excursionistas</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I875" t="n">
+        <v>0</v>
+      </c>
+      <c r="J875" t="n">
+        <v>0</v>
+      </c>
+      <c r="K875" t="n">
+        <v>0</v>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Deportes Limache vs Cobresal</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr"/>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I876" t="n">
+        <v>3</v>
+      </c>
+      <c r="J876" t="n">
+        <v>0</v>
+      </c>
+      <c r="K876" t="n">
+        <v>0</v>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Emelec vs Manta F.C.</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J877" t="n">
+        <v>0</v>
+      </c>
+      <c r="K877" t="n">
+        <v>0</v>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Mushuc Runa vs Leones</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I878" t="n">
+        <v>0</v>
+      </c>
+      <c r="J878" t="n">
+        <v>0</v>
+      </c>
+      <c r="K878" t="n">
+        <v>0</v>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Orense vs Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Orense</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I879" t="n">
+        <v>0</v>
+      </c>
+      <c r="J879" t="n">
+        <v>0</v>
+      </c>
+      <c r="K879" t="n">
+        <v>0</v>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Atlético Nacional vs Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I880" t="n">
+        <v>0</v>
+      </c>
+      <c r="J880" t="n">
+        <v>0</v>
+      </c>
+      <c r="K880" t="n">
+        <v>0</v>
+      </c>
+      <c r="L880" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -39583,7 +41029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40084,6 +41530,25 @@
       </c>
       <c r="E27" t="n">
         <v>93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>34</v>
+      </c>
+      <c r="C28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -40097,7 +41562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42290,6 +43755,132 @@
         <v>0</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L880"/>
+  <dimension ref="A1:L924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39407,8 +39407,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E847" t="inlineStr"/>
-      <c r="F847" t="inlineStr"/>
       <c r="G847" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -39455,8 +39453,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E848" t="inlineStr"/>
-      <c r="F848" t="inlineStr"/>
       <c r="G848" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -39503,8 +39499,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E849" t="inlineStr"/>
-      <c r="F849" t="inlineStr"/>
       <c r="G849" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -39551,8 +39545,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E850" t="inlineStr"/>
-      <c r="F850" t="inlineStr"/>
       <c r="G850" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -39599,8 +39591,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E851" t="inlineStr"/>
-      <c r="F851" t="inlineStr"/>
       <c r="G851" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -39647,8 +39637,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E852" t="inlineStr"/>
-      <c r="F852" t="inlineStr"/>
       <c r="G852" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -39695,8 +39683,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E853" t="inlineStr"/>
-      <c r="F853" t="inlineStr"/>
       <c r="G853" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -39743,8 +39729,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E854" t="inlineStr"/>
-      <c r="F854" t="inlineStr"/>
       <c r="G854" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -39791,8 +39775,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E855" t="inlineStr"/>
-      <c r="F855" t="inlineStr"/>
       <c r="G855" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -39839,8 +39821,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E856" t="inlineStr"/>
-      <c r="F856" t="inlineStr"/>
       <c r="G856" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -39887,8 +39867,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E857" t="inlineStr"/>
-      <c r="F857" t="inlineStr"/>
       <c r="G857" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -39935,8 +39913,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E858" t="inlineStr"/>
-      <c r="F858" t="inlineStr"/>
       <c r="G858" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -39983,8 +39959,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E859" t="inlineStr"/>
-      <c r="F859" t="inlineStr"/>
       <c r="G859" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -40031,8 +40005,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E860" t="inlineStr"/>
-      <c r="F860" t="inlineStr"/>
       <c r="G860" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -40079,8 +40051,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E861" t="inlineStr"/>
-      <c r="F861" t="inlineStr"/>
       <c r="G861" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -40127,8 +40097,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E862" t="inlineStr"/>
-      <c r="F862" t="inlineStr"/>
       <c r="G862" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -40175,8 +40143,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E863" t="inlineStr"/>
-      <c r="F863" t="inlineStr"/>
       <c r="G863" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -40223,8 +40189,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E864" t="inlineStr"/>
-      <c r="F864" t="inlineStr"/>
       <c r="G864" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -40271,8 +40235,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E865" t="inlineStr"/>
-      <c r="F865" t="inlineStr"/>
       <c r="G865" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -40319,8 +40281,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E866" t="inlineStr"/>
-      <c r="F866" t="inlineStr"/>
       <c r="G866" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -40367,8 +40327,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E867" t="inlineStr"/>
-      <c r="F867" t="inlineStr"/>
       <c r="G867" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -40415,8 +40373,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E868" t="inlineStr"/>
-      <c r="F868" t="inlineStr"/>
       <c r="G868" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -40463,8 +40419,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr"/>
       <c r="G869" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -40511,8 +40465,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E870" t="inlineStr"/>
-      <c r="F870" t="inlineStr"/>
       <c r="G870" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -40559,8 +40511,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E871" t="inlineStr"/>
-      <c r="F871" t="inlineStr"/>
       <c r="G871" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -40607,8 +40557,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E872" t="inlineStr"/>
-      <c r="F872" t="inlineStr"/>
       <c r="G872" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -40655,8 +40603,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E873" t="inlineStr"/>
-      <c r="F873" t="inlineStr"/>
       <c r="G873" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -40703,8 +40649,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E874" t="inlineStr"/>
-      <c r="F874" t="inlineStr"/>
       <c r="G874" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -40751,8 +40695,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E875" t="inlineStr"/>
-      <c r="F875" t="inlineStr"/>
       <c r="G875" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -40799,8 +40741,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr"/>
       <c r="G876" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -40847,8 +40787,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E877" t="inlineStr"/>
-      <c r="F877" t="inlineStr"/>
       <c r="G877" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -40895,8 +40833,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E878" t="inlineStr"/>
-      <c r="F878" t="inlineStr"/>
       <c r="G878" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -40943,8 +40879,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr"/>
       <c r="G879" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -40991,8 +40925,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E880" t="inlineStr"/>
-      <c r="F880" t="inlineStr"/>
       <c r="G880" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -41013,6 +40945,2118 @@
         <v>0</v>
       </c>
       <c r="L880" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>FC Utrecht vs Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>FC Utrecht</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I881" t="n">
+        <v>0</v>
+      </c>
+      <c r="J881" t="n">
+        <v>0</v>
+      </c>
+      <c r="K881" t="n">
+        <v>0</v>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Al Ettifaq vs Al Faisaly</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Al Ettifaq</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I882" t="n">
+        <v>0</v>
+      </c>
+      <c r="J882" t="n">
+        <v>0</v>
+      </c>
+      <c r="K882" t="n">
+        <v>0</v>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>AEK Athens vs LASK Linz</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I883" t="n">
+        <v>0</v>
+      </c>
+      <c r="J883" t="n">
+        <v>0</v>
+      </c>
+      <c r="K883" t="n">
+        <v>0</v>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Club Brugge vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr"/>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I884" t="n">
+        <v>0</v>
+      </c>
+      <c r="J884" t="n">
+        <v>0</v>
+      </c>
+      <c r="K884" t="n">
+        <v>0</v>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen vs Excelsior</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr"/>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I885" t="n">
+        <v>0</v>
+      </c>
+      <c r="J885" t="n">
+        <v>0</v>
+      </c>
+      <c r="K885" t="n">
+        <v>0</v>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Doncaster Rovers vs Huddersfield Town</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Huddersfield Town</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr"/>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I886" t="n">
+        <v>2</v>
+      </c>
+      <c r="J886" t="n">
+        <v>0</v>
+      </c>
+      <c r="K886" t="n">
+        <v>0</v>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Exeter City vs Tottenham Hotspur U21</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Exeter City</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I887" t="n">
+        <v>1</v>
+      </c>
+      <c r="J887" t="n">
+        <v>0</v>
+      </c>
+      <c r="K887" t="n">
+        <v>0</v>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Al Ittihad vs Al Fayha</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I888" t="n">
+        <v>1</v>
+      </c>
+      <c r="J888" t="n">
+        <v>0</v>
+      </c>
+      <c r="K888" t="n">
+        <v>0</v>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Al Qadsiah vs Al Ahli</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Al Qadsiah</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I889" t="n">
+        <v>0</v>
+      </c>
+      <c r="J889" t="n">
+        <v>0</v>
+      </c>
+      <c r="K889" t="n">
+        <v>0</v>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers vs Sheffield United</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I890" t="n">
+        <v>3</v>
+      </c>
+      <c r="J890" t="n">
+        <v>0</v>
+      </c>
+      <c r="K890" t="n">
+        <v>0</v>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Cardiff City vs Stoke City</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Cardiff City</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I891" t="n">
+        <v>4</v>
+      </c>
+      <c r="J891" t="n">
+        <v>0</v>
+      </c>
+      <c r="K891" t="n">
+        <v>0</v>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Southampton vs Swansea City</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr"/>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I892" t="n">
+        <v>3</v>
+      </c>
+      <c r="J892" t="n">
+        <v>0</v>
+      </c>
+      <c r="K892" t="n">
+        <v>0</v>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Watford vs Preston North End</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr"/>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I893" t="n">
+        <v>0</v>
+      </c>
+      <c r="J893" t="n">
+        <v>0</v>
+      </c>
+      <c r="K893" t="n">
+        <v>0</v>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Wrexham vs Burnley</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr"/>
+      <c r="F894" t="inlineStr"/>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I894" t="n">
+        <v>1</v>
+      </c>
+      <c r="J894" t="n">
+        <v>0</v>
+      </c>
+      <c r="K894" t="n">
+        <v>0</v>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth vs Lincoln City</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr"/>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I895" t="n">
+        <v>5</v>
+      </c>
+      <c r="J895" t="n">
+        <v>0</v>
+      </c>
+      <c r="K895" t="n">
+        <v>0</v>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Crystal Palace vs Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I896" t="n">
+        <v>4</v>
+      </c>
+      <c r="J896" t="n">
+        <v>0</v>
+      </c>
+      <c r="K896" t="n">
+        <v>0</v>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Leyton Orient vs Bradford City</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Bradford City</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I897" t="n">
+        <v>2</v>
+      </c>
+      <c r="J897" t="n">
+        <v>0</v>
+      </c>
+      <c r="K897" t="n">
+        <v>0</v>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Sunderland vs Hull City</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr"/>
+      <c r="F898" t="inlineStr"/>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I898" t="n">
+        <v>1</v>
+      </c>
+      <c r="J898" t="n">
+        <v>0</v>
+      </c>
+      <c r="K898" t="n">
+        <v>0</v>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Hitchin Town vs Biggleswade Town</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Hitchin Town</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr"/>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J899" t="n">
+        <v>0</v>
+      </c>
+      <c r="K899" t="n">
+        <v>0</v>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Needham Market vs Stanway Rovers FC</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Needham Market</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr"/>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I900" t="n">
+        <v>0</v>
+      </c>
+      <c r="J900" t="n">
+        <v>0</v>
+      </c>
+      <c r="K900" t="n">
+        <v>0</v>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Worcester City vs Knowle</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Worcester City</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr"/>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I901" t="n">
+        <v>0</v>
+      </c>
+      <c r="J901" t="n">
+        <v>0</v>
+      </c>
+      <c r="K901" t="n">
+        <v>0</v>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Annan Athletic vs Motherwell B</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Annan Athletic</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr"/>
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I902" t="n">
+        <v>0</v>
+      </c>
+      <c r="J902" t="n">
+        <v>0</v>
+      </c>
+      <c r="K902" t="n">
+        <v>0</v>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Banks O'Dee vs Forfar Athletic</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Forfar Athletic</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I903" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" t="n">
+        <v>0</v>
+      </c>
+      <c r="K903" t="n">
+        <v>0</v>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Berwick Rangers vs Hibernian B</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Berwick Rangers</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I904" t="n">
+        <v>0</v>
+      </c>
+      <c r="J904" t="n">
+        <v>0</v>
+      </c>
+      <c r="K904" t="n">
+        <v>0</v>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Clyde vs East Fife</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>East Fife</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I905" t="n">
+        <v>0</v>
+      </c>
+      <c r="J905" t="n">
+        <v>0</v>
+      </c>
+      <c r="K905" t="n">
+        <v>0</v>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Clydebank vs Alloa Athletic</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Alloa Athletic</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I906" t="n">
+        <v>1</v>
+      </c>
+      <c r="J906" t="n">
+        <v>0</v>
+      </c>
+      <c r="K906" t="n">
+        <v>0</v>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Cove Rangers vs Dumbarton</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Cove Rangers</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I907" t="n">
+        <v>0</v>
+      </c>
+      <c r="J907" t="n">
+        <v>0</v>
+      </c>
+      <c r="K907" t="n">
+        <v>0</v>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Cowdenbeath vs Kilmarnock B</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Cowdenbeath</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I908" t="n">
+        <v>0</v>
+      </c>
+      <c r="J908" t="n">
+        <v>0</v>
+      </c>
+      <c r="K908" t="n">
+        <v>0</v>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Cumbernauld Colts vs Kelty Hearts</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Kelty Hearts</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I909" t="n">
+        <v>0</v>
+      </c>
+      <c r="J909" t="n">
+        <v>0</v>
+      </c>
+      <c r="K909" t="n">
+        <v>0</v>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>East Kilbride vs Bonnyrigg Rose</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>East Kilbride</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I910" t="n">
+        <v>0</v>
+      </c>
+      <c r="J910" t="n">
+        <v>0</v>
+      </c>
+      <c r="K910" t="n">
+        <v>0</v>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Edinburgh City vs Queen of the South</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Queen of the South</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I911" t="n">
+        <v>0</v>
+      </c>
+      <c r="J911" t="n">
+        <v>0</v>
+      </c>
+      <c r="K911" t="n">
+        <v>0</v>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund vs Villarreal</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr"/>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I912" t="n">
+        <v>2</v>
+      </c>
+      <c r="J912" t="n">
+        <v>0</v>
+      </c>
+      <c r="K912" t="n">
+        <v>0</v>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>FC Porto vs Manchester City</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I913" t="n">
+        <v>0</v>
+      </c>
+      <c r="J913" t="n">
+        <v>0</v>
+      </c>
+      <c r="K913" t="n">
+        <v>0</v>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Lille vs Real Betis</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr"/>
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I914" t="n">
+        <v>1</v>
+      </c>
+      <c r="J914" t="n">
+        <v>0</v>
+      </c>
+      <c r="K914" t="n">
+        <v>0</v>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Real Madrid vs Internazionale</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I915" t="n">
+        <v>3</v>
+      </c>
+      <c r="J915" t="n">
+        <v>0</v>
+      </c>
+      <c r="K915" t="n">
+        <v>0</v>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs West Ham United</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I916" t="n">
+        <v>4</v>
+      </c>
+      <c r="J916" t="n">
+        <v>0</v>
+      </c>
+      <c r="K916" t="n">
+        <v>0</v>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Millwall vs Newcastle United</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr"/>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I917" t="n">
+        <v>5</v>
+      </c>
+      <c r="J917" t="n">
+        <v>0</v>
+      </c>
+      <c r="K917" t="n">
+        <v>0</v>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe vs Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I918" t="n">
+        <v>2</v>
+      </c>
+      <c r="J918" t="n">
+        <v>0</v>
+      </c>
+      <c r="K918" t="n">
+        <v>0</v>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Aurora vs Real Potosí</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I919" t="n">
+        <v>0</v>
+      </c>
+      <c r="J919" t="n">
+        <v>0</v>
+      </c>
+      <c r="K919" t="n">
+        <v>0</v>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Hartford Athletic vs Colorado Springs Switchbacks FC</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I920" t="n">
+        <v>1</v>
+      </c>
+      <c r="J920" t="n">
+        <v>0</v>
+      </c>
+      <c r="K920" t="n">
+        <v>0</v>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Cuiabá vs Athletic</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I921" t="n">
+        <v>1</v>
+      </c>
+      <c r="J921" t="n">
+        <v>0</v>
+      </c>
+      <c r="K921" t="n">
+        <v>0</v>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Criciúma vs Juventude</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I922" t="n">
+        <v>1</v>
+      </c>
+      <c r="J922" t="n">
+        <v>0</v>
+      </c>
+      <c r="K922" t="n">
+        <v>0</v>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Boca Juniors vs São Paulo</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J923" t="n">
+        <v>0</v>
+      </c>
+      <c r="K923" t="n">
+        <v>0</v>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero vs Guabirá</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J924" t="n">
+        <v>0</v>
+      </c>
+      <c r="K924" t="n">
+        <v>0</v>
+      </c>
+      <c r="L924" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -41029,7 +43073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41549,6 +43593,25 @@
       </c>
       <c r="E28" t="n">
         <v>34</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>44</v>
+      </c>
+      <c r="C29" t="n">
+        <v>39</v>
+      </c>
+      <c r="D29" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -41562,7 +43625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43881,6 +45944,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>14</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>9</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L924"/>
+  <dimension ref="A1:L974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40971,8 +40971,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr"/>
       <c r="G881" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -41019,8 +41017,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E882" t="inlineStr"/>
-      <c r="F882" t="inlineStr"/>
       <c r="G882" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -41067,8 +41063,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E883" t="inlineStr"/>
-      <c r="F883" t="inlineStr"/>
       <c r="G883" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -41115,8 +41109,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E884" t="inlineStr"/>
-      <c r="F884" t="inlineStr"/>
       <c r="G884" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -41163,8 +41155,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E885" t="inlineStr"/>
-      <c r="F885" t="inlineStr"/>
       <c r="G885" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -41211,8 +41201,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E886" t="inlineStr"/>
-      <c r="F886" t="inlineStr"/>
       <c r="G886" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -41259,8 +41247,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E887" t="inlineStr"/>
-      <c r="F887" t="inlineStr"/>
       <c r="G887" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -41307,8 +41293,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E888" t="inlineStr"/>
-      <c r="F888" t="inlineStr"/>
       <c r="G888" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -41355,8 +41339,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E889" t="inlineStr"/>
-      <c r="F889" t="inlineStr"/>
       <c r="G889" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -41403,8 +41385,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E890" t="inlineStr"/>
-      <c r="F890" t="inlineStr"/>
       <c r="G890" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -41451,8 +41431,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E891" t="inlineStr"/>
-      <c r="F891" t="inlineStr"/>
       <c r="G891" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -41499,8 +41477,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E892" t="inlineStr"/>
-      <c r="F892" t="inlineStr"/>
       <c r="G892" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -41547,8 +41523,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E893" t="inlineStr"/>
-      <c r="F893" t="inlineStr"/>
       <c r="G893" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -41595,8 +41569,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E894" t="inlineStr"/>
-      <c r="F894" t="inlineStr"/>
       <c r="G894" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -41643,8 +41615,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E895" t="inlineStr"/>
-      <c r="F895" t="inlineStr"/>
       <c r="G895" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -41691,8 +41661,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E896" t="inlineStr"/>
-      <c r="F896" t="inlineStr"/>
       <c r="G896" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -41739,8 +41707,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E897" t="inlineStr"/>
-      <c r="F897" t="inlineStr"/>
       <c r="G897" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -41787,8 +41753,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E898" t="inlineStr"/>
-      <c r="F898" t="inlineStr"/>
       <c r="G898" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -41835,8 +41799,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E899" t="inlineStr"/>
-      <c r="F899" t="inlineStr"/>
       <c r="G899" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -41883,8 +41845,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E900" t="inlineStr"/>
-      <c r="F900" t="inlineStr"/>
       <c r="G900" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -41931,8 +41891,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E901" t="inlineStr"/>
-      <c r="F901" t="inlineStr"/>
       <c r="G901" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -41979,8 +41937,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E902" t="inlineStr"/>
-      <c r="F902" t="inlineStr"/>
       <c r="G902" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -42027,8 +41983,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E903" t="inlineStr"/>
-      <c r="F903" t="inlineStr"/>
       <c r="G903" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -42075,8 +42029,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E904" t="inlineStr"/>
-      <c r="F904" t="inlineStr"/>
       <c r="G904" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -42123,8 +42075,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E905" t="inlineStr"/>
-      <c r="F905" t="inlineStr"/>
       <c r="G905" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -42171,8 +42121,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E906" t="inlineStr"/>
-      <c r="F906" t="inlineStr"/>
       <c r="G906" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -42219,8 +42167,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E907" t="inlineStr"/>
-      <c r="F907" t="inlineStr"/>
       <c r="G907" t="inlineStr">
         <is>
           <t>6-1</t>
@@ -42267,8 +42213,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E908" t="inlineStr"/>
-      <c r="F908" t="inlineStr"/>
       <c r="G908" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -42315,8 +42259,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E909" t="inlineStr"/>
-      <c r="F909" t="inlineStr"/>
       <c r="G909" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -42363,8 +42305,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E910" t="inlineStr"/>
-      <c r="F910" t="inlineStr"/>
       <c r="G910" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -42411,8 +42351,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E911" t="inlineStr"/>
-      <c r="F911" t="inlineStr"/>
       <c r="G911" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -42459,8 +42397,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E912" t="inlineStr"/>
-      <c r="F912" t="inlineStr"/>
       <c r="G912" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -42507,8 +42443,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E913" t="inlineStr"/>
-      <c r="F913" t="inlineStr"/>
       <c r="G913" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -42555,8 +42489,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E914" t="inlineStr"/>
-      <c r="F914" t="inlineStr"/>
       <c r="G914" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -42603,8 +42535,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E915" t="inlineStr"/>
-      <c r="F915" t="inlineStr"/>
       <c r="G915" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -42651,8 +42581,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E916" t="inlineStr"/>
-      <c r="F916" t="inlineStr"/>
       <c r="G916" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -42699,8 +42627,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E917" t="inlineStr"/>
-      <c r="F917" t="inlineStr"/>
       <c r="G917" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -42747,8 +42673,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E918" t="inlineStr"/>
-      <c r="F918" t="inlineStr"/>
       <c r="G918" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -42795,8 +42719,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E919" t="inlineStr"/>
-      <c r="F919" t="inlineStr"/>
       <c r="G919" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -42843,8 +42765,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E920" t="inlineStr"/>
-      <c r="F920" t="inlineStr"/>
       <c r="G920" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -42891,8 +42811,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E921" t="inlineStr"/>
-      <c r="F921" t="inlineStr"/>
       <c r="G921" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -42939,8 +42857,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E922" t="inlineStr"/>
-      <c r="F922" t="inlineStr"/>
       <c r="G922" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -42987,8 +42903,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E923" t="inlineStr"/>
-      <c r="F923" t="inlineStr"/>
       <c r="G923" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -43035,8 +42949,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E924" t="inlineStr"/>
-      <c r="F924" t="inlineStr"/>
       <c r="G924" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -43057,6 +42969,2406 @@
         <v>0</v>
       </c>
       <c r="L924" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Al Kholood vs Al Shabab</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I925" t="n">
+        <v>0</v>
+      </c>
+      <c r="J925" t="n">
+        <v>0</v>
+      </c>
+      <c r="K925" t="n">
+        <v>0</v>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Barcelona vs Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I926" t="n">
+        <v>0</v>
+      </c>
+      <c r="J926" t="n">
+        <v>0</v>
+      </c>
+      <c r="K926" t="n">
+        <v>0</v>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart vs Viking FK</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="inlineStr"/>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I927" t="n">
+        <v>0</v>
+      </c>
+      <c r="J927" t="n">
+        <v>0</v>
+      </c>
+      <c r="K927" t="n">
+        <v>0</v>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>FC Twente vs Telstar</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr"/>
+      <c r="F928" t="inlineStr"/>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I928" t="n">
+        <v>0</v>
+      </c>
+      <c r="J928" t="n">
+        <v>0</v>
+      </c>
+      <c r="K928" t="n">
+        <v>0</v>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns vs Siwelele</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I929" t="n">
+        <v>1</v>
+      </c>
+      <c r="J929" t="n">
+        <v>0</v>
+      </c>
+      <c r="K929" t="n">
+        <v>0</v>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Al Fateh vs Al Diriyah</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Al Diriyah</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I930" t="n">
+        <v>0</v>
+      </c>
+      <c r="J930" t="n">
+        <v>0</v>
+      </c>
+      <c r="K930" t="n">
+        <v>0</v>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Al Nassr vs Abha</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr"/>
+      <c r="F931" t="inlineStr"/>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I931" t="n">
+        <v>2</v>
+      </c>
+      <c r="J931" t="n">
+        <v>0</v>
+      </c>
+      <c r="K931" t="n">
+        <v>0</v>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano vs Los Andes</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr"/>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I932" t="n">
+        <v>0</v>
+      </c>
+      <c r="J932" t="n">
+        <v>0</v>
+      </c>
+      <c r="K932" t="n">
+        <v>0</v>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Derby County vs West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr"/>
+      <c r="F933" t="inlineStr"/>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I933" t="n">
+        <v>5</v>
+      </c>
+      <c r="J933" t="n">
+        <v>0</v>
+      </c>
+      <c r="K933" t="n">
+        <v>0</v>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Norwich City vs Birmingham City</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr"/>
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I934" t="n">
+        <v>2</v>
+      </c>
+      <c r="J934" t="n">
+        <v>0</v>
+      </c>
+      <c r="K934" t="n">
+        <v>0</v>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Rangers vs St Mirren</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr"/>
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I935" t="n">
+        <v>3</v>
+      </c>
+      <c r="J935" t="n">
+        <v>0</v>
+      </c>
+      <c r="K935" t="n">
+        <v>0</v>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Exmouth Town vs Banbury United</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Banbury United</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr"/>
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I936" t="n">
+        <v>0</v>
+      </c>
+      <c r="J936" t="n">
+        <v>0</v>
+      </c>
+      <c r="K936" t="n">
+        <v>0</v>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Bishop Auckland vs Emley AFC</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Emley AFC</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I937" t="n">
+        <v>0</v>
+      </c>
+      <c r="J937" t="n">
+        <v>0</v>
+      </c>
+      <c r="K937" t="n">
+        <v>0</v>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Liverpool vs Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I938" t="n">
+        <v>0</v>
+      </c>
+      <c r="J938" t="n">
+        <v>0</v>
+      </c>
+      <c r="K938" t="n">
+        <v>0</v>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Napoli vs Arsenal</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I939" t="n">
+        <v>3</v>
+      </c>
+      <c r="J939" t="n">
+        <v>0</v>
+      </c>
+      <c r="K939" t="n">
+        <v>0</v>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain vs Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I940" t="n">
+        <v>3</v>
+      </c>
+      <c r="J940" t="n">
+        <v>0</v>
+      </c>
+      <c r="K940" t="n">
+        <v>0</v>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Sporting CP vs Galatasaray</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I941" t="n">
+        <v>2</v>
+      </c>
+      <c r="J941" t="n">
+        <v>0</v>
+      </c>
+      <c r="K941" t="n">
+        <v>0</v>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Charlton Athletic vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr"/>
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I942" t="n">
+        <v>3</v>
+      </c>
+      <c r="J942" t="n">
+        <v>0</v>
+      </c>
+      <c r="K942" t="n">
+        <v>0</v>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>St Johnstone vs Celtic</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr"/>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I943" t="n">
+        <v>2</v>
+      </c>
+      <c r="J943" t="n">
+        <v>0</v>
+      </c>
+      <c r="K943" t="n">
+        <v>0</v>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Real Oruro vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="inlineStr"/>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I944" t="n">
+        <v>0</v>
+      </c>
+      <c r="J944" t="n">
+        <v>0</v>
+      </c>
+      <c r="K944" t="n">
+        <v>0</v>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Chelsea vs Leeds United</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr"/>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>6-3</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I945" t="n">
+        <v>2</v>
+      </c>
+      <c r="J945" t="n">
+        <v>0</v>
+      </c>
+      <c r="K945" t="n">
+        <v>0</v>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Moreirense vs Benfica</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr"/>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I946" t="n">
+        <v>4</v>
+      </c>
+      <c r="J946" t="n">
+        <v>0</v>
+      </c>
+      <c r="K946" t="n">
+        <v>0</v>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>C.D. Platense vs Isidro Metapán</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Isidro Metapán</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr"/>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I947" t="n">
+        <v>0</v>
+      </c>
+      <c r="J947" t="n">
+        <v>0</v>
+      </c>
+      <c r="K947" t="n">
+        <v>0</v>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Deportivo San Pedro vs Deportivo Mixco</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Deportivo San Pedro</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I948" t="n">
+        <v>0</v>
+      </c>
+      <c r="J948" t="n">
+        <v>0</v>
+      </c>
+      <c r="K948" t="n">
+        <v>0</v>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Santos vs Atlético-MG</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr"/>
+      <c r="F949" t="inlineStr"/>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I949" t="n">
+        <v>1</v>
+      </c>
+      <c r="J949" t="n">
+        <v>0</v>
+      </c>
+      <c r="K949" t="n">
+        <v>0</v>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Fortaleza vs Avaí</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="inlineStr"/>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I950" t="n">
+        <v>2</v>
+      </c>
+      <c r="J950" t="n">
+        <v>0</v>
+      </c>
+      <c r="K950" t="n">
+        <v>0</v>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto vs The Strongest</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr"/>
+      <c r="F951" t="inlineStr"/>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I951" t="n">
+        <v>0</v>
+      </c>
+      <c r="J951" t="n">
+        <v>0</v>
+      </c>
+      <c r="K951" t="n">
+        <v>0</v>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Botafogo-SP vs Novorizontino</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr"/>
+      <c r="F952" t="inlineStr"/>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I952" t="n">
+        <v>1</v>
+      </c>
+      <c r="J952" t="n">
+        <v>0</v>
+      </c>
+      <c r="K952" t="n">
+        <v>0</v>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>América de Cali vs Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr"/>
+      <c r="F953" t="inlineStr"/>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I953" t="n">
+        <v>0</v>
+      </c>
+      <c r="J953" t="n">
+        <v>0</v>
+      </c>
+      <c r="K953" t="n">
+        <v>0</v>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Atlanta United FC vs Orlando City SC</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr"/>
+      <c r="F954" t="inlineStr"/>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I954" t="n">
+        <v>0</v>
+      </c>
+      <c r="J954" t="n">
+        <v>0</v>
+      </c>
+      <c r="K954" t="n">
+        <v>0</v>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Toronto FC vs Nashville SC</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr"/>
+      <c r="F955" t="inlineStr"/>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I955" t="n">
+        <v>1</v>
+      </c>
+      <c r="J955" t="n">
+        <v>0</v>
+      </c>
+      <c r="K955" t="n">
+        <v>0</v>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>CF Montréal vs Charlotte FC</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>CF Montréal</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr"/>
+      <c r="F956" t="inlineStr"/>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I956" t="n">
+        <v>1</v>
+      </c>
+      <c r="J956" t="n">
+        <v>0</v>
+      </c>
+      <c r="K956" t="n">
+        <v>0</v>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Operário PR vs CRB</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr"/>
+      <c r="F957" t="inlineStr"/>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I957" t="n">
+        <v>3</v>
+      </c>
+      <c r="J957" t="n">
+        <v>0</v>
+      </c>
+      <c r="K957" t="n">
+        <v>0</v>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Philadelphia Union vs FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr"/>
+      <c r="F958" t="inlineStr"/>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I958" t="n">
+        <v>1</v>
+      </c>
+      <c r="J958" t="n">
+        <v>0</v>
+      </c>
+      <c r="K958" t="n">
+        <v>0</v>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>New York City FC vs New England Revolution</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>New York City FC</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr"/>
+      <c r="F959" t="inlineStr"/>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I959" t="n">
+        <v>0</v>
+      </c>
+      <c r="J959" t="n">
+        <v>0</v>
+      </c>
+      <c r="K959" t="n">
+        <v>0</v>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Once Caldas vs Alianza FC</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr"/>
+      <c r="F960" t="inlineStr"/>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I960" t="n">
+        <v>0</v>
+      </c>
+      <c r="J960" t="n">
+        <v>0</v>
+      </c>
+      <c r="K960" t="n">
+        <v>0</v>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Comunicaciones vs Marquense</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Comunicaciones</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr"/>
+      <c r="F961" t="inlineStr"/>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I961" t="n">
+        <v>0</v>
+      </c>
+      <c r="J961" t="n">
+        <v>0</v>
+      </c>
+      <c r="K961" t="n">
+        <v>0</v>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC vs Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr"/>
+      <c r="F962" t="inlineStr"/>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I962" t="n">
+        <v>0</v>
+      </c>
+      <c r="J962" t="n">
+        <v>0</v>
+      </c>
+      <c r="K962" t="n">
+        <v>0</v>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Minnesota United FC vs FC Dallas</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr"/>
+      <c r="F963" t="inlineStr"/>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I963" t="n">
+        <v>0</v>
+      </c>
+      <c r="J963" t="n">
+        <v>0</v>
+      </c>
+      <c r="K963" t="n">
+        <v>0</v>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr"/>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I964" t="n">
+        <v>0</v>
+      </c>
+      <c r="J964" t="n">
+        <v>0</v>
+      </c>
+      <c r="K964" t="n">
+        <v>0</v>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata vs Corinthians</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr"/>
+      <c r="F965" t="inlineStr"/>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I965" t="n">
+        <v>0</v>
+      </c>
+      <c r="J965" t="n">
+        <v>0</v>
+      </c>
+      <c r="K965" t="n">
+        <v>0</v>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Atlético Goianiense vs Ceará</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Atlético Goianiense</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr"/>
+      <c r="F966" t="inlineStr"/>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I966" t="n">
+        <v>0</v>
+      </c>
+      <c r="J966" t="n">
+        <v>0</v>
+      </c>
+      <c r="K966" t="n">
+        <v>0</v>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>CD Municipal Limeño vs Águila</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Águila</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr"/>
+      <c r="F967" t="inlineStr"/>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I967" t="n">
+        <v>0</v>
+      </c>
+      <c r="J967" t="n">
+        <v>0</v>
+      </c>
+      <c r="K967" t="n">
+        <v>0</v>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Saprissa vs Cartaginés</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Saprissa</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr"/>
+      <c r="F968" t="inlineStr"/>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I968" t="n">
+        <v>0</v>
+      </c>
+      <c r="J968" t="n">
+        <v>0</v>
+      </c>
+      <c r="K968" t="n">
+        <v>0</v>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto vs Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr"/>
+      <c r="F969" t="inlineStr"/>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I969" t="n">
+        <v>0</v>
+      </c>
+      <c r="J969" t="n">
+        <v>0</v>
+      </c>
+      <c r="K969" t="n">
+        <v>0</v>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Suchitepequez vs CD Guastatoya</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Suchitepequez</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr"/>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I970" t="n">
+        <v>0</v>
+      </c>
+      <c r="J970" t="n">
+        <v>0</v>
+      </c>
+      <c r="K970" t="n">
+        <v>0</v>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs LA Galaxy</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr"/>
+      <c r="F971" t="inlineStr"/>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I971" t="n">
+        <v>0</v>
+      </c>
+      <c r="J971" t="n">
+        <v>0</v>
+      </c>
+      <c r="K971" t="n">
+        <v>0</v>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>San Diego FC vs San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>San Diego FC</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr"/>
+      <c r="F972" t="inlineStr"/>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I972" t="n">
+        <v>0</v>
+      </c>
+      <c r="J972" t="n">
+        <v>0</v>
+      </c>
+      <c r="K972" t="n">
+        <v>0</v>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Portland Timbers vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr"/>
+      <c r="F973" t="inlineStr"/>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I973" t="n">
+        <v>0</v>
+      </c>
+      <c r="J973" t="n">
+        <v>0</v>
+      </c>
+      <c r="K973" t="n">
+        <v>0</v>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>FC Motagua vs Alianza FC</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>FC Motagua</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr"/>
+      <c r="F974" t="inlineStr"/>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I974" t="n">
+        <v>0</v>
+      </c>
+      <c r="J974" t="n">
+        <v>0</v>
+      </c>
+      <c r="K974" t="n">
+        <v>0</v>
+      </c>
+      <c r="L974" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -43073,7 +45385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43612,6 +45924,25 @@
       </c>
       <c r="E29" t="n">
         <v>44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C30" t="n">
+        <v>41</v>
+      </c>
+      <c r="D30" t="n">
+        <v>82</v>
+      </c>
+      <c r="E30" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -43625,7 +45956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46154,6 +48485,153 @@
         <v>0</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>10</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>8</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>3</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>4</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L974"/>
+  <dimension ref="A1:L990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42995,8 +42995,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E925" t="inlineStr"/>
-      <c r="F925" t="inlineStr"/>
       <c r="G925" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -43043,8 +43041,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E926" t="inlineStr"/>
-      <c r="F926" t="inlineStr"/>
       <c r="G926" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -43091,8 +43087,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E927" t="inlineStr"/>
-      <c r="F927" t="inlineStr"/>
       <c r="G927" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -43139,8 +43133,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E928" t="inlineStr"/>
-      <c r="F928" t="inlineStr"/>
       <c r="G928" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -43187,8 +43179,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E929" t="inlineStr"/>
-      <c r="F929" t="inlineStr"/>
       <c r="G929" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -43235,8 +43225,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E930" t="inlineStr"/>
-      <c r="F930" t="inlineStr"/>
       <c r="G930" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -43283,8 +43271,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E931" t="inlineStr"/>
-      <c r="F931" t="inlineStr"/>
       <c r="G931" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -43331,8 +43317,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E932" t="inlineStr"/>
-      <c r="F932" t="inlineStr"/>
       <c r="G932" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -43379,8 +43363,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E933" t="inlineStr"/>
-      <c r="F933" t="inlineStr"/>
       <c r="G933" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -43427,8 +43409,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E934" t="inlineStr"/>
-      <c r="F934" t="inlineStr"/>
       <c r="G934" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -43475,8 +43455,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E935" t="inlineStr"/>
-      <c r="F935" t="inlineStr"/>
       <c r="G935" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -43523,8 +43501,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E936" t="inlineStr"/>
-      <c r="F936" t="inlineStr"/>
       <c r="G936" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -43571,8 +43547,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E937" t="inlineStr"/>
-      <c r="F937" t="inlineStr"/>
       <c r="G937" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -43619,8 +43593,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E938" t="inlineStr"/>
-      <c r="F938" t="inlineStr"/>
       <c r="G938" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -43667,8 +43639,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E939" t="inlineStr"/>
-      <c r="F939" t="inlineStr"/>
       <c r="G939" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -43715,8 +43685,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E940" t="inlineStr"/>
-      <c r="F940" t="inlineStr"/>
       <c r="G940" t="inlineStr">
         <is>
           <t>6-1</t>
@@ -43763,8 +43731,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E941" t="inlineStr"/>
-      <c r="F941" t="inlineStr"/>
       <c r="G941" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -43811,8 +43777,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E942" t="inlineStr"/>
-      <c r="F942" t="inlineStr"/>
       <c r="G942" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -43859,8 +43823,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E943" t="inlineStr"/>
-      <c r="F943" t="inlineStr"/>
       <c r="G943" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -43907,8 +43869,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E944" t="inlineStr"/>
-      <c r="F944" t="inlineStr"/>
       <c r="G944" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -43955,8 +43915,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E945" t="inlineStr"/>
-      <c r="F945" t="inlineStr"/>
       <c r="G945" t="inlineStr">
         <is>
           <t>6-3</t>
@@ -44003,8 +43961,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E946" t="inlineStr"/>
-      <c r="F946" t="inlineStr"/>
       <c r="G946" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -44051,8 +44007,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E947" t="inlineStr"/>
-      <c r="F947" t="inlineStr"/>
       <c r="G947" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -44099,8 +44053,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E948" t="inlineStr"/>
-      <c r="F948" t="inlineStr"/>
       <c r="G948" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -44147,8 +44099,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E949" t="inlineStr"/>
-      <c r="F949" t="inlineStr"/>
       <c r="G949" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -44195,8 +44145,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E950" t="inlineStr"/>
-      <c r="F950" t="inlineStr"/>
       <c r="G950" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -44243,8 +44191,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E951" t="inlineStr"/>
-      <c r="F951" t="inlineStr"/>
       <c r="G951" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -44291,8 +44237,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E952" t="inlineStr"/>
-      <c r="F952" t="inlineStr"/>
       <c r="G952" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -44339,8 +44283,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E953" t="inlineStr"/>
-      <c r="F953" t="inlineStr"/>
       <c r="G953" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -44387,8 +44329,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E954" t="inlineStr"/>
-      <c r="F954" t="inlineStr"/>
       <c r="G954" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -44435,8 +44375,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E955" t="inlineStr"/>
-      <c r="F955" t="inlineStr"/>
       <c r="G955" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -44483,8 +44421,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E956" t="inlineStr"/>
-      <c r="F956" t="inlineStr"/>
       <c r="G956" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -44531,8 +44467,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E957" t="inlineStr"/>
-      <c r="F957" t="inlineStr"/>
       <c r="G957" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -44579,8 +44513,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E958" t="inlineStr"/>
-      <c r="F958" t="inlineStr"/>
       <c r="G958" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -44627,8 +44559,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E959" t="inlineStr"/>
-      <c r="F959" t="inlineStr"/>
       <c r="G959" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -44675,8 +44605,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E960" t="inlineStr"/>
-      <c r="F960" t="inlineStr"/>
       <c r="G960" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -44723,8 +44651,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E961" t="inlineStr"/>
-      <c r="F961" t="inlineStr"/>
       <c r="G961" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -44771,8 +44697,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E962" t="inlineStr"/>
-      <c r="F962" t="inlineStr"/>
       <c r="G962" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -44819,8 +44743,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E963" t="inlineStr"/>
-      <c r="F963" t="inlineStr"/>
       <c r="G963" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -44867,8 +44789,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E964" t="inlineStr"/>
-      <c r="F964" t="inlineStr"/>
       <c r="G964" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -44915,8 +44835,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E965" t="inlineStr"/>
-      <c r="F965" t="inlineStr"/>
       <c r="G965" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -44963,8 +44881,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E966" t="inlineStr"/>
-      <c r="F966" t="inlineStr"/>
       <c r="G966" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -45011,8 +44927,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E967" t="inlineStr"/>
-      <c r="F967" t="inlineStr"/>
       <c r="G967" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -45059,8 +44973,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E968" t="inlineStr"/>
-      <c r="F968" t="inlineStr"/>
       <c r="G968" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -45107,8 +45019,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E969" t="inlineStr"/>
-      <c r="F969" t="inlineStr"/>
       <c r="G969" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -45155,8 +45065,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E970" t="inlineStr"/>
-      <c r="F970" t="inlineStr"/>
       <c r="G970" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -45203,8 +45111,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E971" t="inlineStr"/>
-      <c r="F971" t="inlineStr"/>
       <c r="G971" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -45251,8 +45157,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E972" t="inlineStr"/>
-      <c r="F972" t="inlineStr"/>
       <c r="G972" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -45299,8 +45203,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E973" t="inlineStr"/>
-      <c r="F973" t="inlineStr"/>
       <c r="G973" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -45347,8 +45249,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E974" t="inlineStr"/>
-      <c r="F974" t="inlineStr"/>
       <c r="G974" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -45369,6 +45269,774 @@
         <v>0</v>
       </c>
       <c r="L974" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Fenerbahce vs AS Roma</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr"/>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I975" t="n">
+        <v>0</v>
+      </c>
+      <c r="J975" t="n">
+        <v>0</v>
+      </c>
+      <c r="K975" t="n">
+        <v>0</v>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Shakhtar Donetsk</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr"/>
+      <c r="F976" t="inlineStr"/>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I976" t="n">
+        <v>0</v>
+      </c>
+      <c r="J976" t="n">
+        <v>0</v>
+      </c>
+      <c r="K976" t="n">
+        <v>0</v>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Panathinaikos vs Kifisia</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr"/>
+      <c r="F977" t="inlineStr"/>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I977" t="n">
+        <v>1</v>
+      </c>
+      <c r="J977" t="n">
+        <v>0</v>
+      </c>
+      <c r="K977" t="n">
+        <v>0</v>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Bayern Munich vs Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr"/>
+      <c r="F978" t="inlineStr"/>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I978" t="n">
+        <v>4</v>
+      </c>
+      <c r="J978" t="n">
+        <v>0</v>
+      </c>
+      <c r="K978" t="n">
+        <v>0</v>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Como vs RB Leipzig</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr"/>
+      <c r="F979" t="inlineStr"/>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I979" t="n">
+        <v>0</v>
+      </c>
+      <c r="J979" t="n">
+        <v>0</v>
+      </c>
+      <c r="K979" t="n">
+        <v>0</v>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Manchester United vs Sabah FK</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr"/>
+      <c r="F980" t="inlineStr"/>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I980" t="n">
+        <v>3</v>
+      </c>
+      <c r="J980" t="n">
+        <v>0</v>
+      </c>
+      <c r="K980" t="n">
+        <v>0</v>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Stevenage vs Luton Town</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Luton Town</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr"/>
+      <c r="F981" t="inlineStr"/>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I981" t="n">
+        <v>1</v>
+      </c>
+      <c r="J981" t="n">
+        <v>0</v>
+      </c>
+      <c r="K981" t="n">
+        <v>0</v>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Estrela vs Braga</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr"/>
+      <c r="F982" t="inlineStr"/>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I982" t="n">
+        <v>1</v>
+      </c>
+      <c r="J982" t="n">
+        <v>0</v>
+      </c>
+      <c r="K982" t="n">
+        <v>0</v>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Aurora FC vs Municipal</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr"/>
+      <c r="F983" t="inlineStr"/>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I983" t="n">
+        <v>0</v>
+      </c>
+      <c r="J983" t="n">
+        <v>0</v>
+      </c>
+      <c r="K983" t="n">
+        <v>0</v>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Vila Nova vs Goiás</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr"/>
+      <c r="F984" t="inlineStr"/>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I984" t="n">
+        <v>1</v>
+      </c>
+      <c r="J984" t="n">
+        <v>0</v>
+      </c>
+      <c r="K984" t="n">
+        <v>0</v>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Always Ready</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr"/>
+      <c r="F985" t="inlineStr"/>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I985" t="n">
+        <v>0</v>
+      </c>
+      <c r="J985" t="n">
+        <v>0</v>
+      </c>
+      <c r="K985" t="n">
+        <v>0</v>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>São Bernardo vs Londrina</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr"/>
+      <c r="F986" t="inlineStr"/>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I986" t="n">
+        <v>0</v>
+      </c>
+      <c r="J986" t="n">
+        <v>0</v>
+      </c>
+      <c r="K986" t="n">
+        <v>0</v>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Sport vs Ponte Preta</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr"/>
+      <c r="F987" t="inlineStr"/>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I987" t="n">
+        <v>0</v>
+      </c>
+      <c r="J987" t="n">
+        <v>0</v>
+      </c>
+      <c r="K987" t="n">
+        <v>0</v>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Millonarios vs Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr"/>
+      <c r="F988" t="inlineStr"/>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I988" t="n">
+        <v>0</v>
+      </c>
+      <c r="J988" t="n">
+        <v>0</v>
+      </c>
+      <c r="K988" t="n">
+        <v>0</v>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>CD Malacateco vs Antigua GFC</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>CD Malacateco</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr"/>
+      <c r="F989" t="inlineStr"/>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I989" t="n">
+        <v>0</v>
+      </c>
+      <c r="J989" t="n">
+        <v>0</v>
+      </c>
+      <c r="K989" t="n">
+        <v>0</v>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Xelajú MC vs Cobán Imperial</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Xelajú MC</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr"/>
+      <c r="F990" t="inlineStr"/>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
+      <c r="J990" t="n">
+        <v>0</v>
+      </c>
+      <c r="K990" t="n">
+        <v>0</v>
+      </c>
+      <c r="L990" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -45385,7 +46053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45943,6 +46611,25 @@
       </c>
       <c r="E30" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -45956,7 +46643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48632,6 +49319,90 @@
         <v>50</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>4</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L990"/>
+  <dimension ref="A1:L1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45295,8 +45295,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E975" t="inlineStr"/>
-      <c r="F975" t="inlineStr"/>
       <c r="G975" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -45343,8 +45341,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E976" t="inlineStr"/>
-      <c r="F976" t="inlineStr"/>
       <c r="G976" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -45391,8 +45387,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E977" t="inlineStr"/>
-      <c r="F977" t="inlineStr"/>
       <c r="G977" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -45439,8 +45433,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E978" t="inlineStr"/>
-      <c r="F978" t="inlineStr"/>
       <c r="G978" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -45487,8 +45479,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E979" t="inlineStr"/>
-      <c r="F979" t="inlineStr"/>
       <c r="G979" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -45535,8 +45525,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E980" t="inlineStr"/>
-      <c r="F980" t="inlineStr"/>
       <c r="G980" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -45583,8 +45571,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E981" t="inlineStr"/>
-      <c r="F981" t="inlineStr"/>
       <c r="G981" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -45631,8 +45617,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E982" t="inlineStr"/>
-      <c r="F982" t="inlineStr"/>
       <c r="G982" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -45679,8 +45663,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E983" t="inlineStr"/>
-      <c r="F983" t="inlineStr"/>
       <c r="G983" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -45727,8 +45709,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E984" t="inlineStr"/>
-      <c r="F984" t="inlineStr"/>
       <c r="G984" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -45775,8 +45755,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E985" t="inlineStr"/>
-      <c r="F985" t="inlineStr"/>
       <c r="G985" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -45823,8 +45801,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E986" t="inlineStr"/>
-      <c r="F986" t="inlineStr"/>
       <c r="G986" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -45871,8 +45847,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E987" t="inlineStr"/>
-      <c r="F987" t="inlineStr"/>
       <c r="G987" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -45919,8 +45893,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E988" t="inlineStr"/>
-      <c r="F988" t="inlineStr"/>
       <c r="G988" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -45967,8 +45939,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E989" t="inlineStr"/>
-      <c r="F989" t="inlineStr"/>
       <c r="G989" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -46015,8 +45985,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E990" t="inlineStr"/>
-      <c r="F990" t="inlineStr"/>
       <c r="G990" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -46037,6 +46005,2694 @@
         <v>0</v>
       </c>
       <c r="L990" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga vs Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr"/>
+      <c r="F991" t="inlineStr"/>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I991" t="n">
+        <v>0</v>
+      </c>
+      <c r="J991" t="n">
+        <v>0</v>
+      </c>
+      <c r="K991" t="n">
+        <v>0</v>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Vissel Kobe vs Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr"/>
+      <c r="F992" t="inlineStr"/>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I992" t="n">
+        <v>0</v>
+      </c>
+      <c r="J992" t="n">
+        <v>0</v>
+      </c>
+      <c r="K992" t="n">
+        <v>0</v>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Al Qadsiah vs Al Ettifaq</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Al Qadsiah</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr"/>
+      <c r="F993" t="inlineStr"/>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I993" t="n">
+        <v>0</v>
+      </c>
+      <c r="J993" t="n">
+        <v>0</v>
+      </c>
+      <c r="K993" t="n">
+        <v>0</v>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Al Faisaly vs Al Ittihad</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr"/>
+      <c r="F994" t="inlineStr"/>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I994" t="n">
+        <v>0</v>
+      </c>
+      <c r="J994" t="n">
+        <v>0</v>
+      </c>
+      <c r="K994" t="n">
+        <v>0</v>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>SV Darmstadt 98 vs Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr"/>
+      <c r="F995" t="inlineStr"/>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I995" t="n">
+        <v>0</v>
+      </c>
+      <c r="J995" t="n">
+        <v>0</v>
+      </c>
+      <c r="K995" t="n">
+        <v>0</v>
+      </c>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>F.C. København vs AC Horsens</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>F.C. København</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr"/>
+      <c r="F996" t="inlineStr"/>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I996" t="n">
+        <v>0</v>
+      </c>
+      <c r="J996" t="n">
+        <v>0</v>
+      </c>
+      <c r="K996" t="n">
+        <v>0</v>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>BK Häcken vs Mjällby AIF</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>BK Häcken</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr"/>
+      <c r="F997" t="inlineStr"/>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I997" t="n">
+        <v>0</v>
+      </c>
+      <c r="J997" t="n">
+        <v>0</v>
+      </c>
+      <c r="K997" t="n">
+        <v>0</v>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Empoli vs Arezzo</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr"/>
+      <c r="F998" t="inlineStr"/>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I998" t="n">
+        <v>1</v>
+      </c>
+      <c r="J998" t="n">
+        <v>0</v>
+      </c>
+      <c r="K998" t="n">
+        <v>0</v>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Stellenbosch vs Sekhukhune United FC</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr"/>
+      <c r="F999" t="inlineStr"/>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I999" t="n">
+        <v>1</v>
+      </c>
+      <c r="J999" t="n">
+        <v>0</v>
+      </c>
+      <c r="K999" t="n">
+        <v>0</v>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar vs Willem II</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr"/>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1000" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Clermont Foot vs Boulogne</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Clermont Foot</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr"/>
+      <c r="F1001" t="inlineStr"/>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1001" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Dijon FCO vs Stade Laval</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Dijon FCO</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr"/>
+      <c r="F1002" t="inlineStr"/>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1002" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Montpellier vs Pau</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr"/>
+      <c r="F1003" t="inlineStr"/>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>AS Nancy Lorraine vs Stade de Reims</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Stade de Reims</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr"/>
+      <c r="F1004" t="inlineStr"/>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1004" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Rodez Aveyron vs Grenoble</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Rodez Aveyron</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr"/>
+      <c r="F1005" t="inlineStr"/>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1005" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1005" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>FC Eindhoven vs FC Dordrecht</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>FC Eindhoven</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr"/>
+      <c r="F1006" t="inlineStr"/>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>FC Emmen vs De Graafschap</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>FC Emmen</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr"/>
+      <c r="F1007" t="inlineStr"/>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1007" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Heracles Almelo vs Jong AZ</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Heracles Almelo</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr"/>
+      <c r="F1008" t="inlineStr"/>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1008" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Jong Ajax vs RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr"/>
+      <c r="F1009" t="inlineStr"/>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1009" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>MVV Maastricht vs Almere City</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr"/>
+      <c r="F1010" t="inlineStr"/>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1010" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>NAC Breda vs Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>NAC Breda</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr"/>
+      <c r="F1011" t="inlineStr"/>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1011" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>VVV-Venlo vs TOP Oss</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>VVV-Venlo</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr"/>
+      <c r="F1012" t="inlineStr"/>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Al Ahli vs Al Hazem</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr"/>
+      <c r="F1013" t="inlineStr"/>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Helmond Sport vs Jong PSV</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Jong PSV</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr"/>
+      <c r="F1014" t="inlineStr"/>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>1. FC Union Berlin vs Schalke 04</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>1. FC Union Berlin</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr"/>
+      <c r="F1015" t="inlineStr"/>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Greenock Morton vs Livingston</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Livingston</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr"/>
+      <c r="F1016" t="inlineStr"/>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1016" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Burgos vs Ceuta</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr"/>
+      <c r="F1017" t="inlineStr"/>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Stade Rennais vs Marseille</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Stade Rennais</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr"/>
+      <c r="F1018" t="inlineStr"/>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Venezia vs Fiorentina</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr"/>
+      <c r="F1019" t="inlineStr"/>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1019" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1019" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>KV Mechelen vs Anderlecht</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr"/>
+      <c r="F1020" t="inlineStr"/>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1020" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Kidderminster Harriers vs Hartlepool United</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Kidderminster Harriers</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr"/>
+      <c r="F1021" t="inlineStr"/>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Stenhousemuir vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr"/>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Sevilla vs Valencia</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr"/>
+      <c r="F1023" t="inlineStr"/>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1023" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>West Ham United vs Wrexham</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr"/>
+      <c r="F1024" t="inlineStr"/>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>6-0</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1024" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Pisa vs Virtus Entella</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr"/>
+      <c r="F1025" t="inlineStr"/>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1025" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano vs Sportivo San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr"/>
+      <c r="F1026" t="inlineStr"/>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>UTC vs Juan Pablo II</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr"/>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1027" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>2 de Mayo vs Libertad</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr"/>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1028" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1028" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Ituzaingó vs Comunicaciones</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Comunicaciones</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr"/>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Aurora</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr"/>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1030" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia vs Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr"/>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1031" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Argentino de Merlo vs Real Pilar</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Real Pilar</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr"/>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>One Knoxville vs FC Naples</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>One Knoxville</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr"/>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1033" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Real Potosí vs Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr"/>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Cusco FC vs Melgar</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr"/>
+      <c r="F1035" t="inlineStr"/>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Boca Juniors vs Central Córdoba (Santiago del Estero)</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr"/>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Necaxa vs Puebla</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr"/>
+      <c r="F1037" t="inlineStr"/>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta) vs Tristán Suárez</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr"/>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Correcaminos UAT vs Cancún FC</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Correcaminos UAT</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr"/>
+      <c r="F1039" t="inlineStr"/>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>CD Estrella Roja vs Platense</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>CD Estrella Roja</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr"/>
+      <c r="F1040" t="inlineStr"/>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe vs Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr"/>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>New Mexico United vs Indy Eleven</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr"/>
+      <c r="F1042" t="inlineStr"/>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Pérez Zeledón vs AD San Carlos</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Pérez Zeledón</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr"/>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Colorado Springs Switchbacks FC vs San Antonio FC</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Colorado Springs Switchbacks FC</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr"/>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Atlante vs Pachuca</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr"/>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Tijuana vs Querétaro</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="inlineStr"/>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1046" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -46053,7 +48709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46630,6 +49286,25 @@
       </c>
       <c r="E31" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>56</v>
+      </c>
+      <c r="C32" t="n">
+        <v>37</v>
+      </c>
+      <c r="D32" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -46643,7 +49318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49403,6 +52078,195 @@
         <v>100</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>7</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>11</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>9</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>13</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>7</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
